--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1368,7 +1368,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="17.85546875" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4.42578125" bestFit="1" customWidth="1" style="70" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="70" min="2" max="2"/>
@@ -2351,7 +2351,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" style="70" min="1" max="1"/>
     <col width="15" customWidth="1" style="70" min="2" max="2"/>
@@ -4837,7 +4837,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.42578125" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.7109375" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -5047,7 +5047,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -9354,7 +9354,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -11227,34 +11227,34 @@
         <v>1564</v>
       </c>
       <c r="E40" s="49" t="n">
+        <v>1566</v>
+      </c>
+      <c r="F40" s="49" t="n">
         <v>1567</v>
       </c>
-      <c r="F40" s="49" t="n">
+      <c r="G40" s="49" t="n">
         <v>1568</v>
       </c>
-      <c r="G40" s="49" t="n">
-        <v>1569</v>
-      </c>
       <c r="H40" s="49" t="n">
+        <v>1571</v>
+      </c>
+      <c r="I40" s="49" t="n">
         <v>1572</v>
       </c>
-      <c r="I40" s="49" t="n">
-        <v>1573</v>
-      </c>
       <c r="J40" s="49" t="n">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K40" s="49" t="n">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L40" s="49" t="n">
+        <v>1586</v>
+      </c>
+      <c r="M40" s="49" t="n">
         <v>1587</v>
       </c>
-      <c r="M40" s="49" t="n">
-        <v>1588</v>
-      </c>
       <c r="N40" s="49" t="n">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="O40" s="45" t="n"/>
     </row>
@@ -11266,40 +11266,40 @@
         <v>5</v>
       </c>
       <c r="C41" s="49" t="n">
+        <v>1601</v>
+      </c>
+      <c r="D41" s="49" t="n">
         <v>1602</v>
       </c>
-      <c r="D41" s="49" t="n">
-        <v>1603</v>
-      </c>
       <c r="E41" s="49" t="n">
+        <v>1604</v>
+      </c>
+      <c r="F41" s="49" t="n">
         <v>1605</v>
       </c>
-      <c r="F41" s="49" t="n">
+      <c r="G41" s="49" t="n">
         <v>1606</v>
       </c>
-      <c r="G41" s="49" t="n">
-        <v>1607</v>
-      </c>
       <c r="H41" s="49" t="n">
+        <v>1610</v>
+      </c>
+      <c r="I41" s="49" t="n">
         <v>1611</v>
       </c>
-      <c r="I41" s="49" t="n">
-        <v>1612</v>
-      </c>
       <c r="J41" s="49" t="n">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="K41" s="49" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="L41" s="49" t="n">
+        <v>1627</v>
+      </c>
+      <c r="M41" s="49" t="n">
         <v>1628</v>
       </c>
-      <c r="M41" s="49" t="n">
-        <v>1629</v>
-      </c>
       <c r="N41" s="49" t="n">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="O41" s="45" t="n"/>
     </row>
@@ -11311,40 +11311,40 @@
         <v>6</v>
       </c>
       <c r="C42" s="49" t="n">
+        <v>1636</v>
+      </c>
+      <c r="D42" s="49" t="n">
         <v>1637</v>
       </c>
-      <c r="D42" s="49" t="n">
-        <v>1638</v>
-      </c>
       <c r="E42" s="49" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F42" s="49" t="n">
         <v>1640</v>
       </c>
-      <c r="F42" s="49" t="n">
+      <c r="G42" s="49" t="n">
         <v>1641</v>
       </c>
-      <c r="G42" s="49" t="n">
-        <v>1642</v>
-      </c>
       <c r="H42" s="49" t="n">
+        <v>1644</v>
+      </c>
+      <c r="I42" s="49" t="n">
         <v>1645</v>
       </c>
-      <c r="I42" s="49" t="n">
-        <v>1646</v>
-      </c>
       <c r="J42" s="49" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="K42" s="49" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="L42" s="49" t="n">
+        <v>1663</v>
+      </c>
+      <c r="M42" s="49" t="n">
         <v>1664</v>
       </c>
-      <c r="M42" s="49" t="n">
-        <v>1665</v>
-      </c>
       <c r="N42" s="49" t="n">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="O42" s="45" t="n"/>
     </row>
@@ -11356,40 +11356,40 @@
         <v>7</v>
       </c>
       <c r="C43" s="49" t="n">
+        <v>1749</v>
+      </c>
+      <c r="D43" s="49" t="n">
         <v>1750</v>
       </c>
-      <c r="D43" s="49" t="n">
-        <v>1751</v>
-      </c>
       <c r="E43" s="49" t="n">
+        <v>1752</v>
+      </c>
+      <c r="F43" s="49" t="n">
         <v>1753</v>
       </c>
-      <c r="F43" s="49" t="n">
+      <c r="G43" s="49" t="n">
         <v>1754</v>
       </c>
-      <c r="G43" s="49" t="n">
-        <v>1755</v>
-      </c>
       <c r="H43" s="49" t="n">
+        <v>1756</v>
+      </c>
+      <c r="I43" s="49" t="n">
         <v>1757</v>
       </c>
-      <c r="I43" s="49" t="n">
-        <v>1758</v>
-      </c>
       <c r="J43" s="49" t="n">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="K43" s="49" t="n">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="L43" s="49" t="n">
+        <v>1778</v>
+      </c>
+      <c r="M43" s="49" t="n">
         <v>1779</v>
       </c>
-      <c r="M43" s="49" t="n">
-        <v>1780</v>
-      </c>
       <c r="N43" s="49" t="n">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="O43" s="45" t="n"/>
     </row>
@@ -11401,40 +11401,40 @@
         <v>7</v>
       </c>
       <c r="C44" s="62" t="n">
+        <v>1816</v>
+      </c>
+      <c r="D44" s="62" t="n">
         <v>1817</v>
       </c>
-      <c r="D44" s="62" t="n">
-        <v>1818</v>
-      </c>
       <c r="E44" s="62" t="n">
+        <v>1823</v>
+      </c>
+      <c r="F44" s="62" t="n">
         <v>1824</v>
       </c>
-      <c r="F44" s="62" t="n">
+      <c r="G44" s="62" t="n">
         <v>1825</v>
       </c>
-      <c r="G44" s="62" t="n">
-        <v>1826</v>
-      </c>
       <c r="H44" s="62" t="n">
+        <v>1828</v>
+      </c>
+      <c r="I44" s="62" t="n">
         <v>1829</v>
       </c>
-      <c r="I44" s="62" t="n">
-        <v>1830</v>
-      </c>
       <c r="J44" s="62" t="n">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="K44" s="62" t="n">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="L44" s="62" t="n">
+        <v>1852</v>
+      </c>
+      <c r="M44" s="62" t="n">
         <v>1853</v>
       </c>
-      <c r="M44" s="62" t="n">
-        <v>1854</v>
-      </c>
       <c r="N44" s="62" t="n">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="O44" s="63" t="inlineStr">
         <is>
@@ -11450,40 +11450,40 @@
         <v>8</v>
       </c>
       <c r="C45" s="49" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D45" s="49" t="n">
         <v>1907</v>
       </c>
-      <c r="D45" s="49" t="n">
-        <v>1908</v>
-      </c>
       <c r="E45" s="49" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F45" s="49" t="n">
         <v>1911</v>
       </c>
-      <c r="F45" s="49" t="n">
+      <c r="G45" s="49" t="n">
         <v>1912</v>
       </c>
-      <c r="G45" s="49" t="n">
-        <v>1913</v>
-      </c>
       <c r="H45" s="49" t="n">
+        <v>1914</v>
+      </c>
+      <c r="I45" s="49" t="n">
         <v>1915</v>
       </c>
-      <c r="I45" s="49" t="n">
-        <v>1916</v>
-      </c>
       <c r="J45" s="49" t="n">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="K45" s="49" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="L45" s="49" t="n">
+        <v>1936</v>
+      </c>
+      <c r="M45" s="49" t="n">
         <v>1937</v>
       </c>
-      <c r="M45" s="49" t="n">
-        <v>1938</v>
-      </c>
       <c r="N45" s="49" t="n">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="O45" s="45" t="n"/>
     </row>
@@ -11495,40 +11495,40 @@
         <v>8</v>
       </c>
       <c r="C46" s="49" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D46" s="49" t="n">
         <v>1948</v>
       </c>
-      <c r="D46" s="49" t="n">
-        <v>1949</v>
-      </c>
       <c r="E46" s="49" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F46" s="49" t="n">
         <v>1951</v>
       </c>
-      <c r="F46" s="49" t="n">
+      <c r="G46" s="49" t="n">
         <v>1952</v>
       </c>
-      <c r="G46" s="49" t="n">
-        <v>1953</v>
-      </c>
       <c r="H46" s="49" t="n">
+        <v>1954</v>
+      </c>
+      <c r="I46" s="49" t="n">
         <v>1955</v>
       </c>
-      <c r="I46" s="49" t="n">
-        <v>1956</v>
-      </c>
       <c r="J46" s="49" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="K46" s="49" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="L46" s="49" t="n">
+        <v>1975</v>
+      </c>
+      <c r="M46" s="49" t="n">
         <v>1976</v>
       </c>
-      <c r="M46" s="49" t="n">
-        <v>1977</v>
-      </c>
       <c r="N46" s="49" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="O46" s="45" t="n"/>
     </row>
@@ -11540,40 +11540,40 @@
         <v>8</v>
       </c>
       <c r="C47" s="49" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D47" s="49" t="n">
         <v>1986</v>
       </c>
-      <c r="D47" s="49" t="n">
-        <v>1987</v>
-      </c>
       <c r="E47" s="49" t="n">
+        <v>1989</v>
+      </c>
+      <c r="F47" s="49" t="n">
         <v>1990</v>
       </c>
-      <c r="F47" s="49" t="n">
+      <c r="G47" s="49" t="n">
         <v>1991</v>
       </c>
-      <c r="G47" s="49" t="n">
-        <v>1992</v>
-      </c>
       <c r="H47" s="49" t="n">
+        <v>1997</v>
+      </c>
+      <c r="I47" s="49" t="n">
         <v>1998</v>
       </c>
-      <c r="I47" s="49" t="n">
-        <v>1999</v>
-      </c>
       <c r="J47" s="49" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="K47" s="49" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="L47" s="49" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M47" s="49" t="n">
         <v>2021</v>
       </c>
-      <c r="M47" s="49" t="n">
-        <v>2022</v>
-      </c>
       <c r="N47" s="49" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="O47" s="45" t="n"/>
     </row>
@@ -11585,40 +11585,40 @@
         <v>9</v>
       </c>
       <c r="C48" s="49" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D48" s="49" t="n">
         <v>2028</v>
       </c>
-      <c r="D48" s="49" t="n">
-        <v>2029</v>
-      </c>
       <c r="E48" s="49" t="n">
+        <v>2030</v>
+      </c>
+      <c r="F48" s="49" t="n">
         <v>2031</v>
       </c>
-      <c r="F48" s="49" t="n">
+      <c r="G48" s="49" t="n">
         <v>2032</v>
       </c>
-      <c r="G48" s="49" t="n">
-        <v>2033</v>
-      </c>
       <c r="H48" s="49" t="n">
+        <v>2039</v>
+      </c>
+      <c r="I48" s="49" t="n">
         <v>2040</v>
       </c>
-      <c r="I48" s="49" t="n">
-        <v>2041</v>
-      </c>
       <c r="J48" s="49" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="K48" s="49" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="L48" s="49" t="n">
+        <v>2060</v>
+      </c>
+      <c r="M48" s="49" t="n">
         <v>2061</v>
       </c>
-      <c r="M48" s="49" t="n">
-        <v>2062</v>
-      </c>
       <c r="N48" s="49" t="n">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="O48" s="45" t="n"/>
     </row>
@@ -11630,40 +11630,40 @@
         <v>9</v>
       </c>
       <c r="C49" s="49" t="n">
+        <v>2083</v>
+      </c>
+      <c r="D49" s="49" t="n">
         <v>2084</v>
       </c>
-      <c r="D49" s="49" t="n">
-        <v>2085</v>
-      </c>
       <c r="E49" s="49" t="n">
+        <v>2086</v>
+      </c>
+      <c r="F49" s="49" t="n">
         <v>2087</v>
       </c>
-      <c r="F49" s="49" t="n">
+      <c r="G49" s="49" t="n">
         <v>2088</v>
       </c>
-      <c r="G49" s="49" t="n">
+      <c r="H49" s="49" t="n">
         <v>2089</v>
       </c>
-      <c r="H49" s="49" t="n">
+      <c r="I49" s="49" t="n">
         <v>2090</v>
       </c>
-      <c r="I49" s="49" t="n">
-        <v>2091</v>
-      </c>
       <c r="J49" s="49" t="n">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="K49" s="49" t="n">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="L49" s="49" t="n">
+        <v>2111</v>
+      </c>
+      <c r="M49" s="49" t="n">
         <v>2112</v>
       </c>
-      <c r="M49" s="49" t="n">
-        <v>2113</v>
-      </c>
       <c r="N49" s="49" t="n">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="O49" s="45" t="n"/>
     </row>
@@ -11675,40 +11675,40 @@
         <v>9</v>
       </c>
       <c r="C50" s="49" t="n">
+        <v>2137</v>
+      </c>
+      <c r="D50" s="49" t="n">
         <v>2138</v>
       </c>
-      <c r="D50" s="49" t="n">
-        <v>2139</v>
-      </c>
       <c r="E50" s="49" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F50" s="49" t="n">
         <v>2141</v>
       </c>
-      <c r="F50" s="49" t="n">
+      <c r="G50" s="49" t="n">
         <v>2142</v>
       </c>
-      <c r="G50" s="49" t="n">
+      <c r="H50" s="49" t="n">
         <v>2143</v>
       </c>
-      <c r="H50" s="49" t="n">
+      <c r="I50" s="49" t="n">
         <v>2144</v>
       </c>
-      <c r="I50" s="49" t="n">
-        <v>2145</v>
-      </c>
       <c r="J50" s="49" t="n">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="K50" s="49" t="n">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="L50" s="49" t="n">
+        <v>2161</v>
+      </c>
+      <c r="M50" s="49" t="n">
         <v>2162</v>
       </c>
-      <c r="M50" s="49" t="n">
-        <v>2163</v>
-      </c>
       <c r="N50" s="49" t="n">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="O50" s="45" t="n"/>
     </row>
@@ -11720,40 +11720,40 @@
         <v>9</v>
       </c>
       <c r="C51" s="64" t="n">
+        <v>2174</v>
+      </c>
+      <c r="D51" s="64" t="n">
         <v>2175</v>
       </c>
-      <c r="D51" s="64" t="n">
+      <c r="E51" s="64" t="n">
         <v>2176</v>
       </c>
-      <c r="E51" s="64" t="n">
+      <c r="F51" s="64" t="n">
         <v>2177</v>
       </c>
-      <c r="F51" s="64" t="n">
+      <c r="G51" s="64" t="n">
         <v>2178</v>
       </c>
-      <c r="G51" s="64" t="n">
-        <v>2179</v>
-      </c>
       <c r="H51" s="64" t="n">
+        <v>2180</v>
+      </c>
+      <c r="I51" s="64" t="n">
         <v>2181</v>
       </c>
-      <c r="I51" s="64" t="n">
-        <v>2182</v>
-      </c>
       <c r="J51" s="64" t="n">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K51" s="64" t="n">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="L51" s="64" t="n">
+        <v>2201</v>
+      </c>
+      <c r="M51" s="64" t="n">
         <v>2202</v>
       </c>
-      <c r="M51" s="64" t="n">
-        <v>2203</v>
-      </c>
       <c r="N51" s="64" t="n">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="O51" s="65" t="inlineStr">
         <is>
@@ -11769,40 +11769,40 @@
         <v>9</v>
       </c>
       <c r="C52" s="49" t="n">
+        <v>2210</v>
+      </c>
+      <c r="D52" s="49" t="n">
         <v>2211</v>
       </c>
-      <c r="D52" s="49" t="n">
-        <v>2212</v>
-      </c>
       <c r="E52" s="49" t="n">
+        <v>2215</v>
+      </c>
+      <c r="F52" s="49" t="n">
         <v>2216</v>
       </c>
-      <c r="F52" s="49" t="n">
+      <c r="G52" s="49" t="n">
         <v>2217</v>
       </c>
-      <c r="G52" s="49" t="n">
-        <v>2218</v>
-      </c>
       <c r="H52" s="49" t="n">
+        <v>2221</v>
+      </c>
+      <c r="I52" s="49" t="n">
         <v>2222</v>
       </c>
-      <c r="I52" s="49" t="n">
-        <v>2223</v>
-      </c>
       <c r="J52" s="49" t="n">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="K52" s="49" t="n">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="L52" s="49" t="n">
+        <v>2241</v>
+      </c>
+      <c r="M52" s="49" t="n">
         <v>2242</v>
       </c>
-      <c r="M52" s="49" t="n">
-        <v>2243</v>
-      </c>
       <c r="N52" s="49" t="n">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="O52" s="45" t="n"/>
     </row>
@@ -11814,40 +11814,40 @@
         <v>10</v>
       </c>
       <c r="C53" s="49" t="n">
+        <v>2257</v>
+      </c>
+      <c r="D53" s="49" t="n">
         <v>2258</v>
       </c>
-      <c r="D53" s="49" t="n">
-        <v>2259</v>
-      </c>
       <c r="E53" s="49" t="n">
+        <v>2262</v>
+      </c>
+      <c r="F53" s="49" t="n">
         <v>2263</v>
       </c>
-      <c r="F53" s="49" t="n">
+      <c r="G53" s="49" t="n">
         <v>2264</v>
       </c>
-      <c r="G53" s="49" t="n">
-        <v>2265</v>
-      </c>
       <c r="H53" s="49" t="n">
+        <v>2268</v>
+      </c>
+      <c r="I53" s="49" t="n">
         <v>2269</v>
       </c>
-      <c r="I53" s="49" t="n">
-        <v>2270</v>
-      </c>
       <c r="J53" s="49" t="n">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="K53" s="49" t="n">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="L53" s="49" t="n">
+        <v>2283</v>
+      </c>
+      <c r="M53" s="49" t="n">
         <v>2284</v>
       </c>
-      <c r="M53" s="49" t="n">
-        <v>2285</v>
-      </c>
       <c r="N53" s="49" t="n">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="O53" s="45" t="n"/>
     </row>
@@ -11859,40 +11859,40 @@
         <v>10</v>
       </c>
       <c r="C54" s="49" t="n">
+        <v>2315</v>
+      </c>
+      <c r="D54" s="49" t="n">
         <v>2316</v>
       </c>
-      <c r="D54" s="49" t="n">
+      <c r="E54" s="49" t="n">
         <v>2317</v>
       </c>
-      <c r="E54" s="49" t="n">
+      <c r="F54" s="49" t="n">
         <v>2318</v>
       </c>
-      <c r="F54" s="49" t="n">
+      <c r="G54" s="49" t="n">
         <v>2319</v>
       </c>
-      <c r="G54" s="49" t="n">
-        <v>2320</v>
-      </c>
       <c r="H54" s="49" t="n">
+        <v>2322</v>
+      </c>
+      <c r="I54" s="49" t="n">
         <v>2323</v>
       </c>
-      <c r="I54" s="49" t="n">
-        <v>2324</v>
-      </c>
       <c r="J54" s="49" t="n">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="K54" s="49" t="n">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="L54" s="49" t="n">
+        <v>2340</v>
+      </c>
+      <c r="M54" s="49" t="n">
         <v>2341</v>
       </c>
-      <c r="M54" s="49" t="n">
-        <v>2342</v>
-      </c>
       <c r="N54" s="49" t="n">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="O54" s="45" t="n"/>
     </row>
@@ -11904,40 +11904,40 @@
         <v>10</v>
       </c>
       <c r="C55" s="49" t="n">
+        <v>2373</v>
+      </c>
+      <c r="D55" s="49" t="n">
         <v>2374</v>
       </c>
-      <c r="D55" s="49" t="n">
-        <v>2375</v>
-      </c>
       <c r="E55" s="49" t="n">
+        <v>2377</v>
+      </c>
+      <c r="F55" s="49" t="n">
         <v>2378</v>
       </c>
-      <c r="F55" s="49" t="n">
+      <c r="G55" s="49" t="n">
         <v>2379</v>
       </c>
-      <c r="G55" s="49" t="n">
-        <v>2380</v>
-      </c>
       <c r="H55" s="49" t="n">
+        <v>2382</v>
+      </c>
+      <c r="I55" s="49" t="n">
         <v>2383</v>
       </c>
-      <c r="I55" s="49" t="n">
-        <v>2384</v>
-      </c>
       <c r="J55" s="49" t="n">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="K55" s="49" t="n">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="L55" s="49" t="n">
+        <v>2398</v>
+      </c>
+      <c r="M55" s="49" t="n">
         <v>2399</v>
       </c>
-      <c r="M55" s="49" t="n">
-        <v>2400</v>
-      </c>
       <c r="N55" s="49" t="n">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="O55" s="45" t="n"/>
     </row>
@@ -11949,40 +11949,40 @@
         <v>11</v>
       </c>
       <c r="C56" s="49" t="n">
+        <v>2411</v>
+      </c>
+      <c r="D56" s="49" t="n">
         <v>2412</v>
       </c>
-      <c r="D56" s="49" t="n">
-        <v>2413</v>
-      </c>
       <c r="E56" s="49" t="n">
+        <v>2415</v>
+      </c>
+      <c r="F56" s="49" t="n">
         <v>2416</v>
       </c>
-      <c r="F56" s="49" t="n">
+      <c r="G56" s="49" t="n">
         <v>2417</v>
       </c>
-      <c r="G56" s="49" t="n">
-        <v>2418</v>
-      </c>
       <c r="H56" s="49" t="n">
+        <v>2420</v>
+      </c>
+      <c r="I56" s="49" t="n">
         <v>2421</v>
       </c>
-      <c r="I56" s="49" t="n">
-        <v>2422</v>
-      </c>
       <c r="J56" s="49" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="K56" s="49" t="n">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="L56" s="49" t="n">
+        <v>2448</v>
+      </c>
+      <c r="M56" s="49" t="n">
         <v>2449</v>
       </c>
-      <c r="M56" s="49" t="n">
-        <v>2450</v>
-      </c>
       <c r="N56" s="49" t="n">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="O56" s="45" t="n"/>
     </row>
@@ -11994,40 +11994,40 @@
         <v>11</v>
       </c>
       <c r="C57" s="66" t="n">
+        <v>2459</v>
+      </c>
+      <c r="D57" s="66" t="n">
         <v>2460</v>
       </c>
-      <c r="D57" s="66" t="n">
-        <v>2461</v>
-      </c>
       <c r="E57" s="66" t="n">
+        <v>2464</v>
+      </c>
+      <c r="F57" s="66" t="n">
         <v>2465</v>
       </c>
-      <c r="F57" s="66" t="n">
+      <c r="G57" s="66" t="n">
         <v>2466</v>
       </c>
-      <c r="G57" s="66" t="n">
-        <v>2467</v>
-      </c>
       <c r="H57" s="66" t="n">
+        <v>2471</v>
+      </c>
+      <c r="I57" s="66" t="n">
         <v>2472</v>
       </c>
-      <c r="I57" s="66" t="n">
-        <v>2473</v>
-      </c>
       <c r="J57" s="66" t="n">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="K57" s="66" t="n">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="L57" s="66" t="n">
+        <v>2491</v>
+      </c>
+      <c r="M57" s="66" t="n">
         <v>2492</v>
       </c>
-      <c r="M57" s="66" t="n">
-        <v>2493</v>
-      </c>
       <c r="N57" s="66" t="n">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="O57" s="67" t="inlineStr">
         <is>
@@ -12043,40 +12043,40 @@
         <v>11</v>
       </c>
       <c r="C58" s="49" t="n">
+        <v>2527</v>
+      </c>
+      <c r="D58" s="49" t="n">
         <v>2528</v>
       </c>
-      <c r="D58" s="49" t="n">
-        <v>2529</v>
-      </c>
       <c r="E58" s="49" t="n">
+        <v>2531</v>
+      </c>
+      <c r="F58" s="49" t="n">
         <v>2532</v>
       </c>
-      <c r="F58" s="49" t="n">
+      <c r="G58" s="49" t="n">
         <v>2533</v>
       </c>
-      <c r="G58" s="49" t="n">
-        <v>2534</v>
-      </c>
       <c r="H58" s="49" t="n">
+        <v>2535</v>
+      </c>
+      <c r="I58" s="49" t="n">
         <v>2536</v>
       </c>
-      <c r="I58" s="49" t="n">
-        <v>2537</v>
-      </c>
       <c r="J58" s="49" t="n">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="K58" s="49" t="n">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="L58" s="49" t="n">
+        <v>2550</v>
+      </c>
+      <c r="M58" s="49" t="n">
         <v>2551</v>
       </c>
-      <c r="M58" s="49" t="n">
-        <v>2552</v>
-      </c>
       <c r="N58" s="49" t="n">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="O58" s="45" t="n"/>
     </row>
@@ -12088,40 +12088,40 @@
         <v>12</v>
       </c>
       <c r="C59" s="49" t="n">
+        <v>2579</v>
+      </c>
+      <c r="D59" s="49" t="n">
         <v>2580</v>
       </c>
-      <c r="D59" s="49" t="n">
+      <c r="E59" s="49" t="n">
         <v>2581</v>
       </c>
-      <c r="E59" s="49" t="n">
+      <c r="F59" s="49" t="n">
         <v>2582</v>
       </c>
-      <c r="F59" s="49" t="n">
+      <c r="G59" s="49" t="n">
         <v>2583</v>
       </c>
-      <c r="G59" s="49" t="n">
-        <v>2584</v>
-      </c>
       <c r="H59" s="49" t="n">
+        <v>2586</v>
+      </c>
+      <c r="I59" s="49" t="n">
         <v>2587</v>
       </c>
-      <c r="I59" s="49" t="n">
-        <v>2588</v>
-      </c>
       <c r="J59" s="49" t="n">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="K59" s="49" t="n">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="L59" s="49" t="n">
+        <v>2604</v>
+      </c>
+      <c r="M59" s="49" t="n">
         <v>2605</v>
       </c>
-      <c r="M59" s="49" t="n">
-        <v>2606</v>
-      </c>
       <c r="N59" s="49" t="n">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="O59" s="45" t="n"/>
     </row>
@@ -12133,40 +12133,40 @@
         <v>12</v>
       </c>
       <c r="C60" s="68" t="n">
+        <v>2628</v>
+      </c>
+      <c r="D60" s="68" t="n">
         <v>2629</v>
       </c>
-      <c r="D60" s="68" t="n">
-        <v>2630</v>
-      </c>
       <c r="E60" s="68" t="n">
+        <v>2633</v>
+      </c>
+      <c r="F60" s="68" t="n">
         <v>2634</v>
       </c>
-      <c r="F60" s="68" t="n">
+      <c r="G60" s="68" t="n">
         <v>2635</v>
       </c>
-      <c r="G60" s="68" t="n">
-        <v>2636</v>
-      </c>
       <c r="H60" s="68" t="n">
+        <v>2638</v>
+      </c>
+      <c r="I60" s="68" t="n">
         <v>2639</v>
       </c>
-      <c r="I60" s="68" t="n">
-        <v>2640</v>
-      </c>
       <c r="J60" s="68" t="n">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="K60" s="68" t="n">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="L60" s="68" t="n">
+        <v>2662</v>
+      </c>
+      <c r="M60" s="68" t="n">
         <v>2663</v>
       </c>
-      <c r="M60" s="68" t="n">
-        <v>2664</v>
-      </c>
       <c r="N60" s="68" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="O60" s="69" t="inlineStr">
         <is>
@@ -12182,40 +12182,40 @@
         <v>12</v>
       </c>
       <c r="C61" s="49" t="n">
+        <v>2675</v>
+      </c>
+      <c r="D61" s="49" t="n">
         <v>2676</v>
       </c>
-      <c r="D61" s="49" t="n">
-        <v>2677</v>
-      </c>
       <c r="E61" s="49" t="n">
+        <v>2678</v>
+      </c>
+      <c r="F61" s="49" t="n">
         <v>2679</v>
       </c>
-      <c r="F61" s="49" t="n">
+      <c r="G61" s="49" t="n">
         <v>2680</v>
       </c>
-      <c r="G61" s="49" t="n">
+      <c r="H61" s="49" t="n">
         <v>2681</v>
       </c>
-      <c r="H61" s="49" t="n">
+      <c r="I61" s="49" t="n">
         <v>2682</v>
       </c>
-      <c r="I61" s="49" t="n">
-        <v>2683</v>
-      </c>
       <c r="J61" s="49" t="n">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="K61" s="49" t="n">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="L61" s="49" t="n">
+        <v>2698</v>
+      </c>
+      <c r="M61" s="49" t="n">
         <v>2699</v>
       </c>
-      <c r="M61" s="49" t="n">
-        <v>2700</v>
-      </c>
       <c r="N61" s="49" t="n">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="O61" s="45" t="n"/>
     </row>
@@ -12227,40 +12227,40 @@
         <v>12</v>
       </c>
       <c r="C62" s="49" t="n">
+        <v>2719</v>
+      </c>
+      <c r="D62" s="49" t="n">
         <v>2720</v>
       </c>
-      <c r="D62" s="49" t="n">
-        <v>2721</v>
-      </c>
       <c r="E62" s="49" t="n">
+        <v>2724</v>
+      </c>
+      <c r="F62" s="49" t="n">
         <v>2725</v>
       </c>
-      <c r="F62" s="49" t="n">
+      <c r="G62" s="49" t="n">
         <v>2726</v>
       </c>
-      <c r="G62" s="49" t="n">
-        <v>2727</v>
-      </c>
       <c r="H62" s="49" t="n">
+        <v>2729</v>
+      </c>
+      <c r="I62" s="49" t="n">
         <v>2730</v>
       </c>
-      <c r="I62" s="49" t="n">
-        <v>2731</v>
-      </c>
       <c r="J62" s="49" t="n">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="K62" s="49" t="n">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="L62" s="49" t="n">
+        <v>2746</v>
+      </c>
+      <c r="M62" s="49" t="n">
         <v>2747</v>
       </c>
-      <c r="M62" s="49" t="n">
-        <v>2748</v>
-      </c>
       <c r="N62" s="49" t="n">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="O62" s="45" t="n"/>
     </row>
@@ -12272,40 +12272,40 @@
         <v>12</v>
       </c>
       <c r="C63" s="49" t="n">
+        <v>2754</v>
+      </c>
+      <c r="D63" s="49" t="n">
         <v>2755</v>
       </c>
-      <c r="D63" s="49" t="n">
-        <v>2756</v>
-      </c>
       <c r="E63" s="49" t="n">
+        <v>2758</v>
+      </c>
+      <c r="F63" s="49" t="n">
         <v>2759</v>
       </c>
-      <c r="F63" s="49" t="n">
+      <c r="G63" s="49" t="n">
         <v>2760</v>
       </c>
-      <c r="G63" s="49" t="n">
-        <v>2761</v>
-      </c>
       <c r="H63" s="49" t="n">
+        <v>2762</v>
+      </c>
+      <c r="I63" s="49" t="n">
         <v>2763</v>
       </c>
-      <c r="I63" s="49" t="n">
-        <v>2764</v>
-      </c>
       <c r="J63" s="49" t="n">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="K63" s="49" t="n">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="L63" s="49" t="n">
+        <v>2776</v>
+      </c>
+      <c r="M63" s="49" t="n">
         <v>2777</v>
       </c>
-      <c r="M63" s="49" t="n">
-        <v>2778</v>
-      </c>
       <c r="N63" s="49" t="n">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="O63" s="45" t="n"/>
     </row>
@@ -12317,40 +12317,40 @@
         <v>12</v>
       </c>
       <c r="C64" s="49" t="n">
+        <v>2783</v>
+      </c>
+      <c r="D64" s="49" t="n">
         <v>2784</v>
       </c>
-      <c r="D64" s="49" t="n">
-        <v>2785</v>
-      </c>
       <c r="E64" s="49" t="n">
+        <v>2787</v>
+      </c>
+      <c r="F64" s="49" t="n">
         <v>2788</v>
       </c>
-      <c r="F64" s="49" t="n">
+      <c r="G64" s="49" t="n">
         <v>2789</v>
       </c>
-      <c r="G64" s="49" t="n">
-        <v>2790</v>
-      </c>
       <c r="H64" s="49" t="n">
+        <v>2794</v>
+      </c>
+      <c r="I64" s="49" t="n">
         <v>2795</v>
       </c>
-      <c r="I64" s="49" t="n">
-        <v>2796</v>
-      </c>
       <c r="J64" s="49" t="n">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="K64" s="49" t="n">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="L64" s="49" t="n">
+        <v>2810</v>
+      </c>
+      <c r="M64" s="49" t="n">
         <v>2811</v>
       </c>
-      <c r="M64" s="49" t="n">
-        <v>2812</v>
-      </c>
       <c r="N64" s="49" t="n">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="O64" s="45" t="n"/>
     </row>
@@ -12362,40 +12362,40 @@
         <v>12</v>
       </c>
       <c r="C65" s="49" t="n">
+        <v>2816</v>
+      </c>
+      <c r="D65" s="49" t="n">
         <v>2817</v>
       </c>
-      <c r="D65" s="49" t="n">
-        <v>2818</v>
-      </c>
       <c r="E65" s="49" t="n">
+        <v>2820</v>
+      </c>
+      <c r="F65" s="49" t="n">
         <v>2821</v>
       </c>
-      <c r="F65" s="49" t="n">
+      <c r="G65" s="49" t="n">
         <v>2822</v>
       </c>
-      <c r="G65" s="49" t="n">
-        <v>2823</v>
-      </c>
       <c r="H65" s="49" t="n">
+        <v>2825</v>
+      </c>
+      <c r="I65" s="49" t="n">
         <v>2826</v>
       </c>
-      <c r="I65" s="49" t="n">
-        <v>2827</v>
-      </c>
       <c r="J65" s="49" t="n">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="K65" s="49" t="n">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="L65" s="49" t="n">
+        <v>2838</v>
+      </c>
+      <c r="M65" s="49" t="n">
         <v>2839</v>
       </c>
-      <c r="M65" s="49" t="n">
-        <v>2840</v>
-      </c>
       <c r="N65" s="49" t="n">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="O65" s="45" t="n"/>
     </row>
@@ -12407,40 +12407,40 @@
         <v>12</v>
       </c>
       <c r="C66" s="49" t="n">
+        <v>2844</v>
+      </c>
+      <c r="D66" s="49" t="n">
         <v>2845</v>
       </c>
-      <c r="D66" s="49" t="n">
-        <v>2846</v>
-      </c>
       <c r="E66" s="49" t="n">
+        <v>2847</v>
+      </c>
+      <c r="F66" s="49" t="n">
         <v>2848</v>
       </c>
-      <c r="F66" s="49" t="n">
+      <c r="G66" s="49" t="n">
         <v>2849</v>
       </c>
-      <c r="G66" s="49" t="n">
+      <c r="H66" s="49" t="n">
         <v>2850</v>
       </c>
-      <c r="H66" s="49" t="n">
+      <c r="I66" s="49" t="n">
         <v>2851</v>
       </c>
-      <c r="I66" s="49" t="n">
-        <v>2852</v>
-      </c>
       <c r="J66" s="49" t="n">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="K66" s="49" t="n">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="L66" s="49" t="n">
+        <v>2864</v>
+      </c>
+      <c r="M66" s="49" t="n">
         <v>2865</v>
       </c>
-      <c r="M66" s="49" t="n">
-        <v>2866</v>
-      </c>
       <c r="N66" s="49" t="n">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="O66" s="45" t="n"/>
     </row>
@@ -12452,40 +12452,40 @@
         <v>13</v>
       </c>
       <c r="C67" s="49" t="n">
+        <v>2870</v>
+      </c>
+      <c r="D67" s="49" t="n">
         <v>2871</v>
       </c>
-      <c r="D67" s="49" t="n">
-        <v>2872</v>
-      </c>
       <c r="E67" s="49" t="n">
+        <v>2874</v>
+      </c>
+      <c r="F67" s="49" t="n">
         <v>2875</v>
       </c>
-      <c r="F67" s="49" t="n">
+      <c r="G67" s="49" t="n">
         <v>2876</v>
       </c>
-      <c r="G67" s="49" t="n">
-        <v>2877</v>
-      </c>
       <c r="H67" s="49" t="n">
+        <v>2881</v>
+      </c>
+      <c r="I67" s="49" t="n">
         <v>2882</v>
       </c>
-      <c r="I67" s="49" t="n">
-        <v>2883</v>
-      </c>
       <c r="J67" s="49" t="n">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="K67" s="49" t="n">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="L67" s="49" t="n">
+        <v>2903</v>
+      </c>
+      <c r="M67" s="49" t="n">
         <v>2904</v>
       </c>
-      <c r="M67" s="49" t="n">
-        <v>2905</v>
-      </c>
       <c r="N67" s="49" t="n">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="O67" s="45" t="n"/>
     </row>
@@ -12497,40 +12497,40 @@
         <v>13</v>
       </c>
       <c r="C68" s="49" t="n">
+        <v>2912</v>
+      </c>
+      <c r="D68" s="49" t="n">
         <v>2913</v>
       </c>
-      <c r="D68" s="49" t="n">
-        <v>2914</v>
-      </c>
       <c r="E68" s="49" t="n">
+        <v>2915</v>
+      </c>
+      <c r="F68" s="49" t="n">
         <v>2916</v>
       </c>
-      <c r="F68" s="49" t="n">
+      <c r="G68" s="49" t="n">
         <v>2917</v>
       </c>
-      <c r="G68" s="49" t="n">
-        <v>2918</v>
-      </c>
       <c r="H68" s="49" t="n">
+        <v>2921</v>
+      </c>
+      <c r="I68" s="49" t="n">
         <v>2922</v>
       </c>
-      <c r="I68" s="49" t="n">
-        <v>2923</v>
-      </c>
       <c r="J68" s="49" t="n">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="K68" s="49" t="n">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="L68" s="49" t="n">
+        <v>2937</v>
+      </c>
+      <c r="M68" s="49" t="n">
         <v>2938</v>
       </c>
-      <c r="M68" s="49" t="n">
-        <v>2939</v>
-      </c>
       <c r="N68" s="49" t="n">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="O68" s="45" t="n"/>
     </row>
@@ -12542,40 +12542,40 @@
         <v>13</v>
       </c>
       <c r="C69" s="49" t="n">
+        <v>2945</v>
+      </c>
+      <c r="D69" s="49" t="n">
         <v>2946</v>
       </c>
-      <c r="D69" s="49" t="n">
+      <c r="E69" s="49" t="n">
         <v>2947</v>
       </c>
-      <c r="E69" s="49" t="n">
+      <c r="F69" s="49" t="n">
         <v>2948</v>
       </c>
-      <c r="F69" s="49" t="n">
+      <c r="G69" s="49" t="n">
         <v>2949</v>
       </c>
-      <c r="G69" s="49" t="n">
-        <v>2950</v>
-      </c>
       <c r="H69" s="49" t="n">
+        <v>2954</v>
+      </c>
+      <c r="I69" s="49" t="n">
         <v>2955</v>
       </c>
-      <c r="I69" s="49" t="n">
-        <v>2956</v>
-      </c>
       <c r="J69" s="49" t="n">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="K69" s="49" t="n">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="L69" s="49" t="n">
+        <v>2974</v>
+      </c>
+      <c r="M69" s="49" t="n">
         <v>2975</v>
       </c>
-      <c r="M69" s="49" t="n">
-        <v>2976</v>
-      </c>
       <c r="N69" s="49" t="n">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="O69" s="45" t="n"/>
     </row>
@@ -12587,40 +12587,40 @@
         <v>13</v>
       </c>
       <c r="C70" s="49" t="n">
+        <v>2983</v>
+      </c>
+      <c r="D70" s="49" t="n">
         <v>2984</v>
       </c>
-      <c r="D70" s="49" t="n">
-        <v>2985</v>
-      </c>
       <c r="E70" s="49" t="n">
+        <v>2986</v>
+      </c>
+      <c r="F70" s="49" t="n">
         <v>2987</v>
       </c>
-      <c r="F70" s="49" t="n">
+      <c r="G70" s="49" t="n">
         <v>2988</v>
       </c>
-      <c r="G70" s="49" t="n">
+      <c r="H70" s="49" t="n">
         <v>2989</v>
       </c>
-      <c r="H70" s="49" t="n">
+      <c r="I70" s="49" t="n">
         <v>2990</v>
       </c>
-      <c r="I70" s="49" t="n">
-        <v>2991</v>
-      </c>
       <c r="J70" s="49" t="n">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="K70" s="49" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="L70" s="49" t="n">
+        <v>3007</v>
+      </c>
+      <c r="M70" s="49" t="n">
         <v>3008</v>
       </c>
-      <c r="M70" s="49" t="n">
-        <v>3009</v>
-      </c>
       <c r="N70" s="49" t="n">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="O70" s="45" t="n"/>
     </row>
@@ -12632,40 +12632,40 @@
         <v>13</v>
       </c>
       <c r="C71" s="49" t="n">
+        <v>3016</v>
+      </c>
+      <c r="D71" s="49" t="n">
         <v>3017</v>
       </c>
-      <c r="D71" s="49" t="n">
-        <v>3018</v>
-      </c>
       <c r="E71" s="49" t="n">
+        <v>3020</v>
+      </c>
+      <c r="F71" s="49" t="n">
         <v>3021</v>
       </c>
-      <c r="F71" s="49" t="n">
+      <c r="G71" s="49" t="n">
         <v>3022</v>
       </c>
-      <c r="G71" s="49" t="n">
-        <v>3023</v>
-      </c>
       <c r="H71" s="49" t="n">
+        <v>3025</v>
+      </c>
+      <c r="I71" s="49" t="n">
         <v>3026</v>
       </c>
-      <c r="I71" s="49" t="n">
-        <v>3027</v>
-      </c>
       <c r="J71" s="49" t="n">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="K71" s="49" t="n">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="L71" s="49" t="n">
+        <v>3037</v>
+      </c>
+      <c r="M71" s="49" t="n">
         <v>3038</v>
       </c>
-      <c r="M71" s="49" t="n">
-        <v>3039</v>
-      </c>
       <c r="N71" s="49" t="n">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="O71" s="45" t="n"/>
     </row>
@@ -12682,7 +12682,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9.140625" customWidth="1" style="55" min="5" max="5"/>
   </cols>
@@ -15139,7 +15139,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -17019,8 +17019,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.85546875" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -17895,7 +17895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="55">
@@ -18766,7 +18766,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -18825,19 +18825,19 @@
         <v>2</v>
       </c>
       <c r="D2" s="49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" s="49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" s="49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G2" s="49" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H2" s="49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -18848,22 +18848,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D3" s="49" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E3" s="49" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F3" s="49" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G3" s="49" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H3" s="49" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -18874,22 +18874,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="49" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D4" s="49" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E4" s="49" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F4" s="49" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G4" s="49" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H4" s="49" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -18900,22 +18900,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E5" s="49" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F5" s="49" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="G5" s="49" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="H5" s="49" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -18926,22 +18926,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E6" s="49" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="F6" s="49" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="G6" s="49" t="n">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="H6" s="49" t="n">
-        <v>74</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -18952,22 +18952,22 @@
         <v>2</v>
       </c>
       <c r="C7" s="49" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="E7" s="49" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="F7" s="49" t="n">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="G7" s="49" t="n">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="H7" s="49" t="n">
-        <v>87</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -18978,22 +18978,22 @@
         <v>2</v>
       </c>
       <c r="C8" s="49" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="E8" s="49" t="n">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="F8" s="49" t="n">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="G8" s="49" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="H8" s="49" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
@@ -19004,22 +19004,22 @@
         <v>2</v>
       </c>
       <c r="C9" s="49" t="n">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="E9" s="49" t="n">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="F9" s="49" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="G9" s="49" t="n">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="H9" s="49" t="n">
-        <v>124</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -19030,22 +19030,22 @@
         <v>3</v>
       </c>
       <c r="C10" s="49" t="n">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>131</v>
+        <v>215</v>
       </c>
       <c r="E10" s="49" t="n">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="F10" s="49" t="n">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="G10" s="49" t="n">
-        <v>143</v>
+        <v>236</v>
       </c>
       <c r="H10" s="49" t="n">
-        <v>143</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -19056,22 +19056,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="49" t="n">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="D11" s="49" t="n">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="E11" s="49" t="n">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="F11" s="49" t="n">
-        <v>159</v>
+        <v>263</v>
       </c>
       <c r="G11" s="49" t="n">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="H11" s="49" t="n">
-        <v>160</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -19082,22 +19082,22 @@
         <v>3</v>
       </c>
       <c r="C12" s="49" t="n">
-        <v>162</v>
+        <v>266</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>168</v>
+        <v>277</v>
       </c>
       <c r="E12" s="49" t="n">
-        <v>172</v>
+        <v>285</v>
       </c>
       <c r="F12" s="49" t="n">
-        <v>178</v>
+        <v>296</v>
       </c>
       <c r="G12" s="49" t="n">
-        <v>179</v>
+        <v>297</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>179</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13">
@@ -19108,22 +19108,22 @@
         <v>3</v>
       </c>
       <c r="C13" s="49" t="n">
-        <v>181</v>
+        <v>299</v>
       </c>
       <c r="D13" s="49" t="n">
-        <v>188</v>
+        <v>312</v>
       </c>
       <c r="E13" s="49" t="n">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="F13" s="49" t="n">
-        <v>196</v>
+        <v>327</v>
       </c>
       <c r="G13" s="49" t="n">
-        <v>197</v>
+        <v>328</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>197</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14">
@@ -19134,22 +19134,22 @@
         <v>4</v>
       </c>
       <c r="C14" s="49" t="n">
-        <v>199</v>
+        <v>330</v>
       </c>
       <c r="D14" s="49" t="n">
-        <v>205</v>
+        <v>341</v>
       </c>
       <c r="E14" s="49" t="n">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="F14" s="49" t="n">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="G14" s="49" t="n">
-        <v>219</v>
+        <v>366</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>227</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15">
@@ -19160,22 +19160,22 @@
         <v>4</v>
       </c>
       <c r="C15" s="49" t="n">
-        <v>229</v>
+        <v>384</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>240</v>
+        <v>405</v>
       </c>
       <c r="E15" s="49" t="n">
-        <v>245</v>
+        <v>413</v>
       </c>
       <c r="F15" s="49" t="n">
-        <v>248</v>
+        <v>418</v>
       </c>
       <c r="G15" s="49" t="n">
-        <v>249</v>
+        <v>419</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>253</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16">
@@ -19186,22 +19186,22 @@
         <v>4</v>
       </c>
       <c r="C16" s="49" t="n">
-        <v>255</v>
+        <v>429</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="E16" s="49" t="n">
-        <v>268</v>
+        <v>453</v>
       </c>
       <c r="F16" s="49" t="n">
-        <v>275</v>
+        <v>467</v>
       </c>
       <c r="G16" s="49" t="n">
-        <v>276</v>
+        <v>468</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>280</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17">
@@ -19212,22 +19212,22 @@
         <v>4</v>
       </c>
       <c r="C17" s="49" t="n">
-        <v>282</v>
+        <v>478</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>293</v>
+        <v>499</v>
       </c>
       <c r="E17" s="49" t="n">
-        <v>298</v>
+        <v>507</v>
       </c>
       <c r="F17" s="49" t="n">
-        <v>304</v>
+        <v>518</v>
       </c>
       <c r="G17" s="49" t="n">
-        <v>305</v>
+        <v>519</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>311</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18">
@@ -19238,22 +19238,22 @@
         <v>5</v>
       </c>
       <c r="C18" s="49" t="n">
-        <v>313</v>
+        <v>533</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>320</v>
+        <v>546</v>
       </c>
       <c r="E18" s="49" t="n">
-        <v>325</v>
+        <v>553</v>
       </c>
       <c r="F18" s="49" t="n">
-        <v>329</v>
+        <v>560</v>
       </c>
       <c r="G18" s="49" t="n">
-        <v>330</v>
+        <v>561</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>330</v>
+        <v>561</v>
       </c>
     </row>
     <row r="19">
@@ -19264,22 +19264,22 @@
         <v>5</v>
       </c>
       <c r="C19" s="49" t="n">
-        <v>332</v>
+        <v>563</v>
       </c>
       <c r="D19" s="49" t="n">
-        <v>335</v>
+        <v>568</v>
       </c>
       <c r="E19" s="49" t="n">
-        <v>338</v>
+        <v>572</v>
       </c>
       <c r="F19" s="49" t="n">
-        <v>342</v>
+        <v>579</v>
       </c>
       <c r="G19" s="49" t="n">
-        <v>343</v>
+        <v>580</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>347</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20">
@@ -19290,22 +19290,22 @@
         <v>5</v>
       </c>
       <c r="C20" s="49" t="n">
-        <v>349</v>
+        <v>590</v>
       </c>
       <c r="D20" s="49" t="n">
-        <v>356</v>
+        <v>603</v>
       </c>
       <c r="E20" s="49" t="n">
-        <v>361</v>
+        <v>609</v>
       </c>
       <c r="F20" s="49" t="n">
-        <v>365</v>
+        <v>616</v>
       </c>
       <c r="G20" s="49" t="n">
-        <v>366</v>
+        <v>617</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>371</v>
+        <v>627</v>
       </c>
     </row>
     <row r="21">
@@ -19316,22 +19316,22 @@
         <v>5</v>
       </c>
       <c r="C21" s="49" t="n">
-        <v>373</v>
+        <v>629</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>383</v>
+        <v>648</v>
       </c>
       <c r="E21" s="49" t="n">
-        <v>389</v>
+        <v>657</v>
       </c>
       <c r="F21" s="49" t="n">
-        <v>396</v>
+        <v>670</v>
       </c>
       <c r="G21" s="49" t="n">
-        <v>397</v>
+        <v>671</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>411</v>
+        <v>696</v>
       </c>
     </row>
     <row r="22">
@@ -19342,22 +19342,22 @@
         <v>6</v>
       </c>
       <c r="C22" s="49" t="n">
-        <v>413</v>
+        <v>698</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>419</v>
+        <v>708</v>
       </c>
       <c r="E22" s="49" t="n">
-        <v>422</v>
+        <v>713</v>
       </c>
       <c r="F22" s="49" t="n">
-        <v>425</v>
+        <v>718</v>
       </c>
       <c r="G22" s="49" t="n">
-        <v>426</v>
+        <v>719</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>429</v>
+        <v>725</v>
       </c>
     </row>
     <row r="23">
@@ -19368,22 +19368,22 @@
         <v>6</v>
       </c>
       <c r="C23" s="49" t="n">
-        <v>431</v>
+        <v>727</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>438</v>
+        <v>740</v>
       </c>
       <c r="E23" s="49" t="n">
-        <v>444</v>
+        <v>750</v>
       </c>
       <c r="F23" s="49" t="n">
-        <v>449</v>
+        <v>758</v>
       </c>
       <c r="G23" s="49" t="n">
-        <v>450</v>
+        <v>759</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>454</v>
+        <v>767</v>
       </c>
     </row>
     <row r="24">
@@ -19394,22 +19394,22 @@
         <v>6</v>
       </c>
       <c r="C24" s="49" t="n">
-        <v>456</v>
+        <v>769</v>
       </c>
       <c r="D24" s="49" t="n">
-        <v>464</v>
+        <v>784</v>
       </c>
       <c r="E24" s="49" t="n">
-        <v>469</v>
+        <v>793</v>
       </c>
       <c r="F24" s="49" t="n">
-        <v>474</v>
+        <v>802</v>
       </c>
       <c r="G24" s="49" t="n">
-        <v>475</v>
+        <v>803</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>482</v>
+        <v>817</v>
       </c>
     </row>
     <row r="25">
@@ -19420,22 +19420,22 @@
         <v>6</v>
       </c>
       <c r="C25" s="49" t="n">
-        <v>484</v>
+        <v>819</v>
       </c>
       <c r="D25" s="49" t="n">
-        <v>489</v>
+        <v>828</v>
       </c>
       <c r="E25" s="49" t="n">
-        <v>492</v>
+        <v>833</v>
       </c>
       <c r="F25" s="49" t="n">
-        <v>496</v>
+        <v>840</v>
       </c>
       <c r="G25" s="49" t="n">
-        <v>497</v>
+        <v>841</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>499</v>
+        <v>846</v>
       </c>
     </row>
     <row r="26">
@@ -19446,22 +19446,22 @@
         <v>9</v>
       </c>
       <c r="C26" s="49" t="n">
-        <v>501</v>
+        <v>848</v>
       </c>
       <c r="D26" s="49" t="n">
-        <v>506</v>
+        <v>856</v>
       </c>
       <c r="E26" s="49" t="n">
-        <v>511</v>
+        <v>863</v>
       </c>
       <c r="F26" s="49" t="n">
-        <v>515</v>
+        <v>870</v>
       </c>
       <c r="G26" s="49" t="n">
-        <v>516</v>
+        <v>871</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>521</v>
+        <v>879</v>
       </c>
     </row>
     <row r="27">
@@ -19472,22 +19472,22 @@
         <v>9</v>
       </c>
       <c r="C27" s="49" t="n">
-        <v>523</v>
+        <v>881</v>
       </c>
       <c r="D27" s="49" t="n">
-        <v>530</v>
+        <v>894</v>
       </c>
       <c r="E27" s="49" t="n">
-        <v>533</v>
+        <v>899</v>
       </c>
       <c r="F27" s="49" t="n">
-        <v>540</v>
+        <v>911</v>
       </c>
       <c r="G27" s="49" t="n">
-        <v>541</v>
+        <v>912</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>545</v>
+        <v>920</v>
       </c>
     </row>
     <row r="28">
@@ -19498,22 +19498,22 @@
         <v>10</v>
       </c>
       <c r="C28" s="49" t="n">
-        <v>547</v>
+        <v>922</v>
       </c>
       <c r="D28" s="49" t="n">
-        <v>552</v>
+        <v>932</v>
       </c>
       <c r="E28" s="49" t="n">
-        <v>555</v>
+        <v>938</v>
       </c>
       <c r="F28" s="49" t="n">
-        <v>559</v>
+        <v>946</v>
       </c>
       <c r="G28" s="49" t="n">
-        <v>560</v>
+        <v>947</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>563</v>
+        <v>953</v>
       </c>
     </row>
     <row r="29">
@@ -19524,22 +19524,22 @@
         <v>10</v>
       </c>
       <c r="C29" s="49" t="n">
-        <v>565</v>
+        <v>955</v>
       </c>
       <c r="D29" s="49" t="n">
-        <v>568</v>
+        <v>961</v>
       </c>
       <c r="E29" s="49" t="n">
-        <v>570</v>
+        <v>965</v>
       </c>
       <c r="F29" s="49" t="n">
-        <v>574</v>
+        <v>973</v>
       </c>
       <c r="G29" s="49" t="n">
-        <v>575</v>
+        <v>974</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>577</v>
+        <v>979</v>
       </c>
     </row>
     <row r="30">
@@ -19550,22 +19550,22 @@
         <v>10</v>
       </c>
       <c r="C30" s="49" t="n">
-        <v>579</v>
+        <v>981</v>
       </c>
       <c r="D30" s="49" t="n">
-        <v>583</v>
+        <v>989</v>
       </c>
       <c r="E30" s="49" t="n">
-        <v>587</v>
+        <v>997</v>
       </c>
       <c r="F30" s="49" t="n">
-        <v>591</v>
+        <v>1005</v>
       </c>
       <c r="G30" s="49" t="n">
-        <v>592</v>
+        <v>1006</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>595</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="31">
@@ -19576,22 +19576,22 @@
         <v>10</v>
       </c>
       <c r="C31" s="49" t="n">
-        <v>597</v>
+        <v>1015</v>
       </c>
       <c r="D31" s="49" t="n">
-        <v>601</v>
+        <v>1023</v>
       </c>
       <c r="E31" s="49" t="n">
-        <v>604</v>
+        <v>1029</v>
       </c>
       <c r="F31" s="49" t="n">
-        <v>607</v>
+        <v>1035</v>
       </c>
       <c r="G31" s="49" t="n">
-        <v>608</v>
+        <v>1036</v>
       </c>
       <c r="H31" s="49" t="n">
-        <v>610</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="32">
@@ -19602,22 +19602,22 @@
         <v>11</v>
       </c>
       <c r="C32" s="49" t="n">
-        <v>612</v>
+        <v>1043</v>
       </c>
       <c r="D32" s="49" t="n">
-        <v>625</v>
+        <v>1068</v>
       </c>
       <c r="E32" s="49" t="n">
-        <v>632</v>
+        <v>1081</v>
       </c>
       <c r="F32" s="49" t="n">
-        <v>637</v>
+        <v>1090</v>
       </c>
       <c r="G32" s="49" t="n">
-        <v>638</v>
+        <v>1091</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>646</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="33">
@@ -19628,22 +19628,22 @@
         <v>11</v>
       </c>
       <c r="C33" s="49" t="n">
-        <v>648</v>
+        <v>1109</v>
       </c>
       <c r="D33" s="49" t="n">
-        <v>656</v>
+        <v>1124</v>
       </c>
       <c r="E33" s="49" t="n">
-        <v>661</v>
+        <v>1133</v>
       </c>
       <c r="F33" s="49" t="n">
-        <v>664</v>
+        <v>1138</v>
       </c>
       <c r="G33" s="49" t="n">
-        <v>665</v>
+        <v>1139</v>
       </c>
       <c r="H33" s="49" t="n">
-        <v>668</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="34">
@@ -19654,22 +19654,22 @@
         <v>11</v>
       </c>
       <c r="C34" s="49" t="n">
-        <v>670</v>
+        <v>1147</v>
       </c>
       <c r="D34" s="49" t="n">
-        <v>676</v>
+        <v>1157</v>
       </c>
       <c r="E34" s="49" t="n">
-        <v>681</v>
+        <v>1166</v>
       </c>
       <c r="F34" s="49" t="n">
-        <v>686</v>
+        <v>1175</v>
       </c>
       <c r="G34" s="49" t="n">
-        <v>687</v>
+        <v>1176</v>
       </c>
       <c r="H34" s="49" t="n">
-        <v>690</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="35">
@@ -19680,22 +19680,22 @@
         <v>11</v>
       </c>
       <c r="C35" s="49" t="n">
-        <v>692</v>
+        <v>1184</v>
       </c>
       <c r="D35" s="49" t="n">
-        <v>698</v>
+        <v>1195</v>
       </c>
       <c r="E35" s="49" t="n">
-        <v>703</v>
+        <v>1204</v>
       </c>
       <c r="F35" s="49" t="n">
-        <v>709</v>
+        <v>1215</v>
       </c>
       <c r="G35" s="49" t="n">
-        <v>710</v>
+        <v>1216</v>
       </c>
       <c r="H35" s="49" t="n">
-        <v>724</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="36">
@@ -19706,22 +19706,22 @@
         <v>12</v>
       </c>
       <c r="C36" s="49" t="n">
-        <v>726</v>
+        <v>1243</v>
       </c>
       <c r="D36" s="49" t="n">
-        <v>734</v>
+        <v>1259</v>
       </c>
       <c r="E36" s="49" t="n">
-        <v>736</v>
+        <v>1263</v>
       </c>
       <c r="F36" s="49" t="n">
-        <v>742</v>
+        <v>1275</v>
       </c>
       <c r="G36" s="49" t="n">
-        <v>743</v>
+        <v>1276</v>
       </c>
       <c r="H36" s="49" t="n">
-        <v>745</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="37">
@@ -19732,22 +19732,22 @@
         <v>12</v>
       </c>
       <c r="C37" s="49" t="n">
-        <v>747</v>
+        <v>1283</v>
       </c>
       <c r="D37" s="49" t="n">
-        <v>755</v>
+        <v>1298</v>
       </c>
       <c r="E37" s="49" t="n">
-        <v>760</v>
+        <v>1307</v>
       </c>
       <c r="F37" s="49" t="n">
-        <v>765</v>
+        <v>1316</v>
       </c>
       <c r="G37" s="49" t="n">
-        <v>766</v>
+        <v>1317</v>
       </c>
       <c r="H37" s="49" t="n">
-        <v>770</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="38">
@@ -19758,22 +19758,22 @@
         <v>12</v>
       </c>
       <c r="C38" s="49" t="n">
-        <v>772</v>
+        <v>1327</v>
       </c>
       <c r="D38" s="49" t="n">
-        <v>774</v>
+        <v>1330</v>
       </c>
       <c r="E38" s="49" t="n">
-        <v>780</v>
+        <v>1342</v>
       </c>
       <c r="F38" s="49" t="n">
-        <v>783</v>
+        <v>1348</v>
       </c>
       <c r="G38" s="49" t="n">
-        <v>784</v>
+        <v>1349</v>
       </c>
       <c r="H38" s="49" t="n">
-        <v>788</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="39">
@@ -19784,22 +19784,22 @@
         <v>12</v>
       </c>
       <c r="C39" s="49" t="n">
-        <v>790</v>
+        <v>1359</v>
       </c>
       <c r="D39" s="49" t="n">
-        <v>799</v>
+        <v>1376</v>
       </c>
       <c r="E39" s="49" t="n">
-        <v>805</v>
+        <v>1387</v>
       </c>
       <c r="F39" s="49" t="n">
-        <v>810</v>
+        <v>1396</v>
       </c>
       <c r="G39" s="49" t="n">
-        <v>811</v>
+        <v>1397</v>
       </c>
       <c r="H39" s="49" t="n">
-        <v>822</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="40">
@@ -19810,22 +19810,22 @@
         <v>13</v>
       </c>
       <c r="C40" s="49" t="n">
-        <v>824</v>
+        <v>1422</v>
       </c>
       <c r="D40" s="49" t="n">
-        <v>828</v>
+        <v>1430</v>
       </c>
       <c r="E40" s="49" t="n">
-        <v>834</v>
+        <v>1442</v>
       </c>
       <c r="F40" s="49" t="n">
-        <v>836</v>
+        <v>1446</v>
       </c>
       <c r="G40" s="49" t="n">
-        <v>837</v>
+        <v>1447</v>
       </c>
       <c r="H40" s="49" t="n">
-        <v>844</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="41">
@@ -19836,22 +19836,22 @@
         <v>1</v>
       </c>
       <c r="C41" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D41" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E41" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F41" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G41" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H41" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="42">
@@ -19862,22 +19862,22 @@
         <v>2</v>
       </c>
       <c r="C42" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D42" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E42" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F42" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G42" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H42" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="43">
@@ -19888,22 +19888,22 @@
         <v>3</v>
       </c>
       <c r="C43" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D43" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E43" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F43" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G43" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H43" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="44">
@@ -19914,22 +19914,22 @@
         <v>4</v>
       </c>
       <c r="C44" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D44" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E44" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F44" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G44" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H44" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="45">
@@ -19940,22 +19940,22 @@
         <v>5</v>
       </c>
       <c r="C45" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D45" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E45" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F45" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G45" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H45" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="46">
@@ -19966,22 +19966,22 @@
         <v>6</v>
       </c>
       <c r="C46" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D46" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E46" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F46" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G46" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H46" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="47">
@@ -19992,22 +19992,22 @@
         <v>9</v>
       </c>
       <c r="C47" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E47" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F47" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G47" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H47" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="48">
@@ -20018,22 +20018,22 @@
         <v>10</v>
       </c>
       <c r="C48" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D48" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E48" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F48" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G48" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H48" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="49">
@@ -20044,22 +20044,22 @@
         <v>11</v>
       </c>
       <c r="C49" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D49" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E49" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F49" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G49" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H49" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="50">
@@ -20070,22 +20070,22 @@
         <v>12</v>
       </c>
       <c r="C50" s="49" t="n">
-        <v>846</v>
+        <v>1464</v>
       </c>
       <c r="D50" s="49" t="n">
-        <v>849</v>
+        <v>1468</v>
       </c>
       <c r="E50" s="49" t="n">
-        <v>851</v>
+        <v>1471</v>
       </c>
       <c r="F50" s="49" t="n">
-        <v>854</v>
+        <v>1475</v>
       </c>
       <c r="G50" s="49" t="n">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="H50" s="49" t="n">
-        <v>856</v>
+        <v>1478</v>
       </c>
     </row>
   </sheetData>
@@ -20100,7 +20100,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -20249,8 +20249,8 @@
       <c r="B3" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
+      <c r="C3" s="49" t="inlineStr"/>
+      <c r="D3" s="49" t="inlineStr"/>
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="49" t="n">
         <v>45</v>
@@ -20290,8 +20290,8 @@
       <c r="B4" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
+      <c r="C4" s="49" t="inlineStr"/>
+      <c r="D4" s="49" t="inlineStr"/>
       <c r="E4" s="49" t="n"/>
       <c r="F4" s="49" t="n">
         <v>71</v>
@@ -20331,10 +20331,10 @@
       <c r="B5" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
+      <c r="C5" s="49" t="inlineStr"/>
+      <c r="D5" s="49" t="inlineStr"/>
       <c r="E5" s="49" t="n"/>
-      <c r="F5" s="49" t="n"/>
+      <c r="F5" s="49" t="inlineStr"/>
       <c r="G5" s="49" t="n">
         <v>107</v>
       </c>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="868" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="868" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المناسبات" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -136,6 +136,14 @@
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="21">
@@ -529,7 +537,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -732,6 +740,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1368,7 +1382,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17.85546875" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="17.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="4.42578125" bestFit="1" customWidth="1" style="70" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="70" min="2" max="2"/>
@@ -1383,8 +1397,8 @@
     <col width="11.140625" customWidth="1" style="70" min="11" max="11"/>
     <col width="17.85546875" customWidth="1" style="70" min="12" max="12"/>
     <col width="28" customWidth="1" style="70" min="13" max="13"/>
-    <col width="17.85546875" customWidth="1" style="70" min="14" max="97"/>
-    <col width="17.85546875" customWidth="1" style="70" min="98" max="16384"/>
+    <col width="17.85546875" customWidth="1" style="70" min="14" max="105"/>
+    <col width="17.85546875" customWidth="1" style="70" min="106" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" s="55">
@@ -1418,23 +1432,23 @@
           <t>المناسبة</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="I1" s="83" t="inlineStr">
         <is>
           <t>دور القمر</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="J1" s="83" t="inlineStr">
         <is>
           <t>الفصح</t>
         </is>
       </c>
-      <c r="K1" s="80" t="n"/>
-      <c r="M1" s="91" t="inlineStr">
+      <c r="K1" s="82" t="n"/>
+      <c r="M1" s="93" t="inlineStr">
         <is>
           <t>السنة القبطية الحالية</t>
         </is>
       </c>
-      <c r="N1" s="80" t="n"/>
+      <c r="N1" s="82" t="n"/>
       <c r="R1" s="1" t="n"/>
     </row>
     <row r="2" ht="23.25" customHeight="1" s="55">
@@ -1461,21 +1475,21 @@
           <t>النيروز</t>
         </is>
       </c>
-      <c r="I2" s="82" t="n"/>
-      <c r="J2" s="81" t="inlineStr">
+      <c r="I2" s="84" t="n"/>
+      <c r="J2" s="83" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="K2" s="81" t="inlineStr">
+      <c r="K2" s="83" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
       </c>
-      <c r="M2" s="79" t="n">
-        <v>1741</v>
-      </c>
-      <c r="N2" s="80" t="n"/>
+      <c r="M2" s="81" t="n">
+        <v>1742</v>
+      </c>
+      <c r="N2" s="82" t="n"/>
       <c r="R2" s="2" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1" s="55">
@@ -1587,12 +1601,12 @@
       <c r="K5" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="85" t="inlineStr">
+      <c r="M5" s="87" t="inlineStr">
         <is>
           <t>لضمان عمل البرنامج بشكل صحيح لا تُغيّر أي شئ يدويًا في الملف</t>
         </is>
       </c>
-      <c r="N5" s="86" t="n"/>
+      <c r="N5" s="88" t="n"/>
       <c r="R5" s="5" t="n"/>
       <c r="T5" s="6" t="n"/>
     </row>
@@ -1629,8 +1643,8 @@
       <c r="K6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="87" t="n"/>
-      <c r="N6" s="88" t="n"/>
+      <c r="M6" s="89" t="n"/>
+      <c r="N6" s="90" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="T6" s="6" t="n"/>
     </row>
@@ -1651,7 +1665,7 @@
         <v/>
       </c>
       <c r="F7" s="37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="38" t="inlineStr">
         <is>
@@ -1667,8 +1681,8 @@
       <c r="K7" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="87" t="n"/>
-      <c r="N7" s="88" t="n"/>
+      <c r="M7" s="89" t="n"/>
+      <c r="N7" s="90" t="n"/>
       <c r="R7" s="5" t="n"/>
       <c r="T7" s="6" t="n"/>
     </row>
@@ -1705,8 +1719,8 @@
       <c r="K8" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="87" t="n"/>
-      <c r="N8" s="88" t="n"/>
+      <c r="M8" s="89" t="n"/>
+      <c r="N8" s="90" t="n"/>
       <c r="R8" s="5" t="n"/>
       <c r="T8" s="6" t="n"/>
     </row>
@@ -1743,8 +1757,8 @@
       <c r="K9" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M9" s="87" t="n"/>
-      <c r="N9" s="88" t="n"/>
+      <c r="M9" s="89" t="n"/>
+      <c r="N9" s="90" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="T9" s="6" t="n"/>
     </row>
@@ -1781,8 +1795,8 @@
       <c r="K10" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M10" s="87" t="n"/>
-      <c r="N10" s="88" t="n"/>
+      <c r="M10" s="89" t="n"/>
+      <c r="N10" s="90" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="T10" s="6" t="n"/>
     </row>
@@ -1796,14 +1810,14 @@
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="36">
         <f>VLOOKUP(D11, $A$2:$B$100, 2, FALSE)</f>
         <v/>
       </c>
       <c r="F11" s="37" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G11" s="38" t="inlineStr">
         <is>
@@ -1819,8 +1833,8 @@
       <c r="K11" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M11" s="87" t="n"/>
-      <c r="N11" s="88" t="n"/>
+      <c r="M11" s="89" t="n"/>
+      <c r="N11" s="90" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="T11" s="6" t="n"/>
     </row>
@@ -1834,14 +1848,14 @@
         </is>
       </c>
       <c r="D12" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="36">
         <f>VLOOKUP(D12, $A$2:$B$100, 2, FALSE)</f>
         <v/>
       </c>
       <c r="F12" s="37" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G12" s="38" t="inlineStr">
         <is>
@@ -1857,8 +1871,8 @@
       <c r="K12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M12" s="87" t="n"/>
-      <c r="N12" s="88" t="n"/>
+      <c r="M12" s="89" t="n"/>
+      <c r="N12" s="90" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="T12" s="6" t="n"/>
     </row>
@@ -1879,7 +1893,7 @@
         <v/>
       </c>
       <c r="F13" s="37" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G13" s="38" t="inlineStr">
         <is>
@@ -1895,8 +1909,8 @@
       <c r="K13" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="87" t="n"/>
-      <c r="N13" s="88" t="n"/>
+      <c r="M13" s="89" t="n"/>
+      <c r="N13" s="90" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="T13" s="6" t="n"/>
     </row>
@@ -1933,8 +1947,8 @@
       <c r="K14" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M14" s="87" t="n"/>
-      <c r="N14" s="88" t="n"/>
+      <c r="M14" s="89" t="n"/>
+      <c r="N14" s="90" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="T14" s="6" t="n"/>
     </row>
@@ -1963,21 +1977,21 @@
       <c r="K15" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M15" s="87" t="n"/>
-      <c r="N15" s="88" t="n"/>
+      <c r="M15" s="89" t="n"/>
+      <c r="N15" s="90" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="T15" s="6" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" s="55">
       <c r="D16" s="35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="36">
         <f>VLOOKUP(D16, $A$2:$B$100, 2, FALSE)</f>
         <v/>
       </c>
       <c r="F16" s="37" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G16" s="38" t="inlineStr">
         <is>
@@ -1993,21 +2007,21 @@
       <c r="K16" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M16" s="87" t="n"/>
-      <c r="N16" s="88" t="n"/>
+      <c r="M16" s="89" t="n"/>
+      <c r="N16" s="90" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="T16" s="6" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" s="55" thickBot="1">
       <c r="D17" s="35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="36">
         <f>VLOOKUP(D17, $A$2:$B$100, 2, FALSE)</f>
         <v/>
       </c>
       <c r="F17" s="37" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G17" s="38" t="inlineStr">
         <is>
@@ -2023,21 +2037,21 @@
       <c r="K17" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M17" s="89" t="n"/>
-      <c r="N17" s="90" t="n"/>
+      <c r="M17" s="91" t="n"/>
+      <c r="N17" s="92" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="T17" s="6" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" s="55" thickTop="1">
       <c r="D18" s="35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="36">
         <f>VLOOKUP(D18, $A$2:$B$100, 2, FALSE)</f>
         <v/>
       </c>
       <c r="F18" s="37" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G18" s="38" t="inlineStr">
         <is>
@@ -2066,7 +2080,7 @@
         <v/>
       </c>
       <c r="F19" s="37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G19" s="38" t="inlineStr">
         <is>
@@ -2095,7 +2109,7 @@
         <v/>
       </c>
       <c r="F20" s="37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G20" s="38" t="inlineStr">
         <is>
@@ -2124,7 +2138,7 @@
         <v/>
       </c>
       <c r="F21" s="37" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G21" s="38" t="inlineStr">
         <is>
@@ -2153,7 +2167,7 @@
         <v/>
       </c>
       <c r="F22" s="37" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G22" s="38" t="inlineStr">
         <is>
@@ -2179,17 +2193,17 @@
           <t>دخول السيد المسيح إلى أرض مصر</t>
         </is>
       </c>
-      <c r="I23" s="83" t="inlineStr">
+      <c r="I23" s="85" t="inlineStr">
         <is>
           <t>دور القمر في السنة الحالية</t>
         </is>
       </c>
-      <c r="J23" s="84" t="inlineStr">
+      <c r="J23" s="86" t="inlineStr">
         <is>
           <t>الفصح في السنة الحالية</t>
         </is>
       </c>
-      <c r="K23" s="80" t="n"/>
+      <c r="K23" s="82" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="55">
       <c r="D24" s="39" t="n">
@@ -2200,14 +2214,14 @@
         <v/>
       </c>
       <c r="F24" s="40" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G24" s="41" t="inlineStr">
         <is>
           <t>عيد الصعود</t>
         </is>
       </c>
-      <c r="I24" s="82" t="n"/>
+      <c r="I24" s="84" t="n"/>
       <c r="J24" s="11" t="inlineStr">
         <is>
           <t>اليوم</t>
@@ -2221,14 +2235,14 @@
     </row>
     <row r="25" ht="21" customHeight="1" s="55">
       <c r="D25" s="39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="36">
         <f>VLOOKUP(D25, $A$2:$B$100, 2, FALSE)</f>
         <v/>
       </c>
       <c r="F25" s="40" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G25" s="41" t="inlineStr">
         <is>
@@ -2236,7 +2250,7 @@
         </is>
       </c>
       <c r="I25" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="15">
         <f>VLOOKUP(I25,I3:J21, 2, FALSE)</f>
@@ -2351,7 +2365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="70" min="1" max="1"/>
     <col width="15" customWidth="1" style="70" min="2" max="2"/>
@@ -2371,8 +2385,8 @@
     <col width="12.7109375" customWidth="1" style="70" min="17" max="17"/>
     <col width="13.85546875" customWidth="1" style="70" min="18" max="18"/>
     <col width="14.140625" customWidth="1" style="70" min="19" max="19"/>
-    <col width="9.140625" customWidth="1" style="70" min="20" max="51"/>
-    <col width="9.140625" customWidth="1" style="70" min="52" max="16384"/>
+    <col width="9.140625" customWidth="1" style="70" min="20" max="59"/>
+    <col width="9.140625" customWidth="1" style="70" min="60" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" customFormat="1" customHeight="1" s="44">
@@ -2474,7 +2488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="45" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B2" s="45" t="n">
         <v>6</v>
@@ -2527,7 +2541,7 @@
     </row>
     <row r="3">
       <c r="A3" s="45" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B3" s="45" t="n">
         <v>6</v>
@@ -2586,7 +2600,7 @@
     </row>
     <row r="4">
       <c r="A4" s="45" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B4" s="45" t="n">
         <v>6</v>
@@ -2635,7 +2649,7 @@
     </row>
     <row r="5">
       <c r="A5" s="45" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B5" s="45" t="n">
         <v>6</v>
@@ -2680,7 +2694,7 @@
     </row>
     <row r="6">
       <c r="A6" s="45" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B6" s="45" t="n">
         <v>6</v>
@@ -2725,7 +2739,7 @@
     </row>
     <row r="7">
       <c r="A7" s="45" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" s="45" t="n">
         <v>6</v>
@@ -2770,7 +2784,7 @@
     </row>
     <row r="8">
       <c r="A8" s="45" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B8" s="45" t="n">
         <v>6</v>
@@ -2815,7 +2829,7 @@
     </row>
     <row r="9">
       <c r="A9" s="45" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B9" s="45" t="n">
         <v>6</v>
@@ -2858,7 +2872,7 @@
     </row>
     <row r="10">
       <c r="A10" s="45" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B10" s="45" t="n">
         <v>6</v>
@@ -2917,7 +2931,7 @@
     </row>
     <row r="11">
       <c r="A11" s="45" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B11" s="45" t="n">
         <v>6</v>
@@ -2962,7 +2976,7 @@
     </row>
     <row r="12">
       <c r="A12" s="45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B12" s="45" t="n">
         <v>6</v>
@@ -3007,7 +3021,7 @@
     </row>
     <row r="13">
       <c r="A13" s="45" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B13" s="45" t="n">
         <v>6</v>
@@ -3052,7 +3066,7 @@
     </row>
     <row r="14">
       <c r="A14" s="45" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B14" s="45" t="n">
         <v>6</v>
@@ -3097,7 +3111,7 @@
     </row>
     <row r="15">
       <c r="A15" s="45" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B15" s="45" t="n">
         <v>6</v>
@@ -3142,7 +3156,7 @@
     </row>
     <row r="16">
       <c r="A16" s="45" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B16" s="45" t="n">
         <v>6</v>
@@ -3185,7 +3199,7 @@
     </row>
     <row r="17">
       <c r="A17" s="45" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B17" s="45" t="n">
         <v>6</v>
@@ -3244,10 +3258,10 @@
     </row>
     <row r="18">
       <c r="A18" s="45" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B18" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="45" t="n"/>
       <c r="D18" s="45" t="n"/>
@@ -3289,10 +3303,10 @@
     </row>
     <row r="19">
       <c r="A19" s="45" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B19" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="45" t="n"/>
       <c r="D19" s="45" t="n"/>
@@ -3334,10 +3348,10 @@
     </row>
     <row r="20">
       <c r="A20" s="45" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B20" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="45" t="n"/>
       <c r="D20" s="45" t="n"/>
@@ -3379,10 +3393,10 @@
     </row>
     <row r="21">
       <c r="A21" s="45" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B21" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="45" t="n"/>
       <c r="D21" s="45" t="n"/>
@@ -3424,10 +3438,10 @@
     </row>
     <row r="22">
       <c r="A22" s="45" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B22" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="45" t="n"/>
       <c r="D22" s="45" t="n"/>
@@ -3469,10 +3483,10 @@
     </row>
     <row r="23">
       <c r="A23" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="B23" s="45" t="n">
         <v>6</v>
-      </c>
-      <c r="B23" s="45" t="n">
-        <v>7</v>
       </c>
       <c r="C23" s="45" t="n"/>
       <c r="D23" s="45" t="n"/>
@@ -3512,10 +3526,10 @@
     </row>
     <row r="24">
       <c r="A24" s="45" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B24" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="45" t="n">
         <v>1059</v>
@@ -3571,10 +3585,10 @@
     </row>
     <row r="25">
       <c r="A25" s="45" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B25" s="45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="45" t="n"/>
       <c r="D25" s="45" t="n"/>
@@ -3616,7 +3630,7 @@
     </row>
     <row r="26">
       <c r="A26" s="45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B26" s="45" t="n">
         <v>7</v>
@@ -3661,7 +3675,7 @@
     </row>
     <row r="27">
       <c r="A27" s="45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B27" s="45" t="n">
         <v>7</v>
@@ -3706,7 +3720,7 @@
     </row>
     <row r="28">
       <c r="A28" s="45" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B28" s="45" t="n">
         <v>7</v>
@@ -3751,7 +3765,7 @@
     </row>
     <row r="29">
       <c r="A29" s="45" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B29" s="45" t="n">
         <v>7</v>
@@ -3796,7 +3810,7 @@
     </row>
     <row r="30">
       <c r="A30" s="45" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B30" s="45" t="n">
         <v>7</v>
@@ -3839,7 +3853,7 @@
     </row>
     <row r="31">
       <c r="A31" s="45" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B31" s="45" t="n">
         <v>7</v>
@@ -3898,7 +3912,7 @@
     </row>
     <row r="32">
       <c r="A32" s="45" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B32" s="45" t="n">
         <v>7</v>
@@ -3943,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" s="45" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B33" s="45" t="n">
         <v>7</v>
@@ -3988,7 +4002,7 @@
     </row>
     <row r="34">
       <c r="A34" s="45" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B34" s="45" t="n">
         <v>7</v>
@@ -4033,7 +4047,7 @@
     </row>
     <row r="35">
       <c r="A35" s="45" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B35" s="45" t="n">
         <v>7</v>
@@ -4078,7 +4092,7 @@
     </row>
     <row r="36">
       <c r="A36" s="45" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B36" s="45" t="n">
         <v>7</v>
@@ -4123,7 +4137,7 @@
     </row>
     <row r="37">
       <c r="A37" s="45" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B37" s="45" t="n">
         <v>7</v>
@@ -4166,7 +4180,7 @@
     </row>
     <row r="38">
       <c r="A38" s="45" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B38" s="45" t="n">
         <v>7</v>
@@ -4225,7 +4239,7 @@
     </row>
     <row r="39">
       <c r="A39" s="45" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B39" s="45" t="n">
         <v>7</v>
@@ -4270,7 +4284,7 @@
     </row>
     <row r="40">
       <c r="A40" s="45" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B40" s="45" t="n">
         <v>7</v>
@@ -4315,7 +4329,7 @@
     </row>
     <row r="41">
       <c r="A41" s="45" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B41" s="45" t="n">
         <v>7</v>
@@ -4360,7 +4374,7 @@
     </row>
     <row r="42">
       <c r="A42" s="45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B42" s="45" t="n">
         <v>7</v>
@@ -4405,7 +4419,7 @@
     </row>
     <row r="43">
       <c r="A43" s="45" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B43" s="45" t="n">
         <v>7</v>
@@ -4450,7 +4464,7 @@
     </row>
     <row r="44">
       <c r="A44" s="45" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B44" s="45" t="n">
         <v>7</v>
@@ -4493,7 +4507,7 @@
     </row>
     <row r="45">
       <c r="A45" s="45" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B45" s="45" t="n">
         <v>7</v>
@@ -4552,7 +4566,7 @@
     </row>
     <row r="46">
       <c r="A46" s="45" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B46" s="45" t="n">
         <v>7</v>
@@ -4597,7 +4611,7 @@
     </row>
     <row r="47">
       <c r="A47" s="45" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B47" s="45" t="n">
         <v>7</v>
@@ -4642,10 +4656,10 @@
     </row>
     <row r="48">
       <c r="A48" s="45" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B48" s="45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48" s="45" t="n"/>
       <c r="D48" s="45" t="n"/>
@@ -4687,10 +4701,10 @@
     </row>
     <row r="49">
       <c r="A49" s="45" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B49" s="45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="45" t="n"/>
       <c r="D49" s="45" t="n"/>
@@ -4732,10 +4746,10 @@
     </row>
     <row r="50">
       <c r="A50" s="45" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B50" s="45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" s="45" t="n"/>
       <c r="D50" s="45" t="n"/>
@@ -4777,10 +4791,10 @@
     </row>
     <row r="51">
       <c r="A51" s="45" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B51" s="45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C51" s="45" t="n"/>
       <c r="D51" s="45" t="n"/>
@@ -4837,7 +4851,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.42578125" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.7109375" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -4971,10 +4985,10 @@
     </row>
     <row r="2" ht="23.25" customHeight="1" s="55">
       <c r="A2" s="48" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B2" s="48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="48" t="n">
         <v>1</v>
@@ -5046,8 +5060,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -5056,53 +5070,59 @@
     <col width="12.7109375" bestFit="1" customWidth="1" style="55" min="5" max="5"/>
     <col width="9.28515625" bestFit="1" customWidth="1" style="55" min="7" max="7"/>
     <col width="15.140625" bestFit="1" customWidth="1" style="55" min="8" max="8"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" style="70" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="55">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="C1" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">البولس </t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="D1" s="83" t="inlineStr">
         <is>
           <t>الكاثوليكون</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>الابركسيس</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="F1" s="83" t="inlineStr">
         <is>
           <t>المزمور</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="G1" s="83" t="inlineStr">
         <is>
           <t>الإنجيل</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="H1" s="83" t="inlineStr">
         <is>
           <t>نهاية الانجيل</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="I1" s="79" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="55">
       <c r="A2" s="8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>8</v>
@@ -5125,10 +5145,15 @@
       <c r="H2" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="I2" s="80" t="inlineStr">
+        <is>
+          <t>عيد القيامة</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B3" s="49" t="n">
         <v>8</v>
@@ -5151,10 +5176,11 @@
       <c r="H3" s="49" t="n">
         <v>64</v>
       </c>
+      <c r="I3" s="45" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="49" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B4" s="49" t="n">
         <v>8</v>
@@ -5177,10 +5203,11 @@
       <c r="H4" s="49" t="n">
         <v>87</v>
       </c>
+      <c r="I4" s="45" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="49" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B5" s="49" t="n">
         <v>8</v>
@@ -5203,10 +5230,11 @@
       <c r="H5" s="49" t="n">
         <v>108</v>
       </c>
+      <c r="I5" s="45" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="49" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B6" s="49" t="n">
         <v>8</v>
@@ -5229,10 +5257,11 @@
       <c r="H6" s="49" t="n">
         <v>126</v>
       </c>
+      <c r="I6" s="45" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="49" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="49" t="n">
         <v>8</v>
@@ -5255,10 +5284,11 @@
       <c r="H7" s="49" t="n">
         <v>140</v>
       </c>
+      <c r="I7" s="45" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="49" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="49" t="n">
         <v>8</v>
@@ -5281,10 +5311,11 @@
       <c r="H8" s="49" t="n">
         <v>159</v>
       </c>
+      <c r="I8" s="45" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="49" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B9" s="49" t="n">
         <v>8</v>
@@ -5307,10 +5338,11 @@
       <c r="H9" s="49" t="n">
         <v>180</v>
       </c>
+      <c r="I9" s="45" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="49" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="49" t="n">
         <v>8</v>
@@ -5333,10 +5365,11 @@
       <c r="H10" s="49" t="n">
         <v>189</v>
       </c>
+      <c r="I10" s="45" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="49" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B11" s="49" t="n">
         <v>8</v>
@@ -5359,10 +5392,11 @@
       <c r="H11" s="49" t="n">
         <v>198</v>
       </c>
+      <c r="I11" s="45" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="49" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B12" s="49" t="n">
         <v>8</v>
@@ -5385,10 +5419,11 @@
       <c r="H12" s="49" t="n">
         <v>209</v>
       </c>
+      <c r="I12" s="45" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="49" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B13" s="49" t="n">
         <v>8</v>
@@ -5411,10 +5446,11 @@
       <c r="H13" s="49" t="n">
         <v>220</v>
       </c>
+      <c r="I13" s="45" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="49" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B14" s="49" t="n">
         <v>8</v>
@@ -5437,10 +5473,11 @@
       <c r="H14" s="49" t="n">
         <v>228</v>
       </c>
+      <c r="I14" s="45" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B15" s="49" t="n">
         <v>8</v>
@@ -5463,10 +5500,11 @@
       <c r="H15" s="49" t="n">
         <v>242</v>
       </c>
+      <c r="I15" s="45" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="49" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B16" s="49" t="n">
         <v>8</v>
@@ -5489,10 +5527,11 @@
       <c r="H16" s="49" t="n">
         <v>260</v>
       </c>
+      <c r="I16" s="45" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="49" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B17" s="49" t="n">
         <v>8</v>
@@ -5515,10 +5554,11 @@
       <c r="H17" s="49" t="n">
         <v>268</v>
       </c>
+      <c r="I17" s="45" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="49" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B18" s="49" t="n">
         <v>8</v>
@@ -5541,10 +5581,11 @@
       <c r="H18" s="49" t="n">
         <v>281</v>
       </c>
+      <c r="I18" s="45" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="49" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B19" s="49" t="n">
         <v>8</v>
@@ -5567,10 +5608,11 @@
       <c r="H19" s="49" t="n">
         <v>290</v>
       </c>
+      <c r="I19" s="45" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="49" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B20" s="49" t="n">
         <v>8</v>
@@ -5593,13 +5635,14 @@
       <c r="H20" s="49" t="n">
         <v>300</v>
       </c>
+      <c r="I20" s="45" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="49" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B21" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="49" t="n">
         <v>302</v>
@@ -5619,13 +5662,14 @@
       <c r="H21" s="49" t="n">
         <v>312</v>
       </c>
+      <c r="I21" s="45" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="49" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B22" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="49" t="n">
         <v>314</v>
@@ -5645,13 +5689,14 @@
       <c r="H22" s="49" t="n">
         <v>328</v>
       </c>
+      <c r="I22" s="45" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="49" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B23" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="49" t="n">
         <v>330</v>
@@ -5671,13 +5716,14 @@
       <c r="H23" s="49" t="n">
         <v>358</v>
       </c>
+      <c r="I23" s="45" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="49" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B24" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="49" t="n">
         <v>360</v>
@@ -5697,13 +5743,14 @@
       <c r="H24" s="49" t="n">
         <v>370</v>
       </c>
+      <c r="I24" s="45" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="49" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B25" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="49" t="n">
         <v>372</v>
@@ -5723,13 +5770,14 @@
       <c r="H25" s="49" t="n">
         <v>378</v>
       </c>
+      <c r="I25" s="45" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="49" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B26" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="49" t="n">
         <v>380</v>
@@ -5749,13 +5797,14 @@
       <c r="H26" s="49" t="n">
         <v>395</v>
       </c>
+      <c r="I26" s="45" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="49" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B27" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="49" t="n">
         <v>397</v>
@@ -5775,13 +5824,14 @@
       <c r="H27" s="49" t="n">
         <v>407</v>
       </c>
+      <c r="I27" s="45" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" s="49" t="n">
         <v>8</v>
-      </c>
-      <c r="B28" s="49" t="n">
-        <v>9</v>
       </c>
       <c r="C28" s="49" t="n">
         <v>409</v>
@@ -5801,10 +5851,11 @@
       <c r="H28" s="49" t="n">
         <v>418</v>
       </c>
+      <c r="I28" s="45" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B29" s="49" t="n">
         <v>9</v>
@@ -5827,10 +5878,11 @@
       <c r="H29" s="49" t="n">
         <v>437</v>
       </c>
+      <c r="I29" s="45" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="49" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B30" s="49" t="n">
         <v>9</v>
@@ -5853,10 +5905,11 @@
       <c r="H30" s="49" t="n">
         <v>458</v>
       </c>
+      <c r="I30" s="45" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B31" s="49" t="n">
         <v>9</v>
@@ -5879,10 +5932,11 @@
       <c r="H31" s="49" t="n">
         <v>470</v>
       </c>
+      <c r="I31" s="45" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="49" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B32" s="49" t="n">
         <v>9</v>
@@ -5905,10 +5959,11 @@
       <c r="H32" s="49" t="n">
         <v>481</v>
       </c>
+      <c r="I32" s="45" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B33" s="49" t="n">
         <v>9</v>
@@ -5931,10 +5986,11 @@
       <c r="H33" s="49" t="n">
         <v>494</v>
       </c>
+      <c r="I33" s="45" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="49" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B34" s="49" t="n">
         <v>9</v>
@@ -5957,10 +6013,11 @@
       <c r="H34" s="49" t="n">
         <v>506</v>
       </c>
+      <c r="I34" s="45" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="49" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B35" s="49" t="n">
         <v>9</v>
@@ -5983,10 +6040,11 @@
       <c r="H35" s="49" t="n">
         <v>515</v>
       </c>
+      <c r="I35" s="45" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="49" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B36" s="49" t="n">
         <v>9</v>
@@ -6009,10 +6067,11 @@
       <c r="H36" s="49" t="n">
         <v>534</v>
       </c>
+      <c r="I36" s="45" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="49" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B37" s="49" t="n">
         <v>9</v>
@@ -6035,10 +6094,11 @@
       <c r="H37" s="49" t="n">
         <v>559</v>
       </c>
+      <c r="I37" s="45" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="49" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B38" s="49" t="n">
         <v>9</v>
@@ -6061,10 +6121,11 @@
       <c r="H38" s="49" t="n">
         <v>574</v>
       </c>
+      <c r="I38" s="45" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="49" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B39" s="49" t="n">
         <v>9</v>
@@ -6087,10 +6148,11 @@
       <c r="H39" s="49" t="n">
         <v>587</v>
       </c>
+      <c r="I39" s="45" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="49" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B40" s="49" t="n">
         <v>9</v>
@@ -6113,10 +6175,11 @@
       <c r="H40" s="49" t="n">
         <v>602</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="I40" s="45" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="55">
       <c r="A41" s="8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B41" s="8" t="n">
         <v>9</v>
@@ -6139,10 +6202,15 @@
       <c r="H41" s="8" t="n">
         <v>625</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="I41" s="80" t="inlineStr">
+        <is>
+          <t>عيد الصعود</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="55">
       <c r="A42" s="49" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B42" s="49" t="n">
         <v>9</v>
@@ -6165,10 +6233,11 @@
       <c r="H42" s="49" t="n">
         <v>643</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="I42" s="80" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="55">
       <c r="A43" s="49" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B43" s="49" t="n">
         <v>9</v>
@@ -6191,10 +6260,11 @@
       <c r="H43" s="49" t="n">
         <v>658</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="I43" s="80" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="55">
       <c r="A44" s="49" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B44" s="49" t="n">
         <v>9</v>
@@ -6217,10 +6287,11 @@
       <c r="H44" s="49" t="n">
         <v>678</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="I44" s="80" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="55">
       <c r="A45" s="49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B45" s="49" t="n">
         <v>9</v>
@@ -6243,10 +6314,11 @@
       <c r="H45" s="49" t="n">
         <v>694</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="I45" s="80" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="55">
       <c r="A46" s="49" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B46" s="49" t="n">
         <v>9</v>
@@ -6269,10 +6341,11 @@
       <c r="H46" s="49" t="n">
         <v>707</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="I46" s="80" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="55">
       <c r="A47" s="49" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B47" s="49" t="n">
         <v>9</v>
@@ -6295,10 +6368,11 @@
       <c r="H47" s="49" t="n">
         <v>724</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="I47" s="80" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" s="55">
       <c r="A48" s="49" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B48" s="49" t="n">
         <v>9</v>
@@ -6321,10 +6395,11 @@
       <c r="H48" s="49" t="n">
         <v>740</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="I48" s="80" t="n"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" s="55">
       <c r="A49" s="49" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B49" s="49" t="n">
         <v>9</v>
@@ -6347,10 +6422,11 @@
       <c r="H49" s="49" t="n">
         <v>751</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="I49" s="80" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="55">
       <c r="A50" s="49" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B50" s="49" t="n">
         <v>9</v>
@@ -6373,13 +6449,14 @@
       <c r="H50" s="49" t="n">
         <v>777</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="I50" s="80" t="n"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" s="55">
       <c r="A51" s="8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B51" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>779</v>
@@ -6398,6 +6475,11 @@
       </c>
       <c r="H51" s="8" t="n">
         <v>813</v>
+      </c>
+      <c r="I51" s="80" t="inlineStr">
+        <is>
+          <t>عيد العنصرة</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +9436,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -12682,7 +12764,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.140625" customWidth="1" style="55" min="5" max="5"/>
   </cols>
@@ -15139,7 +15221,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -17019,8 +17101,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.85546875" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -17895,7 +17977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="55">
@@ -18766,7 +18848,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -20100,7 +20182,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -20197,10 +20279,10 @@
     </row>
     <row r="2">
       <c r="A2" s="49" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B2" s="49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="49" t="n">
         <v>2</v>
@@ -20244,10 +20326,10 @@
     </row>
     <row r="3">
       <c r="A3" s="49" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B3" s="49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="49" t="inlineStr"/>
       <c r="D3" s="49" t="inlineStr"/>
@@ -20285,10 +20367,10 @@
     </row>
     <row r="4">
       <c r="A4" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="B4" s="49" t="n">
         <v>5</v>
-      </c>
-      <c r="B4" s="49" t="n">
-        <v>6</v>
       </c>
       <c r="C4" s="49" t="inlineStr"/>
       <c r="D4" s="49" t="inlineStr"/>
@@ -20326,10 +20408,10 @@
     </row>
     <row r="5">
       <c r="A5" s="49" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B5" s="49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="49" t="inlineStr"/>
       <c r="D5" s="49" t="inlineStr"/>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="868" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="868" firstSheet="6" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المناسبات" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قطمارس الصوم الكبير" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قرائات أحد الشعانين" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قطمارس الخماسين" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السنكسار " sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السنكسار" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -146,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -264,6 +264,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF34BA8D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,7 +543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -739,13 +745,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -772,6 +778,16 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1382,7 +1398,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="17.85546875" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4.42578125" bestFit="1" customWidth="1" style="70" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="70" min="2" max="2"/>
@@ -1397,8 +1413,8 @@
     <col width="11.140625" customWidth="1" style="70" min="11" max="11"/>
     <col width="17.85546875" customWidth="1" style="70" min="12" max="12"/>
     <col width="28" customWidth="1" style="70" min="13" max="13"/>
-    <col width="17.85546875" customWidth="1" style="70" min="14" max="105"/>
-    <col width="17.85546875" customWidth="1" style="70" min="106" max="16384"/>
+    <col width="17.85546875" customWidth="1" style="70" min="14" max="108"/>
+    <col width="17.85546875" customWidth="1" style="70" min="109" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" s="55">
@@ -2365,7 +2381,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" style="70" min="1" max="1"/>
     <col width="15" customWidth="1" style="70" min="2" max="2"/>
@@ -2385,8 +2401,8 @@
     <col width="12.7109375" customWidth="1" style="70" min="17" max="17"/>
     <col width="13.85546875" customWidth="1" style="70" min="18" max="18"/>
     <col width="14.140625" customWidth="1" style="70" min="19" max="19"/>
-    <col width="9.140625" customWidth="1" style="70" min="20" max="59"/>
-    <col width="9.140625" customWidth="1" style="70" min="60" max="16384"/>
+    <col width="9.140625" customWidth="1" style="70" min="20" max="62"/>
+    <col width="9.140625" customWidth="1" style="70" min="63" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" customFormat="1" customHeight="1" s="44">
@@ -4851,7 +4867,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.42578125" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.7109375" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -5061,7 +5077,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -5114,7 +5130,7 @@
           <t>نهاية الانجيل</t>
         </is>
       </c>
-      <c r="I1" s="79" t="inlineStr">
+      <c r="I1" s="78" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
@@ -5145,7 +5161,7 @@
       <c r="H2" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="I2" s="80" t="inlineStr">
+      <c r="I2" s="79" t="inlineStr">
         <is>
           <t>عيد القيامة</t>
         </is>
@@ -6202,7 +6218,7 @@
       <c r="H41" s="8" t="n">
         <v>625</v>
       </c>
-      <c r="I41" s="80" t="inlineStr">
+      <c r="I41" s="79" t="inlineStr">
         <is>
           <t>عيد الصعود</t>
         </is>
@@ -6233,7 +6249,7 @@
       <c r="H42" s="49" t="n">
         <v>643</v>
       </c>
-      <c r="I42" s="80" t="n"/>
+      <c r="I42" s="79" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="55">
       <c r="A43" s="49" t="n">
@@ -6260,7 +6276,7 @@
       <c r="H43" s="49" t="n">
         <v>658</v>
       </c>
-      <c r="I43" s="80" t="n"/>
+      <c r="I43" s="79" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="55">
       <c r="A44" s="49" t="n">
@@ -6287,7 +6303,7 @@
       <c r="H44" s="49" t="n">
         <v>678</v>
       </c>
-      <c r="I44" s="80" t="n"/>
+      <c r="I44" s="79" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="55">
       <c r="A45" s="49" t="n">
@@ -6314,7 +6330,7 @@
       <c r="H45" s="49" t="n">
         <v>694</v>
       </c>
-      <c r="I45" s="80" t="n"/>
+      <c r="I45" s="79" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="55">
       <c r="A46" s="49" t="n">
@@ -6341,7 +6357,7 @@
       <c r="H46" s="49" t="n">
         <v>707</v>
       </c>
-      <c r="I46" s="80" t="n"/>
+      <c r="I46" s="79" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="55">
       <c r="A47" s="49" t="n">
@@ -6368,7 +6384,7 @@
       <c r="H47" s="49" t="n">
         <v>724</v>
       </c>
-      <c r="I47" s="80" t="n"/>
+      <c r="I47" s="79" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="55">
       <c r="A48" s="49" t="n">
@@ -6395,7 +6411,7 @@
       <c r="H48" s="49" t="n">
         <v>740</v>
       </c>
-      <c r="I48" s="80" t="n"/>
+      <c r="I48" s="79" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="55">
       <c r="A49" s="49" t="n">
@@ -6422,7 +6438,7 @@
       <c r="H49" s="49" t="n">
         <v>751</v>
       </c>
-      <c r="I49" s="80" t="n"/>
+      <c r="I49" s="79" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="55">
       <c r="A50" s="49" t="n">
@@ -6449,7 +6465,7 @@
       <c r="H50" s="49" t="n">
         <v>777</v>
       </c>
-      <c r="I50" s="80" t="n"/>
+      <c r="I50" s="79" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="55">
       <c r="A51" s="8" t="n">
@@ -6476,7 +6492,7 @@
       <c r="H51" s="8" t="n">
         <v>813</v>
       </c>
-      <c r="I51" s="80" t="inlineStr">
+      <c r="I51" s="79" t="inlineStr">
         <is>
           <t>عيد العنصرة</t>
         </is>
@@ -6493,2938 +6509,5638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:F351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
+    <row r="1" ht="27.75" customHeight="1" s="55">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>اليوم</t>
+        </is>
+      </c>
+      <c r="B1" s="94" t="inlineStr">
+        <is>
+          <t>الشهر</t>
+        </is>
+      </c>
+      <c r="C1" s="94" t="inlineStr">
+        <is>
+          <t>عناوين فقط</t>
+        </is>
+      </c>
+      <c r="D1" s="97" t="n"/>
+      <c r="E1" s="94" t="inlineStr">
+        <is>
+          <t>النص كامل</t>
+        </is>
+      </c>
+      <c r="F1" s="97" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B1" t="n">
+      <c r="B2" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+      <c r="C2" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C3" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C4" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="49" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="C5" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="C6" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="C7" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="C8" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C9" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="49" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="C10" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C11" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="C12" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="C13" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="C14" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="D14" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="C15" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="C16" s="49" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" s="49" t="n">
+        <v>31</v>
+      </c>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="C17" s="49" t="n">
+        <v>33</v>
+      </c>
+      <c r="D17" s="49" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="C18" s="49" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="C19" s="49" t="n">
+        <v>37</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>37</v>
+      </c>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="C20" s="49" t="n">
+        <v>39</v>
+      </c>
+      <c r="D20" s="49" t="n">
+        <v>39</v>
+      </c>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="C21" s="49" t="n">
+        <v>41</v>
+      </c>
+      <c r="D21" s="49" t="n">
+        <v>41</v>
+      </c>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="C22" s="49" t="n">
+        <v>43</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <v>43</v>
+      </c>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="C23" s="49" t="n">
+        <v>45</v>
+      </c>
+      <c r="D23" s="49" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="C24" s="49" t="n">
+        <v>47</v>
+      </c>
+      <c r="D24" s="49" t="n">
+        <v>47</v>
+      </c>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="C25" s="49" t="n">
+        <v>49</v>
+      </c>
+      <c r="D25" s="49" t="n">
+        <v>49</v>
+      </c>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="C26" s="49" t="n">
+        <v>51</v>
+      </c>
+      <c r="D26" s="49" t="n">
+        <v>51</v>
+      </c>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B27" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="C27" s="49" t="n">
+        <v>53</v>
+      </c>
+      <c r="D27" s="49" t="n">
+        <v>53</v>
+      </c>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B28" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="C28" s="49" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" s="49" t="n">
+        <v>55</v>
+      </c>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="C29" s="49" t="n">
+        <v>57</v>
+      </c>
+      <c r="D29" s="49" t="n">
+        <v>57</v>
+      </c>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="C30" s="49" t="n">
+        <v>59</v>
+      </c>
+      <c r="D30" s="49" t="n">
+        <v>59</v>
+      </c>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B31" s="49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="C31" s="49" t="n">
+        <v>61</v>
+      </c>
+      <c r="D31" s="49" t="n">
+        <v>61</v>
+      </c>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B32" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="C32" s="49" t="n">
+        <v>63</v>
+      </c>
+      <c r="D32" s="49" t="n">
+        <v>63</v>
+      </c>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B33" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="C33" s="49" t="n">
+        <v>65</v>
+      </c>
+      <c r="D33" s="49" t="n">
+        <v>65</v>
+      </c>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B34" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="C34" s="49" t="n">
+        <v>67</v>
+      </c>
+      <c r="D34" s="49" t="n">
+        <v>67</v>
+      </c>
+      <c r="E34" s="49" t="n"/>
+      <c r="F34" s="49" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="C35" s="49" t="n">
+        <v>69</v>
+      </c>
+      <c r="D35" s="49" t="n">
+        <v>69</v>
+      </c>
+      <c r="E35" s="49" t="n"/>
+      <c r="F35" s="49" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B36" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="C36" s="49" t="n">
+        <v>71</v>
+      </c>
+      <c r="D36" s="49" t="n">
+        <v>71</v>
+      </c>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B37" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="C37" s="49" t="n">
+        <v>73</v>
+      </c>
+      <c r="D37" s="49" t="n">
+        <v>73</v>
+      </c>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B38" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="C38" s="49" t="n">
+        <v>75</v>
+      </c>
+      <c r="D38" s="49" t="n">
+        <v>75</v>
+      </c>
+      <c r="E38" s="49" t="n"/>
+      <c r="F38" s="49" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B39" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="C39" s="49" t="n">
+        <v>77</v>
+      </c>
+      <c r="D39" s="49" t="n">
+        <v>77</v>
+      </c>
+      <c r="E39" s="49" t="n"/>
+      <c r="F39" s="49" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B40" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="C40" s="49" t="n">
+        <v>79</v>
+      </c>
+      <c r="D40" s="49" t="n">
+        <v>79</v>
+      </c>
+      <c r="E40" s="49" t="n"/>
+      <c r="F40" s="49" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B41" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="C41" s="49" t="n">
+        <v>81</v>
+      </c>
+      <c r="D41" s="49" t="n">
+        <v>81</v>
+      </c>
+      <c r="E41" s="49" t="n"/>
+      <c r="F41" s="49" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="C42" s="49" t="n">
+        <v>83</v>
+      </c>
+      <c r="D42" s="49" t="n">
+        <v>83</v>
+      </c>
+      <c r="E42" s="49" t="n"/>
+      <c r="F42" s="49" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B43" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="C43" s="49" t="n">
+        <v>85</v>
+      </c>
+      <c r="D43" s="49" t="n">
+        <v>85</v>
+      </c>
+      <c r="E43" s="49" t="n"/>
+      <c r="F43" s="49" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B44" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
+      <c r="C44" s="49" t="n">
+        <v>87</v>
+      </c>
+      <c r="D44" s="49" t="n">
+        <v>87</v>
+      </c>
+      <c r="E44" s="49" t="n"/>
+      <c r="F44" s="49" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B45" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="C45" s="49" t="n">
+        <v>89</v>
+      </c>
+      <c r="D45" s="49" t="n">
+        <v>89</v>
+      </c>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B46" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="C46" s="49" t="n">
+        <v>91</v>
+      </c>
+      <c r="D46" s="49" t="n">
+        <v>91</v>
+      </c>
+      <c r="E46" s="49" t="n"/>
+      <c r="F46" s="49" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B47" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="C47" s="49" t="n">
+        <v>93</v>
+      </c>
+      <c r="D47" s="49" t="n">
+        <v>93</v>
+      </c>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B48" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="C48" s="49" t="n">
+        <v>95</v>
+      </c>
+      <c r="D48" s="49" t="n">
+        <v>95</v>
+      </c>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B49" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="C49" s="49" t="n">
+        <v>97</v>
+      </c>
+      <c r="D49" s="49" t="n">
+        <v>97</v>
+      </c>
+      <c r="E49" s="49" t="n"/>
+      <c r="F49" s="49" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B50" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="C50" s="49" t="n">
+        <v>99</v>
+      </c>
+      <c r="D50" s="49" t="n">
+        <v>99</v>
+      </c>
+      <c r="E50" s="49" t="n"/>
+      <c r="F50" s="49" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B51" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
+      <c r="C51" s="49" t="n">
+        <v>101</v>
+      </c>
+      <c r="D51" s="49" t="n">
+        <v>101</v>
+      </c>
+      <c r="E51" s="49" t="n"/>
+      <c r="F51" s="49" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B52" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="C52" s="49" t="n">
+        <v>103</v>
+      </c>
+      <c r="D52" s="49" t="n">
+        <v>103</v>
+      </c>
+      <c r="E52" s="49" t="n"/>
+      <c r="F52" s="49" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B53" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="C53" s="49" t="n">
+        <v>105</v>
+      </c>
+      <c r="D53" s="49" t="n">
+        <v>105</v>
+      </c>
+      <c r="E53" s="49" t="n"/>
+      <c r="F53" s="49" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B54" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="C54" s="49" t="n">
+        <v>107</v>
+      </c>
+      <c r="D54" s="49" t="n">
+        <v>107</v>
+      </c>
+      <c r="E54" s="49" t="n"/>
+      <c r="F54" s="49" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B55" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="C55" s="49" t="n">
+        <v>109</v>
+      </c>
+      <c r="D55" s="49" t="n">
+        <v>109</v>
+      </c>
+      <c r="E55" s="49" t="n"/>
+      <c r="F55" s="49" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B56" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="C56" s="49" t="n">
+        <v>111</v>
+      </c>
+      <c r="D56" s="49" t="n">
+        <v>111</v>
+      </c>
+      <c r="E56" s="49" t="n"/>
+      <c r="F56" s="49" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B57" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
+      <c r="C57" s="49" t="n">
+        <v>113</v>
+      </c>
+      <c r="D57" s="49" t="n">
+        <v>113</v>
+      </c>
+      <c r="E57" s="49" t="n"/>
+      <c r="F57" s="49" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B58" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="C58" s="49" t="n">
+        <v>115</v>
+      </c>
+      <c r="D58" s="49" t="n">
+        <v>115</v>
+      </c>
+      <c r="E58" s="49" t="n"/>
+      <c r="F58" s="49" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B59" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="C59" s="49" t="n">
+        <v>117</v>
+      </c>
+      <c r="D59" s="49" t="n">
+        <v>117</v>
+      </c>
+      <c r="E59" s="49" t="n"/>
+      <c r="F59" s="49" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B60" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="C60" s="49" t="n">
+        <v>119</v>
+      </c>
+      <c r="D60" s="49" t="n">
+        <v>119</v>
+      </c>
+      <c r="E60" s="49" t="n"/>
+      <c r="F60" s="49" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B61" s="49" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="C61" s="49" t="n">
+        <v>121</v>
+      </c>
+      <c r="D61" s="49" t="n">
+        <v>121</v>
+      </c>
+      <c r="E61" s="49" t="n"/>
+      <c r="F61" s="49" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B62" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
+      <c r="C62" s="49" t="n">
+        <v>123</v>
+      </c>
+      <c r="D62" s="49" t="n">
+        <v>123</v>
+      </c>
+      <c r="E62" s="49" t="n"/>
+      <c r="F62" s="49" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B63" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="C63" s="49" t="n">
+        <v>125</v>
+      </c>
+      <c r="D63" s="49" t="n">
+        <v>125</v>
+      </c>
+      <c r="E63" s="49" t="n"/>
+      <c r="F63" s="49" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B64" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="C64" s="49" t="n">
+        <v>127</v>
+      </c>
+      <c r="D64" s="49" t="n">
+        <v>127</v>
+      </c>
+      <c r="E64" s="49" t="n"/>
+      <c r="F64" s="49" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B65" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
+      <c r="C65" s="49" t="n">
+        <v>129</v>
+      </c>
+      <c r="D65" s="49" t="n">
+        <v>129</v>
+      </c>
+      <c r="E65" s="49" t="n"/>
+      <c r="F65" s="49" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B66" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="C66" s="49" t="n">
+        <v>131</v>
+      </c>
+      <c r="D66" s="49" t="n">
+        <v>131</v>
+      </c>
+      <c r="E66" s="49" t="n"/>
+      <c r="F66" s="49" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B67" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="C67" s="49" t="n">
+        <v>133</v>
+      </c>
+      <c r="D67" s="49" t="n">
+        <v>133</v>
+      </c>
+      <c r="E67" s="49" t="n"/>
+      <c r="F67" s="49" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B68" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="C68" s="49" t="n">
+        <v>135</v>
+      </c>
+      <c r="D68" s="49" t="n">
+        <v>135</v>
+      </c>
+      <c r="E68" s="49" t="n"/>
+      <c r="F68" s="49" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B69" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
+      <c r="C69" s="49" t="n">
+        <v>137</v>
+      </c>
+      <c r="D69" s="49" t="n">
+        <v>137</v>
+      </c>
+      <c r="E69" s="49" t="n"/>
+      <c r="F69" s="49" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B70" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+      <c r="C70" s="49" t="n">
+        <v>139</v>
+      </c>
+      <c r="D70" s="49" t="n">
+        <v>139</v>
+      </c>
+      <c r="E70" s="49" t="n"/>
+      <c r="F70" s="49" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B71" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
+      <c r="C71" s="49" t="n">
+        <v>141</v>
+      </c>
+      <c r="D71" s="49" t="n">
+        <v>141</v>
+      </c>
+      <c r="E71" s="49" t="n"/>
+      <c r="F71" s="49" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B72" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="C72" s="49" t="n">
+        <v>143</v>
+      </c>
+      <c r="D72" s="49" t="n">
+        <v>143</v>
+      </c>
+      <c r="E72" s="49" t="n"/>
+      <c r="F72" s="49" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B73" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
+      <c r="C73" s="49" t="n">
+        <v>145</v>
+      </c>
+      <c r="D73" s="49" t="n">
+        <v>145</v>
+      </c>
+      <c r="E73" s="49" t="n"/>
+      <c r="F73" s="49" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B74" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
+      <c r="C74" s="49" t="n">
+        <v>147</v>
+      </c>
+      <c r="D74" s="49" t="n">
+        <v>148</v>
+      </c>
+      <c r="E74" s="49" t="n"/>
+      <c r="F74" s="49" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B75" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="C75" s="49" t="n">
+        <v>150</v>
+      </c>
+      <c r="D75" s="49" t="n">
+        <v>150</v>
+      </c>
+      <c r="E75" s="49" t="n"/>
+      <c r="F75" s="49" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B76" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
+      <c r="C76" s="49" t="n">
+        <v>152</v>
+      </c>
+      <c r="D76" s="49" t="n">
+        <v>152</v>
+      </c>
+      <c r="E76" s="49" t="n"/>
+      <c r="F76" s="49" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B77" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
+      <c r="C77" s="49" t="n">
+        <v>154</v>
+      </c>
+      <c r="D77" s="49" t="n">
+        <v>155</v>
+      </c>
+      <c r="E77" s="49" t="n"/>
+      <c r="F77" s="49" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B78" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
+      <c r="C78" s="49" t="n">
+        <v>157</v>
+      </c>
+      <c r="D78" s="49" t="n">
+        <v>157</v>
+      </c>
+      <c r="E78" s="49" t="n"/>
+      <c r="F78" s="49" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B79" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
+      <c r="C79" s="49" t="n">
+        <v>159</v>
+      </c>
+      <c r="D79" s="49" t="n">
+        <v>159</v>
+      </c>
+      <c r="E79" s="49" t="n"/>
+      <c r="F79" s="49" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B80" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
+      <c r="C80" s="49" t="n">
+        <v>161</v>
+      </c>
+      <c r="D80" s="49" t="n">
+        <v>161</v>
+      </c>
+      <c r="E80" s="49" t="n"/>
+      <c r="F80" s="49" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B81" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
+      <c r="C81" s="49" t="n">
+        <v>163</v>
+      </c>
+      <c r="D81" s="49" t="n">
+        <v>163</v>
+      </c>
+      <c r="E81" s="49" t="n"/>
+      <c r="F81" s="49" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B82" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
+      <c r="C82" s="49" t="n">
+        <v>165</v>
+      </c>
+      <c r="D82" s="49" t="n">
+        <v>166</v>
+      </c>
+      <c r="E82" s="49" t="n"/>
+      <c r="F82" s="49" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B83" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
+      <c r="C83" s="49" t="n">
+        <v>168</v>
+      </c>
+      <c r="D83" s="49" t="n">
+        <v>168</v>
+      </c>
+      <c r="E83" s="49" t="n"/>
+      <c r="F83" s="49" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B84" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
+      <c r="C84" s="49" t="n">
+        <v>170</v>
+      </c>
+      <c r="D84" s="49" t="n">
+        <v>170</v>
+      </c>
+      <c r="E84" s="49" t="n"/>
+      <c r="F84" s="49" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B85" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
+      <c r="C85" s="49" t="n">
+        <v>172</v>
+      </c>
+      <c r="D85" s="49" t="n">
+        <v>172</v>
+      </c>
+      <c r="E85" s="49" t="n"/>
+      <c r="F85" s="49" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B86" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
+      <c r="C86" s="49" t="n">
+        <v>174</v>
+      </c>
+      <c r="D86" s="49" t="n">
+        <v>174</v>
+      </c>
+      <c r="E86" s="49" t="n"/>
+      <c r="F86" s="49" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B87" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
+      <c r="C87" s="49" t="n">
+        <v>176</v>
+      </c>
+      <c r="D87" s="49" t="n">
+        <v>176</v>
+      </c>
+      <c r="E87" s="49" t="n"/>
+      <c r="F87" s="49" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B88" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
+      <c r="C88" s="49" t="n">
+        <v>178</v>
+      </c>
+      <c r="D88" s="49" t="n">
+        <v>178</v>
+      </c>
+      <c r="E88" s="49" t="n"/>
+      <c r="F88" s="49" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B89" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
+      <c r="C89" s="49" t="n">
+        <v>180</v>
+      </c>
+      <c r="D89" s="49" t="n">
+        <v>180</v>
+      </c>
+      <c r="E89" s="49" t="n"/>
+      <c r="F89" s="49" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B90" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
+      <c r="C90" s="49" t="n">
+        <v>182</v>
+      </c>
+      <c r="D90" s="49" t="n">
+        <v>182</v>
+      </c>
+      <c r="E90" s="49" t="n"/>
+      <c r="F90" s="49" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B91" s="49" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
+      <c r="C91" s="49" t="n">
+        <v>184</v>
+      </c>
+      <c r="D91" s="49" t="n">
+        <v>184</v>
+      </c>
+      <c r="E91" s="49" t="n"/>
+      <c r="F91" s="49" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B92" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
+      <c r="C92" s="49" t="n">
+        <v>186</v>
+      </c>
+      <c r="D92" s="49" t="n">
+        <v>186</v>
+      </c>
+      <c r="E92" s="49" t="n"/>
+      <c r="F92" s="49" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B93" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
+      <c r="C93" s="49" t="n">
+        <v>188</v>
+      </c>
+      <c r="D93" s="49" t="n">
+        <v>188</v>
+      </c>
+      <c r="E93" s="49" t="n"/>
+      <c r="F93" s="49" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B94" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
+      <c r="C94" s="49" t="n">
+        <v>190</v>
+      </c>
+      <c r="D94" s="49" t="n">
+        <v>190</v>
+      </c>
+      <c r="E94" s="49" t="n"/>
+      <c r="F94" s="49" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B95" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
+      <c r="C95" s="49" t="n">
+        <v>192</v>
+      </c>
+      <c r="D95" s="49" t="n">
+        <v>192</v>
+      </c>
+      <c r="E95" s="49" t="n"/>
+      <c r="F95" s="49" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
+      <c r="C96" s="49" t="n">
+        <v>194</v>
+      </c>
+      <c r="D96" s="49" t="n">
+        <v>194</v>
+      </c>
+      <c r="E96" s="49" t="n"/>
+      <c r="F96" s="49" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
+      <c r="C97" s="49" t="n">
+        <v>196</v>
+      </c>
+      <c r="D97" s="49" t="n">
+        <v>196</v>
+      </c>
+      <c r="E97" s="49" t="n"/>
+      <c r="F97" s="49" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B98" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
+      <c r="C98" s="49" t="n">
+        <v>198</v>
+      </c>
+      <c r="D98" s="49" t="n">
+        <v>198</v>
+      </c>
+      <c r="E98" s="49" t="n"/>
+      <c r="F98" s="49" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B99" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
+      <c r="C99" s="49" t="n">
+        <v>200</v>
+      </c>
+      <c r="D99" s="49" t="n">
+        <v>200</v>
+      </c>
+      <c r="E99" s="49" t="n"/>
+      <c r="F99" s="49" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B100" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
+      <c r="C100" s="49" t="n">
+        <v>202</v>
+      </c>
+      <c r="D100" s="49" t="n">
+        <v>202</v>
+      </c>
+      <c r="E100" s="49" t="n"/>
+      <c r="F100" s="49" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B101" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
+      <c r="C101" s="49" t="n">
+        <v>204</v>
+      </c>
+      <c r="D101" s="49" t="n">
+        <v>204</v>
+      </c>
+      <c r="E101" s="49" t="n"/>
+      <c r="F101" s="49" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B102" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
+      <c r="C102" s="49" t="n">
+        <v>206</v>
+      </c>
+      <c r="D102" s="49" t="n">
+        <v>206</v>
+      </c>
+      <c r="E102" s="49" t="n"/>
+      <c r="F102" s="49" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B103" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
+      <c r="C103" s="49" t="n">
+        <v>208</v>
+      </c>
+      <c r="D103" s="49" t="n">
+        <v>208</v>
+      </c>
+      <c r="E103" s="49" t="n"/>
+      <c r="F103" s="49" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B104" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
+      <c r="C104" s="49" t="n">
+        <v>210</v>
+      </c>
+      <c r="D104" s="49" t="n">
+        <v>210</v>
+      </c>
+      <c r="E104" s="49" t="n"/>
+      <c r="F104" s="49" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B105" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
+      <c r="C105" s="49" t="n">
+        <v>212</v>
+      </c>
+      <c r="D105" s="49" t="n">
+        <v>212</v>
+      </c>
+      <c r="E105" s="49" t="n"/>
+      <c r="F105" s="49" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B106" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
+      <c r="C106" s="49" t="n">
+        <v>214</v>
+      </c>
+      <c r="D106" s="49" t="n">
+        <v>214</v>
+      </c>
+      <c r="E106" s="49" t="n"/>
+      <c r="F106" s="49" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B107" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
+      <c r="C107" s="49" t="n">
+        <v>216</v>
+      </c>
+      <c r="D107" s="49" t="n">
+        <v>216</v>
+      </c>
+      <c r="E107" s="49" t="n"/>
+      <c r="F107" s="49" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B108" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
+      <c r="C108" s="49" t="n">
+        <v>218</v>
+      </c>
+      <c r="D108" s="49" t="n">
+        <v>218</v>
+      </c>
+      <c r="E108" s="49" t="n"/>
+      <c r="F108" s="49" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B109" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
+      <c r="C109" s="49" t="n">
+        <v>220</v>
+      </c>
+      <c r="D109" s="49" t="n">
+        <v>220</v>
+      </c>
+      <c r="E109" s="49" t="n"/>
+      <c r="F109" s="49" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B110" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
+      <c r="C110" s="49" t="n">
+        <v>222</v>
+      </c>
+      <c r="D110" s="49" t="n">
+        <v>222</v>
+      </c>
+      <c r="E110" s="49" t="n"/>
+      <c r="F110" s="49" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B111" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
+      <c r="C111" s="49" t="n">
+        <v>224</v>
+      </c>
+      <c r="D111" s="49" t="n">
+        <v>224</v>
+      </c>
+      <c r="E111" s="49" t="n"/>
+      <c r="F111" s="49" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B112" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
+      <c r="C112" s="49" t="n">
+        <v>226</v>
+      </c>
+      <c r="D112" s="49" t="n">
+        <v>226</v>
+      </c>
+      <c r="E112" s="49" t="n"/>
+      <c r="F112" s="49" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B113" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
+      <c r="C113" s="49" t="n">
+        <v>228</v>
+      </c>
+      <c r="D113" s="49" t="n">
+        <v>228</v>
+      </c>
+      <c r="E113" s="49" t="n"/>
+      <c r="F113" s="49" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B114" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
+      <c r="C114" s="49" t="n">
+        <v>230</v>
+      </c>
+      <c r="D114" s="49" t="n">
+        <v>230</v>
+      </c>
+      <c r="E114" s="49" t="n"/>
+      <c r="F114" s="49" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B115" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
+      <c r="C115" s="49" t="n">
+        <v>232</v>
+      </c>
+      <c r="D115" s="49" t="n">
+        <v>232</v>
+      </c>
+      <c r="E115" s="49" t="n"/>
+      <c r="F115" s="49" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B116" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
+      <c r="C116" s="49" t="n">
+        <v>234</v>
+      </c>
+      <c r="D116" s="49" t="n">
+        <v>234</v>
+      </c>
+      <c r="E116" s="49" t="n"/>
+      <c r="F116" s="49" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B117" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
+      <c r="C117" s="49" t="n">
+        <v>236</v>
+      </c>
+      <c r="D117" s="49" t="n">
+        <v>236</v>
+      </c>
+      <c r="E117" s="49" t="n"/>
+      <c r="F117" s="49" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B118" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
+      <c r="C118" s="49" t="n">
+        <v>238</v>
+      </c>
+      <c r="D118" s="49" t="n">
+        <v>238</v>
+      </c>
+      <c r="E118" s="49" t="n"/>
+      <c r="F118" s="49" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B119" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
+      <c r="C119" s="49" t="n">
+        <v>240</v>
+      </c>
+      <c r="D119" s="49" t="n">
+        <v>240</v>
+      </c>
+      <c r="E119" s="49" t="n"/>
+      <c r="F119" s="49" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B120" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
+      <c r="C120" s="49" t="n">
+        <v>242</v>
+      </c>
+      <c r="D120" s="49" t="n">
+        <v>242</v>
+      </c>
+      <c r="E120" s="49" t="n"/>
+      <c r="F120" s="49" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B121" s="49" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
+      <c r="C121" s="49" t="n">
+        <v>244</v>
+      </c>
+      <c r="D121" s="49" t="n">
+        <v>244</v>
+      </c>
+      <c r="E121" s="49" t="n"/>
+      <c r="F121" s="49" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B122" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
+      <c r="C122" s="49" t="n">
+        <v>246</v>
+      </c>
+      <c r="D122" s="49" t="n">
+        <v>246</v>
+      </c>
+      <c r="E122" s="49" t="n"/>
+      <c r="F122" s="49" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B123" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
+      <c r="C123" s="49" t="n">
+        <v>248</v>
+      </c>
+      <c r="D123" s="49" t="n">
+        <v>248</v>
+      </c>
+      <c r="E123" s="49" t="n"/>
+      <c r="F123" s="49" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B124" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
+      <c r="C124" s="49" t="n">
+        <v>250</v>
+      </c>
+      <c r="D124" s="49" t="n">
+        <v>250</v>
+      </c>
+      <c r="E124" s="49" t="n"/>
+      <c r="F124" s="49" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B125" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
+      <c r="C125" s="49" t="n">
+        <v>252</v>
+      </c>
+      <c r="D125" s="49" t="n">
+        <v>252</v>
+      </c>
+      <c r="E125" s="49" t="n"/>
+      <c r="F125" s="49" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B126" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
+      <c r="C126" s="49" t="n">
+        <v>254</v>
+      </c>
+      <c r="D126" s="49" t="n">
+        <v>254</v>
+      </c>
+      <c r="E126" s="49" t="n"/>
+      <c r="F126" s="49" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B127" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
+      <c r="C127" s="49" t="n">
+        <v>256</v>
+      </c>
+      <c r="D127" s="49" t="n">
+        <v>257</v>
+      </c>
+      <c r="E127" s="49" t="n"/>
+      <c r="F127" s="49" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B128" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
+      <c r="C128" s="49" t="n">
+        <v>259</v>
+      </c>
+      <c r="D128" s="49" t="n">
+        <v>259</v>
+      </c>
+      <c r="E128" s="49" t="n"/>
+      <c r="F128" s="49" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B129" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
+      <c r="C129" s="49" t="n">
+        <v>261</v>
+      </c>
+      <c r="D129" s="49" t="n">
+        <v>261</v>
+      </c>
+      <c r="E129" s="49" t="n"/>
+      <c r="F129" s="49" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B130" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
+      <c r="C130" s="49" t="n">
+        <v>263</v>
+      </c>
+      <c r="D130" s="49" t="n">
+        <v>263</v>
+      </c>
+      <c r="E130" s="49" t="n"/>
+      <c r="F130" s="49" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B131" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
+      <c r="C131" s="49" t="n">
+        <v>265</v>
+      </c>
+      <c r="D131" s="49" t="n">
+        <v>265</v>
+      </c>
+      <c r="E131" s="49" t="n"/>
+      <c r="F131" s="49" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B132" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
+      <c r="C132" s="49" t="n">
+        <v>267</v>
+      </c>
+      <c r="D132" s="49" t="n">
+        <v>267</v>
+      </c>
+      <c r="E132" s="49" t="n"/>
+      <c r="F132" s="49" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B133" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
+      <c r="C133" s="49" t="n">
+        <v>269</v>
+      </c>
+      <c r="D133" s="49" t="n">
+        <v>269</v>
+      </c>
+      <c r="E133" s="49" t="n"/>
+      <c r="F133" s="49" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B134" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
+      <c r="C134" s="49" t="n">
+        <v>271</v>
+      </c>
+      <c r="D134" s="49" t="n">
+        <v>271</v>
+      </c>
+      <c r="E134" s="49" t="n"/>
+      <c r="F134" s="49" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B135" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
+      <c r="C135" s="49" t="n">
+        <v>273</v>
+      </c>
+      <c r="D135" s="49" t="n">
+        <v>273</v>
+      </c>
+      <c r="E135" s="49" t="n"/>
+      <c r="F135" s="49" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B136" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
+      <c r="C136" s="49" t="n">
+        <v>275</v>
+      </c>
+      <c r="D136" s="49" t="n">
+        <v>275</v>
+      </c>
+      <c r="E136" s="49" t="n"/>
+      <c r="F136" s="49" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B137" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
+      <c r="C137" s="49" t="n">
+        <v>277</v>
+      </c>
+      <c r="D137" s="49" t="n">
+        <v>277</v>
+      </c>
+      <c r="E137" s="49" t="n"/>
+      <c r="F137" s="49" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B138" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
+      <c r="C138" s="49" t="n">
+        <v>279</v>
+      </c>
+      <c r="D138" s="49" t="n">
+        <v>279</v>
+      </c>
+      <c r="E138" s="49" t="n"/>
+      <c r="F138" s="49" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B139" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
+      <c r="C139" s="49" t="n">
+        <v>281</v>
+      </c>
+      <c r="D139" s="49" t="n">
+        <v>281</v>
+      </c>
+      <c r="E139" s="49" t="n"/>
+      <c r="F139" s="49" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B140" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
+      <c r="C140" s="49" t="n">
+        <v>283</v>
+      </c>
+      <c r="D140" s="49" t="n">
+        <v>283</v>
+      </c>
+      <c r="E140" s="49" t="n"/>
+      <c r="F140" s="49" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B141" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
+      <c r="C141" s="49" t="n">
+        <v>285</v>
+      </c>
+      <c r="D141" s="49" t="n">
+        <v>285</v>
+      </c>
+      <c r="E141" s="49" t="n"/>
+      <c r="F141" s="49" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B142" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
+      <c r="C142" s="49" t="n">
+        <v>287</v>
+      </c>
+      <c r="D142" s="49" t="n">
+        <v>287</v>
+      </c>
+      <c r="E142" s="49" t="n"/>
+      <c r="F142" s="49" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B143" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
+      <c r="C143" s="49" t="n">
+        <v>289</v>
+      </c>
+      <c r="D143" s="49" t="n">
+        <v>289</v>
+      </c>
+      <c r="E143" s="49" t="n"/>
+      <c r="F143" s="49" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B144" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
+      <c r="C144" s="49" t="n">
+        <v>291</v>
+      </c>
+      <c r="D144" s="49" t="n">
+        <v>291</v>
+      </c>
+      <c r="E144" s="49" t="n"/>
+      <c r="F144" s="49" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B145" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
+      <c r="C145" s="49" t="n">
+        <v>293</v>
+      </c>
+      <c r="D145" s="49" t="n">
+        <v>293</v>
+      </c>
+      <c r="E145" s="49" t="n"/>
+      <c r="F145" s="49" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B146" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
+      <c r="C146" s="49" t="n">
+        <v>295</v>
+      </c>
+      <c r="D146" s="49" t="n">
+        <v>295</v>
+      </c>
+      <c r="E146" s="49" t="n"/>
+      <c r="F146" s="49" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B147" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
+      <c r="C147" s="49" t="n">
+        <v>297</v>
+      </c>
+      <c r="D147" s="49" t="n">
+        <v>297</v>
+      </c>
+      <c r="E147" s="49" t="n"/>
+      <c r="F147" s="49" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B148" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
+      <c r="C148" s="49" t="n">
+        <v>299</v>
+      </c>
+      <c r="D148" s="49" t="n">
+        <v>299</v>
+      </c>
+      <c r="E148" s="49" t="n"/>
+      <c r="F148" s="49" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B149" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
+      <c r="C149" s="49" t="n">
+        <v>301</v>
+      </c>
+      <c r="D149" s="49" t="n">
+        <v>301</v>
+      </c>
+      <c r="E149" s="49" t="n"/>
+      <c r="F149" s="49" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B150" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
+      <c r="C150" s="49" t="n">
+        <v>303</v>
+      </c>
+      <c r="D150" s="49" t="n">
+        <v>303</v>
+      </c>
+      <c r="E150" s="49" t="n"/>
+      <c r="F150" s="49" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B151" s="49" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
+      <c r="C151" s="49" t="n">
+        <v>305</v>
+      </c>
+      <c r="D151" s="49" t="n">
+        <v>305</v>
+      </c>
+      <c r="E151" s="49" t="n"/>
+      <c r="F151" s="49" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B152" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
+      <c r="C152" s="49" t="n">
+        <v>307</v>
+      </c>
+      <c r="D152" s="49" t="n">
+        <v>307</v>
+      </c>
+      <c r="E152" s="49" t="n"/>
+      <c r="F152" s="49" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B153" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
+      <c r="C153" s="49" t="n">
+        <v>309</v>
+      </c>
+      <c r="D153" s="49" t="n">
+        <v>309</v>
+      </c>
+      <c r="E153" s="49" t="n"/>
+      <c r="F153" s="49" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B154" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
+      <c r="C154" s="49" t="n">
+        <v>311</v>
+      </c>
+      <c r="D154" s="49" t="n">
+        <v>311</v>
+      </c>
+      <c r="E154" s="49" t="n"/>
+      <c r="F154" s="49" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B155" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
+      <c r="C155" s="49" t="n">
+        <v>313</v>
+      </c>
+      <c r="D155" s="49" t="n">
+        <v>313</v>
+      </c>
+      <c r="E155" s="49" t="n"/>
+      <c r="F155" s="49" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B156" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
+      <c r="C156" s="49" t="n">
+        <v>315</v>
+      </c>
+      <c r="D156" s="49" t="n">
+        <v>316</v>
+      </c>
+      <c r="E156" s="49" t="n"/>
+      <c r="F156" s="49" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B157" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
+      <c r="C157" s="49" t="n">
+        <v>318</v>
+      </c>
+      <c r="D157" s="49" t="n">
+        <v>318</v>
+      </c>
+      <c r="E157" s="49" t="n"/>
+      <c r="F157" s="49" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B158" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
+      <c r="C158" s="49" t="n">
+        <v>320</v>
+      </c>
+      <c r="D158" s="49" t="n">
+        <v>320</v>
+      </c>
+      <c r="E158" s="49" t="n"/>
+      <c r="F158" s="49" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B159" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
+      <c r="C159" s="49" t="n">
+        <v>322</v>
+      </c>
+      <c r="D159" s="49" t="n">
+        <v>322</v>
+      </c>
+      <c r="E159" s="49" t="n"/>
+      <c r="F159" s="49" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B160" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
+      <c r="C160" s="49" t="n">
+        <v>324</v>
+      </c>
+      <c r="D160" s="49" t="n">
+        <v>324</v>
+      </c>
+      <c r="E160" s="49" t="n"/>
+      <c r="F160" s="49" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B161" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
+      <c r="C161" s="49" t="n">
+        <v>326</v>
+      </c>
+      <c r="D161" s="49" t="n">
+        <v>326</v>
+      </c>
+      <c r="E161" s="49" t="n"/>
+      <c r="F161" s="49" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B162" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
+      <c r="C162" s="49" t="n">
+        <v>328</v>
+      </c>
+      <c r="D162" s="49" t="n">
+        <v>328</v>
+      </c>
+      <c r="E162" s="49" t="n"/>
+      <c r="F162" s="49" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B163" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
+      <c r="C163" s="49" t="n">
+        <v>330</v>
+      </c>
+      <c r="D163" s="49" t="n">
+        <v>330</v>
+      </c>
+      <c r="E163" s="49" t="n"/>
+      <c r="F163" s="49" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B164" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
+      <c r="C164" s="49" t="n">
+        <v>332</v>
+      </c>
+      <c r="D164" s="49" t="n">
+        <v>332</v>
+      </c>
+      <c r="E164" s="49" t="n"/>
+      <c r="F164" s="49" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B165" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
+      <c r="C165" s="49" t="n">
+        <v>334</v>
+      </c>
+      <c r="D165" s="49" t="n">
+        <v>334</v>
+      </c>
+      <c r="E165" s="49" t="n"/>
+      <c r="F165" s="49" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B166" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
+      <c r="C166" s="49" t="n">
+        <v>336</v>
+      </c>
+      <c r="D166" s="49" t="n">
+        <v>336</v>
+      </c>
+      <c r="E166" s="49" t="n"/>
+      <c r="F166" s="49" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B167" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
+      <c r="C167" s="49" t="n">
+        <v>338</v>
+      </c>
+      <c r="D167" s="49" t="n">
+        <v>338</v>
+      </c>
+      <c r="E167" s="49" t="n"/>
+      <c r="F167" s="49" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B168" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
+      <c r="C168" s="49" t="n">
+        <v>340</v>
+      </c>
+      <c r="D168" s="49" t="n">
+        <v>340</v>
+      </c>
+      <c r="E168" s="49" t="n"/>
+      <c r="F168" s="49" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B169" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
+      <c r="C169" s="49" t="n">
+        <v>342</v>
+      </c>
+      <c r="D169" s="49" t="n">
+        <v>342</v>
+      </c>
+      <c r="E169" s="49" t="n"/>
+      <c r="F169" s="49" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B170" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
+      <c r="C170" s="49" t="n">
+        <v>344</v>
+      </c>
+      <c r="D170" s="49" t="n">
+        <v>344</v>
+      </c>
+      <c r="E170" s="49" t="n"/>
+      <c r="F170" s="49" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B171" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
+      <c r="C171" s="49" t="n">
+        <v>346</v>
+      </c>
+      <c r="D171" s="49" t="n">
+        <v>346</v>
+      </c>
+      <c r="E171" s="49" t="n"/>
+      <c r="F171" s="49" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B172" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
+      <c r="C172" s="49" t="n">
+        <v>348</v>
+      </c>
+      <c r="D172" s="49" t="n">
+        <v>348</v>
+      </c>
+      <c r="E172" s="49" t="n"/>
+      <c r="F172" s="49" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B173" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
+      <c r="C173" s="49" t="n">
+        <v>350</v>
+      </c>
+      <c r="D173" s="49" t="n">
+        <v>350</v>
+      </c>
+      <c r="E173" s="49" t="n"/>
+      <c r="F173" s="49" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B174" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
+      <c r="C174" s="49" t="n">
+        <v>352</v>
+      </c>
+      <c r="D174" s="49" t="n">
+        <v>352</v>
+      </c>
+      <c r="E174" s="49" t="n"/>
+      <c r="F174" s="49" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B175" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
+      <c r="C175" s="49" t="n">
+        <v>354</v>
+      </c>
+      <c r="D175" s="49" t="n">
+        <v>354</v>
+      </c>
+      <c r="E175" s="49" t="n"/>
+      <c r="F175" s="49" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B176" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
+      <c r="C176" s="49" t="n">
+        <v>356</v>
+      </c>
+      <c r="D176" s="49" t="n">
+        <v>356</v>
+      </c>
+      <c r="E176" s="49" t="n"/>
+      <c r="F176" s="49" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B177" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
+      <c r="C177" s="49" t="n">
+        <v>358</v>
+      </c>
+      <c r="D177" s="49" t="n">
+        <v>358</v>
+      </c>
+      <c r="E177" s="49" t="n"/>
+      <c r="F177" s="49" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B178" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
+      <c r="C178" s="49" t="n">
+        <v>360</v>
+      </c>
+      <c r="D178" s="49" t="n">
+        <v>360</v>
+      </c>
+      <c r="E178" s="49" t="n"/>
+      <c r="F178" s="49" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B179" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
+      <c r="C179" s="49" t="n">
+        <v>362</v>
+      </c>
+      <c r="D179" s="49" t="n">
+        <v>362</v>
+      </c>
+      <c r="E179" s="49" t="n"/>
+      <c r="F179" s="49" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B180" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
+      <c r="C180" s="49" t="n">
+        <v>364</v>
+      </c>
+      <c r="D180" s="49" t="n">
+        <v>364</v>
+      </c>
+      <c r="E180" s="49" t="n"/>
+      <c r="F180" s="49" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B181" s="49" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
+      <c r="C181" s="49" t="n">
+        <v>366</v>
+      </c>
+      <c r="D181" s="49" t="n">
+        <v>366</v>
+      </c>
+      <c r="E181" s="49" t="n"/>
+      <c r="F181" s="49" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B182" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
+      <c r="C182" s="49" t="n">
+        <v>368</v>
+      </c>
+      <c r="D182" s="49" t="n">
+        <v>368</v>
+      </c>
+      <c r="E182" s="49" t="n"/>
+      <c r="F182" s="49" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B183" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
+      <c r="C183" s="49" t="n">
+        <v>370</v>
+      </c>
+      <c r="D183" s="49" t="n">
+        <v>370</v>
+      </c>
+      <c r="E183" s="49" t="n"/>
+      <c r="F183" s="49" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B184" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
+      <c r="C184" s="49" t="n">
+        <v>372</v>
+      </c>
+      <c r="D184" s="49" t="n">
+        <v>372</v>
+      </c>
+      <c r="E184" s="49" t="n"/>
+      <c r="F184" s="49" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B185" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
+      <c r="C185" s="49" t="n">
+        <v>374</v>
+      </c>
+      <c r="D185" s="49" t="n">
+        <v>374</v>
+      </c>
+      <c r="E185" s="49" t="n"/>
+      <c r="F185" s="49" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B186" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
+      <c r="C186" s="49" t="n">
+        <v>376</v>
+      </c>
+      <c r="D186" s="49" t="n">
+        <v>376</v>
+      </c>
+      <c r="E186" s="49" t="n"/>
+      <c r="F186" s="49" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B187" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
+      <c r="C187" s="49" t="n">
+        <v>378</v>
+      </c>
+      <c r="D187" s="49" t="n">
+        <v>378</v>
+      </c>
+      <c r="E187" s="49" t="n"/>
+      <c r="F187" s="49" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B188" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
+      <c r="C188" s="49" t="n">
+        <v>380</v>
+      </c>
+      <c r="D188" s="49" t="n">
+        <v>380</v>
+      </c>
+      <c r="E188" s="49" t="n"/>
+      <c r="F188" s="49" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B189" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
+      <c r="C189" s="49" t="n">
+        <v>382</v>
+      </c>
+      <c r="D189" s="49" t="n">
+        <v>382</v>
+      </c>
+      <c r="E189" s="49" t="n"/>
+      <c r="F189" s="49" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B190" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
+      <c r="C190" s="49" t="n">
+        <v>384</v>
+      </c>
+      <c r="D190" s="49" t="n">
+        <v>384</v>
+      </c>
+      <c r="E190" s="49" t="n"/>
+      <c r="F190" s="49" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B191" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
+      <c r="C191" s="49" t="n">
+        <v>386</v>
+      </c>
+      <c r="D191" s="49" t="n">
+        <v>386</v>
+      </c>
+      <c r="E191" s="49" t="n"/>
+      <c r="F191" s="49" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B192" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
+      <c r="C192" s="49" t="n">
+        <v>388</v>
+      </c>
+      <c r="D192" s="49" t="n">
+        <v>388</v>
+      </c>
+      <c r="E192" s="49" t="n"/>
+      <c r="F192" s="49" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B193" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
+      <c r="C193" s="49" t="n">
+        <v>390</v>
+      </c>
+      <c r="D193" s="49" t="n">
+        <v>390</v>
+      </c>
+      <c r="E193" s="49" t="n"/>
+      <c r="F193" s="49" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B194" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
+      <c r="C194" s="49" t="n">
+        <v>392</v>
+      </c>
+      <c r="D194" s="49" t="n">
+        <v>392</v>
+      </c>
+      <c r="E194" s="49" t="n"/>
+      <c r="F194" s="49" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B195" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
+      <c r="C195" s="49" t="n">
+        <v>394</v>
+      </c>
+      <c r="D195" s="49" t="n">
+        <v>394</v>
+      </c>
+      <c r="E195" s="49" t="n"/>
+      <c r="F195" s="49" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B196" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
+      <c r="C196" s="49" t="n">
+        <v>396</v>
+      </c>
+      <c r="D196" s="49" t="n">
+        <v>396</v>
+      </c>
+      <c r="E196" s="49" t="n"/>
+      <c r="F196" s="49" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B197" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
+      <c r="C197" s="49" t="n">
+        <v>398</v>
+      </c>
+      <c r="D197" s="49" t="n">
+        <v>398</v>
+      </c>
+      <c r="E197" s="49" t="n"/>
+      <c r="F197" s="49" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B198" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
+      <c r="C198" s="49" t="n">
+        <v>400</v>
+      </c>
+      <c r="D198" s="49" t="n">
+        <v>400</v>
+      </c>
+      <c r="E198" s="49" t="n"/>
+      <c r="F198" s="49" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B199" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
+      <c r="C199" s="49" t="n">
+        <v>402</v>
+      </c>
+      <c r="D199" s="49" t="n">
+        <v>402</v>
+      </c>
+      <c r="E199" s="49" t="n"/>
+      <c r="F199" s="49" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B200" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
+      <c r="C200" s="49" t="n">
+        <v>404</v>
+      </c>
+      <c r="D200" s="49" t="n">
+        <v>404</v>
+      </c>
+      <c r="E200" s="49" t="n"/>
+      <c r="F200" s="49" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B201" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
+      <c r="C201" s="49" t="n">
+        <v>406</v>
+      </c>
+      <c r="D201" s="49" t="n">
+        <v>406</v>
+      </c>
+      <c r="E201" s="49" t="n"/>
+      <c r="F201" s="49" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B202" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
+      <c r="C202" s="49" t="n">
+        <v>408</v>
+      </c>
+      <c r="D202" s="49" t="n">
+        <v>408</v>
+      </c>
+      <c r="E202" s="49" t="n"/>
+      <c r="F202" s="49" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B203" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
+      <c r="C203" s="49" t="n">
+        <v>410</v>
+      </c>
+      <c r="D203" s="49" t="n">
+        <v>410</v>
+      </c>
+      <c r="E203" s="49" t="n"/>
+      <c r="F203" s="49" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B204" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
+      <c r="C204" s="49" t="n">
+        <v>412</v>
+      </c>
+      <c r="D204" s="49" t="n">
+        <v>412</v>
+      </c>
+      <c r="E204" s="49" t="n"/>
+      <c r="F204" s="49" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B205" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
+      <c r="C205" s="49" t="n">
+        <v>414</v>
+      </c>
+      <c r="D205" s="49" t="n">
+        <v>414</v>
+      </c>
+      <c r="E205" s="49" t="n"/>
+      <c r="F205" s="49" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B206" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
+      <c r="C206" s="49" t="n">
+        <v>416</v>
+      </c>
+      <c r="D206" s="49" t="n">
+        <v>416</v>
+      </c>
+      <c r="E206" s="49" t="n"/>
+      <c r="F206" s="49" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B207" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
+      <c r="C207" s="49" t="n">
+        <v>418</v>
+      </c>
+      <c r="D207" s="49" t="n">
+        <v>418</v>
+      </c>
+      <c r="E207" s="49" t="n"/>
+      <c r="F207" s="49" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B208" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
+      <c r="C208" s="49" t="n">
+        <v>420</v>
+      </c>
+      <c r="D208" s="49" t="n">
+        <v>420</v>
+      </c>
+      <c r="E208" s="49" t="n"/>
+      <c r="F208" s="49" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B209" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
+      <c r="C209" s="49" t="n">
+        <v>422</v>
+      </c>
+      <c r="D209" s="49" t="n">
+        <v>422</v>
+      </c>
+      <c r="E209" s="49" t="n"/>
+      <c r="F209" s="49" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B210" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
+      <c r="C210" s="49" t="n">
+        <v>424</v>
+      </c>
+      <c r="D210" s="49" t="n">
+        <v>424</v>
+      </c>
+      <c r="E210" s="49" t="n"/>
+      <c r="F210" s="49" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B211" s="49" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
+      <c r="C211" s="49" t="n">
+        <v>426</v>
+      </c>
+      <c r="D211" s="49" t="n">
+        <v>426</v>
+      </c>
+      <c r="E211" s="49" t="n"/>
+      <c r="F211" s="49" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B212" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
+      <c r="C212" s="49" t="n">
+        <v>428</v>
+      </c>
+      <c r="D212" s="49" t="n">
+        <v>428</v>
+      </c>
+      <c r="E212" s="49" t="n"/>
+      <c r="F212" s="49" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B213" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
+      <c r="C213" s="49" t="n">
+        <v>430</v>
+      </c>
+      <c r="D213" s="49" t="n">
+        <v>430</v>
+      </c>
+      <c r="E213" s="49" t="n"/>
+      <c r="F213" s="49" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B214" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
+      <c r="C214" s="49" t="n">
+        <v>432</v>
+      </c>
+      <c r="D214" s="49" t="n">
+        <v>432</v>
+      </c>
+      <c r="E214" s="49" t="n"/>
+      <c r="F214" s="49" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B215" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
+      <c r="C215" s="49" t="n">
+        <v>434</v>
+      </c>
+      <c r="D215" s="49" t="n">
+        <v>434</v>
+      </c>
+      <c r="E215" s="49" t="n"/>
+      <c r="F215" s="49" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B216" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
+      <c r="C216" s="49" t="n">
+        <v>436</v>
+      </c>
+      <c r="D216" s="49" t="n">
+        <v>436</v>
+      </c>
+      <c r="E216" s="49" t="n"/>
+      <c r="F216" s="49" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B217" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
+      <c r="C217" s="49" t="n">
+        <v>438</v>
+      </c>
+      <c r="D217" s="49" t="n">
+        <v>438</v>
+      </c>
+      <c r="E217" s="49" t="n"/>
+      <c r="F217" s="49" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B218" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
+      <c r="C218" s="49" t="n">
+        <v>440</v>
+      </c>
+      <c r="D218" s="49" t="n">
+        <v>440</v>
+      </c>
+      <c r="E218" s="49" t="n"/>
+      <c r="F218" s="49" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B219" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
+      <c r="C219" s="49" t="n">
+        <v>442</v>
+      </c>
+      <c r="D219" s="49" t="n">
+        <v>442</v>
+      </c>
+      <c r="E219" s="49" t="n"/>
+      <c r="F219" s="49" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B220" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
+      <c r="C220" s="49" t="n">
+        <v>444</v>
+      </c>
+      <c r="D220" s="49" t="n">
+        <v>444</v>
+      </c>
+      <c r="E220" s="49" t="n"/>
+      <c r="F220" s="49" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B221" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
+      <c r="C221" s="49" t="n">
+        <v>446</v>
+      </c>
+      <c r="D221" s="49" t="n">
+        <v>446</v>
+      </c>
+      <c r="E221" s="49" t="n"/>
+      <c r="F221" s="49" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B222" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
+      <c r="C222" s="49" t="n">
+        <v>448</v>
+      </c>
+      <c r="D222" s="49" t="n">
+        <v>448</v>
+      </c>
+      <c r="E222" s="49" t="n"/>
+      <c r="F222" s="49" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B223" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
+      <c r="C223" s="49" t="n">
+        <v>450</v>
+      </c>
+      <c r="D223" s="49" t="n">
+        <v>450</v>
+      </c>
+      <c r="E223" s="49" t="n"/>
+      <c r="F223" s="49" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B224" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
+      <c r="C224" s="49" t="n">
+        <v>452</v>
+      </c>
+      <c r="D224" s="49" t="n">
+        <v>452</v>
+      </c>
+      <c r="E224" s="49" t="n"/>
+      <c r="F224" s="49" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B225" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
+      <c r="C225" s="49" t="n">
+        <v>454</v>
+      </c>
+      <c r="D225" s="49" t="n">
+        <v>454</v>
+      </c>
+      <c r="E225" s="49" t="n"/>
+      <c r="F225" s="49" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B226" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="C226" s="49" t="n">
+        <v>456</v>
+      </c>
+      <c r="D226" s="49" t="n">
+        <v>456</v>
+      </c>
+      <c r="E226" s="49" t="n"/>
+      <c r="F226" s="49" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B227" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="C227" s="49" t="n">
+        <v>458</v>
+      </c>
+      <c r="D227" s="49" t="n">
+        <v>458</v>
+      </c>
+      <c r="E227" s="49" t="n"/>
+      <c r="F227" s="49" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B228" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
+      <c r="C228" s="49" t="n">
+        <v>460</v>
+      </c>
+      <c r="D228" s="49" t="n">
+        <v>460</v>
+      </c>
+      <c r="E228" s="49" t="n"/>
+      <c r="F228" s="49" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B229" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
+      <c r="C229" s="49" t="n">
+        <v>462</v>
+      </c>
+      <c r="D229" s="49" t="n">
+        <v>462</v>
+      </c>
+      <c r="E229" s="49" t="n"/>
+      <c r="F229" s="49" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B230" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="C230" s="49" t="n">
+        <v>464</v>
+      </c>
+      <c r="D230" s="49" t="n">
+        <v>464</v>
+      </c>
+      <c r="E230" s="49" t="n"/>
+      <c r="F230" s="49" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B231" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
+      <c r="C231" s="49" t="n">
+        <v>466</v>
+      </c>
+      <c r="D231" s="49" t="n">
+        <v>466</v>
+      </c>
+      <c r="E231" s="49" t="n"/>
+      <c r="F231" s="49" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B232" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
+      <c r="C232" s="49" t="n">
+        <v>468</v>
+      </c>
+      <c r="D232" s="49" t="n">
+        <v>468</v>
+      </c>
+      <c r="E232" s="49" t="n"/>
+      <c r="F232" s="49" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B233" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="C233" s="49" t="n">
+        <v>470</v>
+      </c>
+      <c r="D233" s="49" t="n">
+        <v>470</v>
+      </c>
+      <c r="E233" s="49" t="n"/>
+      <c r="F233" s="49" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B234" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
+      <c r="C234" s="49" t="n">
+        <v>472</v>
+      </c>
+      <c r="D234" s="49" t="n">
+        <v>472</v>
+      </c>
+      <c r="E234" s="49" t="n"/>
+      <c r="F234" s="49" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B235" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
+      <c r="C235" s="49" t="n">
+        <v>474</v>
+      </c>
+      <c r="D235" s="49" t="n">
+        <v>474</v>
+      </c>
+      <c r="E235" s="49" t="n"/>
+      <c r="F235" s="49" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B236" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
+      <c r="C236" s="49" t="n">
+        <v>476</v>
+      </c>
+      <c r="D236" s="49" t="n">
+        <v>476</v>
+      </c>
+      <c r="E236" s="49" t="n"/>
+      <c r="F236" s="49" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B237" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
+      <c r="C237" s="49" t="n">
+        <v>478</v>
+      </c>
+      <c r="D237" s="49" t="n">
+        <v>478</v>
+      </c>
+      <c r="E237" s="49" t="n"/>
+      <c r="F237" s="49" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="49" t="n">
         <v>27</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B238" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
+      <c r="C238" s="49" t="n">
+        <v>480</v>
+      </c>
+      <c r="D238" s="49" t="n">
+        <v>480</v>
+      </c>
+      <c r="E238" s="49" t="n"/>
+      <c r="F238" s="49" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="49" t="n">
         <v>28</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B239" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
+      <c r="C239" s="49" t="n">
+        <v>482</v>
+      </c>
+      <c r="D239" s="49" t="n">
+        <v>482</v>
+      </c>
+      <c r="E239" s="49" t="n"/>
+      <c r="F239" s="49" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B240" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
+      <c r="C240" s="49" t="n">
+        <v>484</v>
+      </c>
+      <c r="D240" s="49" t="n">
+        <v>484</v>
+      </c>
+      <c r="E240" s="49" t="n"/>
+      <c r="F240" s="49" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B241" s="49" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
+      <c r="C241" s="49" t="n">
+        <v>486</v>
+      </c>
+      <c r="D241" s="49" t="n">
+        <v>486</v>
+      </c>
+      <c r="E241" s="49" t="n"/>
+      <c r="F241" s="49" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="B242" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C242" s="49" t="n">
+        <v>488</v>
+      </c>
+      <c r="D242" s="49" t="n">
+        <v>488</v>
+      </c>
+      <c r="E242" s="49" t="n"/>
+      <c r="F242" s="49" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="B243" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C243" s="49" t="n">
+        <v>490</v>
+      </c>
+      <c r="D243" s="49" t="n">
+        <v>490</v>
+      </c>
+      <c r="E243" s="49" t="n"/>
+      <c r="F243" s="49" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="B244" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C244" s="49" t="n">
+        <v>492</v>
+      </c>
+      <c r="D244" s="49" t="n">
+        <v>492</v>
+      </c>
+      <c r="E244" s="49" t="n"/>
+      <c r="F244" s="49" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="B245" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C245" s="49" t="n">
+        <v>494</v>
+      </c>
+      <c r="D245" s="49" t="n">
+        <v>494</v>
+      </c>
+      <c r="E245" s="49" t="n"/>
+      <c r="F245" s="49" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="B246" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C246" s="49" t="n">
+        <v>496</v>
+      </c>
+      <c r="D246" s="49" t="n">
+        <v>496</v>
+      </c>
+      <c r="E246" s="49" t="n"/>
+      <c r="F246" s="49" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="B247" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C247" s="49" t="n">
+        <v>498</v>
+      </c>
+      <c r="D247" s="49" t="n">
+        <v>498</v>
+      </c>
+      <c r="E247" s="49" t="n"/>
+      <c r="F247" s="49" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="B248" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C248" s="49" t="n">
+        <v>500</v>
+      </c>
+      <c r="D248" s="49" t="n">
+        <v>500</v>
+      </c>
+      <c r="E248" s="49" t="n"/>
+      <c r="F248" s="49" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="B249" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C249" s="49" t="n">
+        <v>502</v>
+      </c>
+      <c r="D249" s="49" t="n">
+        <v>502</v>
+      </c>
+      <c r="E249" s="49" t="n"/>
+      <c r="F249" s="49" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="B250" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C250" s="49" t="n">
+        <v>504</v>
+      </c>
+      <c r="D250" s="49" t="n">
+        <v>504</v>
+      </c>
+      <c r="E250" s="49" t="n"/>
+      <c r="F250" s="49" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="B251" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C251" s="49" t="n">
+        <v>506</v>
+      </c>
+      <c r="D251" s="49" t="n">
+        <v>506</v>
+      </c>
+      <c r="E251" s="49" t="n"/>
+      <c r="F251" s="49" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="B252" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C252" s="49" t="n">
+        <v>508</v>
+      </c>
+      <c r="D252" s="49" t="n">
+        <v>508</v>
+      </c>
+      <c r="E252" s="49" t="n"/>
+      <c r="F252" s="49" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="B253" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C253" s="49" t="n">
+        <v>510</v>
+      </c>
+      <c r="D253" s="49" t="n">
+        <v>510</v>
+      </c>
+      <c r="E253" s="49" t="n"/>
+      <c r="F253" s="49" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="B254" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C254" s="49" t="n">
+        <v>512</v>
+      </c>
+      <c r="D254" s="49" t="n">
+        <v>512</v>
+      </c>
+      <c r="E254" s="49" t="n"/>
+      <c r="F254" s="49" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="B255" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C255" s="49" t="n">
+        <v>514</v>
+      </c>
+      <c r="D255" s="49" t="n">
+        <v>514</v>
+      </c>
+      <c r="E255" s="49" t="n"/>
+      <c r="F255" s="49" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B256" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C256" s="49" t="n">
+        <v>516</v>
+      </c>
+      <c r="D256" s="49" t="n">
+        <v>516</v>
+      </c>
+      <c r="E256" s="49" t="n"/>
+      <c r="F256" s="49" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B257" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C257" s="49" t="n">
+        <v>518</v>
+      </c>
+      <c r="D257" s="49" t="n">
+        <v>518</v>
+      </c>
+      <c r="E257" s="49" t="n"/>
+      <c r="F257" s="49" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B258" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C258" s="49" t="n">
+        <v>520</v>
+      </c>
+      <c r="D258" s="49" t="n">
+        <v>520</v>
+      </c>
+      <c r="E258" s="49" t="n"/>
+      <c r="F258" s="49" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B259" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C259" s="49" t="n">
+        <v>522</v>
+      </c>
+      <c r="D259" s="49" t="n">
+        <v>523</v>
+      </c>
+      <c r="E259" s="49" t="n"/>
+      <c r="F259" s="49" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="B260" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C260" s="49" t="n">
+        <v>525</v>
+      </c>
+      <c r="D260" s="49" t="n">
+        <v>525</v>
+      </c>
+      <c r="E260" s="49" t="n"/>
+      <c r="F260" s="49" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="B261" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C261" s="49" t="n">
+        <v>527</v>
+      </c>
+      <c r="D261" s="49" t="n">
+        <v>527</v>
+      </c>
+      <c r="E261" s="49" t="n"/>
+      <c r="F261" s="49" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B262" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C262" s="49" t="n">
+        <v>529</v>
+      </c>
+      <c r="D262" s="49" t="n">
+        <v>529</v>
+      </c>
+      <c r="E262" s="49" t="n"/>
+      <c r="F262" s="49" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B263" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C263" s="49" t="n">
+        <v>531</v>
+      </c>
+      <c r="D263" s="49" t="n">
+        <v>531</v>
+      </c>
+      <c r="E263" s="49" t="n"/>
+      <c r="F263" s="49" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="49" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
+      <c r="B264" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C264" s="49" t="n">
+        <v>533</v>
+      </c>
+      <c r="D264" s="49" t="n">
+        <v>533</v>
+      </c>
+      <c r="E264" s="49" t="n"/>
+      <c r="F264" s="49" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B265" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C265" s="49" t="n">
+        <v>535</v>
+      </c>
+      <c r="D265" s="49" t="n">
+        <v>535</v>
+      </c>
+      <c r="E265" s="49" t="n"/>
+      <c r="F265" s="49" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="B266" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C266" s="49" t="n">
+        <v>537</v>
+      </c>
+      <c r="D266" s="49" t="n">
+        <v>537</v>
+      </c>
+      <c r="E266" s="49" t="n"/>
+      <c r="F266" s="49" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="B267" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C267" s="49" t="n">
+        <v>539</v>
+      </c>
+      <c r="D267" s="49" t="n">
+        <v>539</v>
+      </c>
+      <c r="E267" s="49" t="n"/>
+      <c r="F267" s="49" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="B268" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C268" s="49" t="n">
+        <v>541</v>
+      </c>
+      <c r="D268" s="49" t="n">
+        <v>541</v>
+      </c>
+      <c r="E268" s="49" t="n"/>
+      <c r="F268" s="49" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="B269" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C269" s="49" t="n">
+        <v>543</v>
+      </c>
+      <c r="D269" s="49" t="n">
+        <v>543</v>
+      </c>
+      <c r="E269" s="49" t="n"/>
+      <c r="F269" s="49" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="B270" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C270" s="49" t="n">
+        <v>545</v>
+      </c>
+      <c r="D270" s="49" t="n">
+        <v>545</v>
+      </c>
+      <c r="E270" s="49" t="n"/>
+      <c r="F270" s="49" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B271" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C271" s="49" t="n">
+        <v>547</v>
+      </c>
+      <c r="D271" s="49" t="n">
+        <v>547</v>
+      </c>
+      <c r="E271" s="49" t="n"/>
+      <c r="F271" s="49" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="B272" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C272" s="49" t="n">
+        <v>549</v>
+      </c>
+      <c r="D272" s="49" t="n">
+        <v>549</v>
+      </c>
+      <c r="E272" s="49" t="n"/>
+      <c r="F272" s="49" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="B273" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C273" s="49" t="n">
+        <v>551</v>
+      </c>
+      <c r="D273" s="49" t="n">
+        <v>551</v>
+      </c>
+      <c r="E273" s="49" t="n"/>
+      <c r="F273" s="49" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="B274" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C274" s="49" t="n">
+        <v>553</v>
+      </c>
+      <c r="D274" s="49" t="n">
+        <v>553</v>
+      </c>
+      <c r="E274" s="49" t="n"/>
+      <c r="F274" s="49" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="B275" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C275" s="49" t="n">
+        <v>555</v>
+      </c>
+      <c r="D275" s="49" t="n">
+        <v>555</v>
+      </c>
+      <c r="E275" s="49" t="n"/>
+      <c r="F275" s="49" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="B276" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C276" s="49" t="n">
+        <v>557</v>
+      </c>
+      <c r="D276" s="49" t="n">
+        <v>557</v>
+      </c>
+      <c r="E276" s="49" t="n"/>
+      <c r="F276" s="49" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="B277" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C277" s="49" t="n">
+        <v>559</v>
+      </c>
+      <c r="D277" s="49" t="n">
+        <v>559</v>
+      </c>
+      <c r="E277" s="49" t="n"/>
+      <c r="F277" s="49" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="B278" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C278" s="49" t="n">
+        <v>561</v>
+      </c>
+      <c r="D278" s="49" t="n">
+        <v>561</v>
+      </c>
+      <c r="E278" s="49" t="n"/>
+      <c r="F278" s="49" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="B279" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C279" s="49" t="n">
+        <v>563</v>
+      </c>
+      <c r="D279" s="49" t="n">
+        <v>563</v>
+      </c>
+      <c r="E279" s="49" t="n"/>
+      <c r="F279" s="49" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="B280" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C280" s="49" t="n">
+        <v>565</v>
+      </c>
+      <c r="D280" s="49" t="n">
+        <v>565</v>
+      </c>
+      <c r="E280" s="49" t="n"/>
+      <c r="F280" s="49" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="B281" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C281" s="49" t="n">
+        <v>567</v>
+      </c>
+      <c r="D281" s="49" t="n">
+        <v>567</v>
+      </c>
+      <c r="E281" s="49" t="n"/>
+      <c r="F281" s="49" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="B282" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C282" s="49" t="n">
+        <v>569</v>
+      </c>
+      <c r="D282" s="49" t="n">
+        <v>569</v>
+      </c>
+      <c r="E282" s="49" t="n"/>
+      <c r="F282" s="49" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="B283" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C283" s="49" t="n">
+        <v>571</v>
+      </c>
+      <c r="D283" s="49" t="n">
+        <v>571</v>
+      </c>
+      <c r="E283" s="49" t="n"/>
+      <c r="F283" s="49" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="B284" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C284" s="49" t="n">
+        <v>573</v>
+      </c>
+      <c r="D284" s="49" t="n">
+        <v>573</v>
+      </c>
+      <c r="E284" s="49" t="n"/>
+      <c r="F284" s="49" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="B285" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C285" s="49" t="n">
+        <v>575</v>
+      </c>
+      <c r="D285" s="49" t="n">
+        <v>575</v>
+      </c>
+      <c r="E285" s="49" t="n"/>
+      <c r="F285" s="49" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B286" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C286" s="49" t="n">
+        <v>577</v>
+      </c>
+      <c r="D286" s="49" t="n">
+        <v>577</v>
+      </c>
+      <c r="E286" s="49" t="n"/>
+      <c r="F286" s="49" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B287" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C287" s="49" t="n">
+        <v>579</v>
+      </c>
+      <c r="D287" s="49" t="n">
+        <v>579</v>
+      </c>
+      <c r="E287" s="49" t="n"/>
+      <c r="F287" s="49" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B288" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C288" s="49" t="n">
+        <v>581</v>
+      </c>
+      <c r="D288" s="49" t="n">
+        <v>581</v>
+      </c>
+      <c r="E288" s="49" t="n"/>
+      <c r="F288" s="49" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B289" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C289" s="49" t="n">
+        <v>583</v>
+      </c>
+      <c r="D289" s="49" t="n">
+        <v>583</v>
+      </c>
+      <c r="E289" s="49" t="n"/>
+      <c r="F289" s="49" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="B290" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C290" s="49" t="n">
+        <v>585</v>
+      </c>
+      <c r="D290" s="49" t="n">
+        <v>585</v>
+      </c>
+      <c r="E290" s="49" t="n"/>
+      <c r="F290" s="49" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="B291" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C291" s="49" t="n">
+        <v>587</v>
+      </c>
+      <c r="D291" s="49" t="n">
+        <v>587</v>
+      </c>
+      <c r="E291" s="49" t="n"/>
+      <c r="F291" s="49" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B292" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C292" s="49" t="n">
+        <v>589</v>
+      </c>
+      <c r="D292" s="49" t="n">
+        <v>589</v>
+      </c>
+      <c r="E292" s="49" t="n"/>
+      <c r="F292" s="49" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B293" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C293" s="49" t="n">
+        <v>591</v>
+      </c>
+      <c r="D293" s="49" t="n">
+        <v>591</v>
+      </c>
+      <c r="E293" s="49" t="n"/>
+      <c r="F293" s="49" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="49" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
+      <c r="B294" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C294" s="49" t="n">
+        <v>593</v>
+      </c>
+      <c r="D294" s="49" t="n">
+        <v>593</v>
+      </c>
+      <c r="E294" s="49" t="n"/>
+      <c r="F294" s="49" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B295" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C295" s="49" t="n">
+        <v>595</v>
+      </c>
+      <c r="D295" s="49" t="n">
+        <v>595</v>
+      </c>
+      <c r="E295" s="49" t="n"/>
+      <c r="F295" s="49" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="B296" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C296" s="49" t="n">
+        <v>597</v>
+      </c>
+      <c r="D296" s="49" t="n">
+        <v>597</v>
+      </c>
+      <c r="E296" s="49" t="n"/>
+      <c r="F296" s="49" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="B297" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C297" s="49" t="n">
+        <v>599</v>
+      </c>
+      <c r="D297" s="49" t="n">
+        <v>599</v>
+      </c>
+      <c r="E297" s="49" t="n"/>
+      <c r="F297" s="49" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="B298" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C298" s="49" t="n">
+        <v>601</v>
+      </c>
+      <c r="D298" s="49" t="n">
+        <v>601</v>
+      </c>
+      <c r="E298" s="49" t="n"/>
+      <c r="F298" s="49" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="B299" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C299" s="49" t="n">
+        <v>603</v>
+      </c>
+      <c r="D299" s="49" t="n">
+        <v>603</v>
+      </c>
+      <c r="E299" s="49" t="n"/>
+      <c r="F299" s="49" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="B300" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C300" s="49" t="n">
+        <v>605</v>
+      </c>
+      <c r="D300" s="49" t="n">
+        <v>605</v>
+      </c>
+      <c r="E300" s="49" t="n"/>
+      <c r="F300" s="49" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B301" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C301" s="49" t="n">
+        <v>607</v>
+      </c>
+      <c r="D301" s="49" t="n">
+        <v>607</v>
+      </c>
+      <c r="E301" s="49" t="n"/>
+      <c r="F301" s="49" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="B302" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C302" s="49" t="n">
+        <v>609</v>
+      </c>
+      <c r="D302" s="49" t="n">
+        <v>609</v>
+      </c>
+      <c r="E302" s="49" t="n"/>
+      <c r="F302" s="49" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="B303" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C303" s="49" t="n">
+        <v>611</v>
+      </c>
+      <c r="D303" s="49" t="n">
+        <v>611</v>
+      </c>
+      <c r="E303" s="49" t="n"/>
+      <c r="F303" s="49" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="B304" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C304" s="49" t="n">
+        <v>613</v>
+      </c>
+      <c r="D304" s="49" t="n">
+        <v>614</v>
+      </c>
+      <c r="E304" s="49" t="n"/>
+      <c r="F304" s="49" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="B305" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C305" s="49" t="n">
+        <v>616</v>
+      </c>
+      <c r="D305" s="49" t="n">
+        <v>616</v>
+      </c>
+      <c r="E305" s="49" t="n"/>
+      <c r="F305" s="49" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="B306" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C306" s="49" t="n">
+        <v>618</v>
+      </c>
+      <c r="D306" s="49" t="n">
+        <v>618</v>
+      </c>
+      <c r="E306" s="49" t="n"/>
+      <c r="F306" s="49" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="B307" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C307" s="49" t="n">
+        <v>620</v>
+      </c>
+      <c r="D307" s="49" t="n">
+        <v>620</v>
+      </c>
+      <c r="E307" s="49" t="n"/>
+      <c r="F307" s="49" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="B308" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C308" s="49" t="n">
+        <v>622</v>
+      </c>
+      <c r="D308" s="49" t="n">
+        <v>622</v>
+      </c>
+      <c r="E308" s="49" t="n"/>
+      <c r="F308" s="49" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="B309" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C309" s="49" t="n">
+        <v>624</v>
+      </c>
+      <c r="D309" s="49" t="n">
+        <v>624</v>
+      </c>
+      <c r="E309" s="49" t="n"/>
+      <c r="F309" s="49" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="B310" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C310" s="49" t="n">
+        <v>626</v>
+      </c>
+      <c r="D310" s="49" t="n">
+        <v>627</v>
+      </c>
+      <c r="E310" s="49" t="n"/>
+      <c r="F310" s="49" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="B311" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C311" s="49" t="n">
+        <v>629</v>
+      </c>
+      <c r="D311" s="49" t="n">
+        <v>629</v>
+      </c>
+      <c r="E311" s="49" t="n"/>
+      <c r="F311" s="49" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="B312" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C312" s="49" t="n">
+        <v>631</v>
+      </c>
+      <c r="D312" s="49" t="n">
+        <v>631</v>
+      </c>
+      <c r="E312" s="49" t="n"/>
+      <c r="F312" s="49" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="B313" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C313" s="49" t="n">
+        <v>633</v>
+      </c>
+      <c r="D313" s="49" t="n">
+        <v>633</v>
+      </c>
+      <c r="E313" s="49" t="n"/>
+      <c r="F313" s="49" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="B314" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C314" s="49" t="n">
+        <v>635</v>
+      </c>
+      <c r="D314" s="49" t="n">
+        <v>635</v>
+      </c>
+      <c r="E314" s="49" t="n"/>
+      <c r="F314" s="49" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="B315" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C315" s="49" t="n">
+        <v>637</v>
+      </c>
+      <c r="D315" s="49" t="n">
+        <v>637</v>
+      </c>
+      <c r="E315" s="49" t="n"/>
+      <c r="F315" s="49" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B316" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C316" s="49" t="n">
+        <v>639</v>
+      </c>
+      <c r="D316" s="49" t="n">
+        <v>639</v>
+      </c>
+      <c r="E316" s="49" t="n"/>
+      <c r="F316" s="49" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B317" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C317" s="49" t="n">
+        <v>641</v>
+      </c>
+      <c r="D317" s="49" t="n">
+        <v>641</v>
+      </c>
+      <c r="E317" s="49" t="n"/>
+      <c r="F317" s="49" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B318" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C318" s="49" t="n">
+        <v>643</v>
+      </c>
+      <c r="D318" s="49" t="n">
+        <v>643</v>
+      </c>
+      <c r="E318" s="49" t="n"/>
+      <c r="F318" s="49" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B319" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C319" s="49" t="n">
+        <v>645</v>
+      </c>
+      <c r="D319" s="49" t="n">
+        <v>645</v>
+      </c>
+      <c r="E319" s="49" t="n"/>
+      <c r="F319" s="49" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="B320" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C320" s="49" t="n">
+        <v>647</v>
+      </c>
+      <c r="D320" s="49" t="n">
+        <v>647</v>
+      </c>
+      <c r="E320" s="49" t="n"/>
+      <c r="F320" s="49" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="B321" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C321" s="49" t="n">
+        <v>649</v>
+      </c>
+      <c r="D321" s="49" t="n">
+        <v>649</v>
+      </c>
+      <c r="E321" s="49" t="n"/>
+      <c r="F321" s="49" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B322" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C322" s="49" t="n">
+        <v>651</v>
+      </c>
+      <c r="D322" s="49" t="n">
+        <v>651</v>
+      </c>
+      <c r="E322" s="49" t="n"/>
+      <c r="F322" s="49" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B323" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C323" s="49" t="n">
+        <v>653</v>
+      </c>
+      <c r="D323" s="49" t="n">
+        <v>653</v>
+      </c>
+      <c r="E323" s="49" t="n"/>
+      <c r="F323" s="49" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="49" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
+      <c r="B324" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C324" s="49" t="n">
+        <v>655</v>
+      </c>
+      <c r="D324" s="49" t="n">
+        <v>655</v>
+      </c>
+      <c r="E324" s="49" t="n"/>
+      <c r="F324" s="49" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B325" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C325" s="49" t="n">
+        <v>657</v>
+      </c>
+      <c r="D325" s="49" t="n">
+        <v>657</v>
+      </c>
+      <c r="E325" s="49" t="n"/>
+      <c r="F325" s="49" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="B326" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C326" s="49" t="n">
+        <v>659</v>
+      </c>
+      <c r="D326" s="49" t="n">
+        <v>659</v>
+      </c>
+      <c r="E326" s="49" t="n"/>
+      <c r="F326" s="49" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="B327" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C327" s="49" t="n">
+        <v>661</v>
+      </c>
+      <c r="D327" s="49" t="n">
+        <v>661</v>
+      </c>
+      <c r="E327" s="49" t="n"/>
+      <c r="F327" s="49" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="B328" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C328" s="49" t="n">
+        <v>663</v>
+      </c>
+      <c r="D328" s="49" t="n">
+        <v>663</v>
+      </c>
+      <c r="E328" s="49" t="n"/>
+      <c r="F328" s="49" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="49" t="n">
+        <v>14</v>
+      </c>
+      <c r="B329" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C329" s="49" t="n">
+        <v>665</v>
+      </c>
+      <c r="D329" s="49" t="n">
+        <v>665</v>
+      </c>
+      <c r="E329" s="49" t="n"/>
+      <c r="F329" s="49" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="B330" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C330" s="49" t="n">
+        <v>667</v>
+      </c>
+      <c r="D330" s="49" t="n">
+        <v>667</v>
+      </c>
+      <c r="E330" s="49" t="n"/>
+      <c r="F330" s="49" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B331" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C331" s="49" t="n">
+        <v>669</v>
+      </c>
+      <c r="D331" s="49" t="n">
+        <v>669</v>
+      </c>
+      <c r="E331" s="49" t="n"/>
+      <c r="F331" s="49" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="49" t="n">
+        <v>17</v>
+      </c>
+      <c r="B332" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C332" s="49" t="n">
+        <v>671</v>
+      </c>
+      <c r="D332" s="49" t="n">
+        <v>671</v>
+      </c>
+      <c r="E332" s="49" t="n"/>
+      <c r="F332" s="49" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="B333" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C333" s="49" t="n">
+        <v>673</v>
+      </c>
+      <c r="D333" s="49" t="n">
+        <v>673</v>
+      </c>
+      <c r="E333" s="49" t="n"/>
+      <c r="F333" s="49" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="49" t="n">
+        <v>19</v>
+      </c>
+      <c r="B334" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C334" s="49" t="n">
+        <v>675</v>
+      </c>
+      <c r="D334" s="49" t="n">
+        <v>675</v>
+      </c>
+      <c r="E334" s="49" t="n"/>
+      <c r="F334" s="49" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="B335" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C335" s="49" t="n">
+        <v>677</v>
+      </c>
+      <c r="D335" s="49" t="n">
+        <v>677</v>
+      </c>
+      <c r="E335" s="49" t="n"/>
+      <c r="F335" s="49" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="B336" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C336" s="49" t="n">
+        <v>679</v>
+      </c>
+      <c r="D336" s="49" t="n">
+        <v>679</v>
+      </c>
+      <c r="E336" s="49" t="n"/>
+      <c r="F336" s="49" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="B337" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C337" s="49" t="n">
+        <v>681</v>
+      </c>
+      <c r="D337" s="49" t="n">
+        <v>681</v>
+      </c>
+      <c r="E337" s="49" t="n"/>
+      <c r="F337" s="49" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="B338" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C338" s="49" t="n">
+        <v>683</v>
+      </c>
+      <c r="D338" s="49" t="n">
+        <v>683</v>
+      </c>
+      <c r="E338" s="49" t="n"/>
+      <c r="F338" s="49" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="B339" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C339" s="49" t="n">
+        <v>685</v>
+      </c>
+      <c r="D339" s="49" t="n">
+        <v>685</v>
+      </c>
+      <c r="E339" s="49" t="n"/>
+      <c r="F339" s="49" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="B340" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C340" s="49" t="n">
+        <v>687</v>
+      </c>
+      <c r="D340" s="49" t="n">
+        <v>687</v>
+      </c>
+      <c r="E340" s="49" t="n"/>
+      <c r="F340" s="49" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="B341" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C341" s="49" t="n">
+        <v>689</v>
+      </c>
+      <c r="D341" s="49" t="n">
+        <v>689</v>
+      </c>
+      <c r="E341" s="49" t="n"/>
+      <c r="F341" s="49" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="49" t="n">
+        <v>27</v>
+      </c>
+      <c r="B342" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C342" s="49" t="n">
+        <v>691</v>
+      </c>
+      <c r="D342" s="49" t="n">
+        <v>691</v>
+      </c>
+      <c r="E342" s="49" t="n"/>
+      <c r="F342" s="49" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="B343" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C343" s="49" t="n">
+        <v>693</v>
+      </c>
+      <c r="D343" s="49" t="n">
+        <v>693</v>
+      </c>
+      <c r="E343" s="49" t="n"/>
+      <c r="F343" s="49" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="B344" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C344" s="49" t="n">
+        <v>695</v>
+      </c>
+      <c r="D344" s="49" t="n">
+        <v>695</v>
+      </c>
+      <c r="E344" s="49" t="n"/>
+      <c r="F344" s="49" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="B345" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C345" s="49" t="n">
+        <v>697</v>
+      </c>
+      <c r="D345" s="49" t="n">
+        <v>697</v>
+      </c>
+      <c r="E345" s="49" t="n"/>
+      <c r="F345" s="49" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B346" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="C346" s="49" t="n">
+        <v>699</v>
+      </c>
+      <c r="D346" s="49" t="n">
+        <v>699</v>
+      </c>
+      <c r="E346" s="49" t="n"/>
+      <c r="F346" s="49" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B347" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="C347" s="49" t="n">
+        <v>701</v>
+      </c>
+      <c r="D347" s="49" t="n">
+        <v>701</v>
+      </c>
+      <c r="E347" s="49" t="n"/>
+      <c r="F347" s="49" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B348" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="C348" s="49" t="n">
+        <v>703</v>
+      </c>
+      <c r="D348" s="49" t="n">
+        <v>703</v>
+      </c>
+      <c r="E348" s="49" t="n"/>
+      <c r="F348" s="49" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B244" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
+      <c r="B349" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="C349" s="49" t="n">
+        <v>705</v>
+      </c>
+      <c r="D349" s="49" t="n">
+        <v>705</v>
+      </c>
+      <c r="E349" s="49" t="n"/>
+      <c r="F349" s="49" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B245" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
+      <c r="B350" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="C350" s="49" t="n">
+        <v>707</v>
+      </c>
+      <c r="D350" s="49" t="n">
+        <v>707</v>
+      </c>
+      <c r="E350" s="49" t="n"/>
+      <c r="F350" s="49" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B246" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>7</v>
-      </c>
-      <c r="B247" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>8</v>
-      </c>
-      <c r="B248" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>9</v>
-      </c>
-      <c r="B249" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>10</v>
-      </c>
-      <c r="B250" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>11</v>
-      </c>
-      <c r="B251" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>12</v>
-      </c>
-      <c r="B252" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
+      <c r="B351" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="B253" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>14</v>
-      </c>
-      <c r="B254" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>15</v>
-      </c>
-      <c r="B255" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>16</v>
-      </c>
-      <c r="B256" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>17</v>
-      </c>
-      <c r="B257" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>18</v>
-      </c>
-      <c r="B258" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>19</v>
-      </c>
-      <c r="B259" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>20</v>
-      </c>
-      <c r="B260" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>21</v>
-      </c>
-      <c r="B261" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>22</v>
-      </c>
-      <c r="B262" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>23</v>
-      </c>
-      <c r="B263" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>24</v>
-      </c>
-      <c r="B264" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>25</v>
-      </c>
-      <c r="B265" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>26</v>
-      </c>
-      <c r="B266" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>27</v>
-      </c>
-      <c r="B267" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>28</v>
-      </c>
-      <c r="B268" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>29</v>
-      </c>
-      <c r="B269" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>30</v>
-      </c>
-      <c r="B270" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>1</v>
-      </c>
-      <c r="B271" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>2</v>
-      </c>
-      <c r="B272" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>3</v>
-      </c>
-      <c r="B273" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>4</v>
-      </c>
-      <c r="B274" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>5</v>
-      </c>
-      <c r="B275" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>6</v>
-      </c>
-      <c r="B276" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>7</v>
-      </c>
-      <c r="B277" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>8</v>
-      </c>
-      <c r="B278" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>9</v>
-      </c>
-      <c r="B279" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>10</v>
-      </c>
-      <c r="B280" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>11</v>
-      </c>
-      <c r="B281" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>12</v>
-      </c>
-      <c r="B282" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>13</v>
-      </c>
-      <c r="B283" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>14</v>
-      </c>
-      <c r="B284" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>15</v>
-      </c>
-      <c r="B285" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>16</v>
-      </c>
-      <c r="B286" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>17</v>
-      </c>
-      <c r="B287" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>18</v>
-      </c>
-      <c r="B288" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>19</v>
-      </c>
-      <c r="B289" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>20</v>
-      </c>
-      <c r="B290" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>21</v>
-      </c>
-      <c r="B291" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>22</v>
-      </c>
-      <c r="B292" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>23</v>
-      </c>
-      <c r="B293" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>24</v>
-      </c>
-      <c r="B294" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>25</v>
-      </c>
-      <c r="B295" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>26</v>
-      </c>
-      <c r="B296" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>27</v>
-      </c>
-      <c r="B297" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>28</v>
-      </c>
-      <c r="B298" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>29</v>
-      </c>
-      <c r="B299" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>30</v>
-      </c>
-      <c r="B300" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>1</v>
-      </c>
-      <c r="B301" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>2</v>
-      </c>
-      <c r="B302" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>3</v>
-      </c>
-      <c r="B303" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>4</v>
-      </c>
-      <c r="B304" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>5</v>
-      </c>
-      <c r="B305" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>6</v>
-      </c>
-      <c r="B306" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>7</v>
-      </c>
-      <c r="B307" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>8</v>
-      </c>
-      <c r="B308" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>9</v>
-      </c>
-      <c r="B309" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>10</v>
-      </c>
-      <c r="B310" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>11</v>
-      </c>
-      <c r="B311" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>12</v>
-      </c>
-      <c r="B312" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>13</v>
-      </c>
-      <c r="B313" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>14</v>
-      </c>
-      <c r="B314" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>15</v>
-      </c>
-      <c r="B315" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>16</v>
-      </c>
-      <c r="B316" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>17</v>
-      </c>
-      <c r="B317" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>18</v>
-      </c>
-      <c r="B318" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>19</v>
-      </c>
-      <c r="B319" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>20</v>
-      </c>
-      <c r="B320" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>21</v>
-      </c>
-      <c r="B321" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>22</v>
-      </c>
-      <c r="B322" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>23</v>
-      </c>
-      <c r="B323" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>24</v>
-      </c>
-      <c r="B324" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>25</v>
-      </c>
-      <c r="B325" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>26</v>
-      </c>
-      <c r="B326" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>27</v>
-      </c>
-      <c r="B327" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>28</v>
-      </c>
-      <c r="B328" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>29</v>
-      </c>
-      <c r="B329" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>30</v>
-      </c>
-      <c r="B330" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>1</v>
-      </c>
-      <c r="B331" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>2</v>
-      </c>
-      <c r="B332" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>3</v>
-      </c>
-      <c r="B333" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>4</v>
-      </c>
-      <c r="B334" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>5</v>
-      </c>
-      <c r="B335" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>6</v>
-      </c>
-      <c r="B336" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>7</v>
-      </c>
-      <c r="B337" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>8</v>
-      </c>
-      <c r="B338" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>9</v>
-      </c>
-      <c r="B339" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>10</v>
-      </c>
-      <c r="B340" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>11</v>
-      </c>
-      <c r="B341" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>12</v>
-      </c>
-      <c r="B342" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>13</v>
-      </c>
-      <c r="B343" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>14</v>
-      </c>
-      <c r="B344" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>15</v>
-      </c>
-      <c r="B345" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>16</v>
-      </c>
-      <c r="B346" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>17</v>
-      </c>
-      <c r="B347" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>18</v>
-      </c>
-      <c r="B348" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>19</v>
-      </c>
-      <c r="B349" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>20</v>
-      </c>
-      <c r="B350" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>21</v>
-      </c>
-      <c r="B351" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>22</v>
-      </c>
-      <c r="B352" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>23</v>
-      </c>
-      <c r="B353" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>24</v>
-      </c>
-      <c r="B354" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>25</v>
-      </c>
-      <c r="B355" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>26</v>
-      </c>
-      <c r="B356" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>27</v>
-      </c>
-      <c r="B357" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>28</v>
-      </c>
-      <c r="B358" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>29</v>
-      </c>
-      <c r="B359" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>30</v>
-      </c>
-      <c r="B360" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>1</v>
-      </c>
-      <c r="B361" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>2</v>
-      </c>
-      <c r="B362" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>3</v>
-      </c>
-      <c r="B363" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>4</v>
-      </c>
-      <c r="B364" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>5</v>
-      </c>
-      <c r="B365" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>6</v>
-      </c>
-      <c r="B366" t="n">
-        <v>13</v>
-      </c>
+      <c r="C351" s="49" t="n">
+        <v>709</v>
+      </c>
+      <c r="D351" s="49" t="n">
+        <v>709</v>
+      </c>
+      <c r="E351" s="49" t="n"/>
+      <c r="F351" s="49" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9436,7 +12152,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -12764,7 +15480,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9.140625" customWidth="1" style="55" min="5" max="5"/>
   </cols>
@@ -15221,7 +17937,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -17101,8 +19817,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.85546875" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -17977,7 +20693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="55">
@@ -18848,7 +21564,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>
@@ -20182,7 +22898,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6.28515625" bestFit="1" customWidth="1" style="55" min="1" max="1"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="55" min="2" max="2"/>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="868" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="868" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المناسبات" sheetId="1" state="visible" r:id="rId1"/>
@@ -756,6 +756,15 @@
     <xf numFmtId="0" fontId="11" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -785,15 +794,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1419,8 +1419,8 @@
     <col width="11.140625" customWidth="1" style="68" min="11" max="11"/>
     <col width="17.85546875" customWidth="1" style="68" min="12" max="12"/>
     <col width="28" customWidth="1" style="68" min="13" max="13"/>
-    <col width="17.85546875" customWidth="1" style="68" min="14" max="109"/>
-    <col width="17.85546875" customWidth="1" style="68" min="110" max="16384"/>
+    <col width="17.85546875" customWidth="1" style="68" min="14" max="110"/>
+    <col width="17.85546875" customWidth="1" style="68" min="111" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" s="53">
@@ -1454,26 +1454,26 @@
           <t>المناسبة</t>
         </is>
       </c>
-      <c r="I1" s="82" t="inlineStr">
+      <c r="I1" s="85" t="inlineStr">
         <is>
           <t>دور القمر</t>
         </is>
       </c>
-      <c r="J1" s="82" t="inlineStr">
+      <c r="J1" s="85" t="inlineStr">
         <is>
           <t>الفصح</t>
         </is>
       </c>
-      <c r="K1" s="81" t="n"/>
-      <c r="M1" s="92" t="inlineStr">
+      <c r="K1" s="84" t="n"/>
+      <c r="M1" s="95" t="inlineStr">
         <is>
           <t>السنة القبطية الحالية</t>
         </is>
       </c>
-      <c r="N1" s="81" t="n"/>
+      <c r="N1" s="84" t="n"/>
       <c r="R1" s="1" t="n"/>
     </row>
-    <row r="2" ht="23.25" customHeight="1" s="53">
+    <row r="2" ht="26.25" customHeight="1" s="53">
       <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
@@ -1497,24 +1497,24 @@
           <t>النيروز</t>
         </is>
       </c>
-      <c r="I2" s="83" t="n"/>
-      <c r="J2" s="82" t="inlineStr">
+      <c r="I2" s="86" t="n"/>
+      <c r="J2" s="85" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="K2" s="82" t="inlineStr">
+      <c r="K2" s="85" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
       </c>
-      <c r="M2" s="80" t="n">
+      <c r="M2" s="83" t="n">
         <v>1742</v>
       </c>
-      <c r="N2" s="81" t="n"/>
+      <c r="N2" s="84" t="n"/>
       <c r="R2" s="2" t="n"/>
     </row>
-    <row r="3" ht="18.75" customHeight="1" s="53">
+    <row r="3" ht="21" customHeight="1" s="53">
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="4" t="n"/>
     </row>
-    <row r="4" ht="18.75" customHeight="1" s="53" thickBot="1">
+    <row r="4" ht="21.75" customHeight="1" s="53" thickBot="1">
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="R4" s="5" t="n"/>
       <c r="T4" s="6" t="n"/>
     </row>
-    <row r="5" ht="18.75" customHeight="1" s="53" thickTop="1">
+    <row r="5" ht="21.75" customHeight="1" s="53" thickTop="1">
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
@@ -1623,16 +1623,16 @@
       <c r="K5" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="86" t="inlineStr">
+      <c r="M5" s="89" t="inlineStr">
         <is>
           <t>لضمان عمل البرنامج بشكل صحيح لا تُغيّر أي شئ يدويًا في الملف</t>
         </is>
       </c>
-      <c r="N5" s="87" t="n"/>
+      <c r="N5" s="90" t="n"/>
       <c r="R5" s="5" t="n"/>
       <c r="T5" s="6" t="n"/>
     </row>
-    <row r="6" ht="18.75" customHeight="1" s="53">
+    <row r="6" ht="21" customHeight="1" s="53">
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
@@ -1665,12 +1665,12 @@
       <c r="K6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="88" t="n"/>
-      <c r="N6" s="89" t="n"/>
+      <c r="M6" s="91" t="n"/>
+      <c r="N6" s="92" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="T6" s="6" t="n"/>
     </row>
-    <row r="7" ht="18.75" customHeight="1" s="53">
+    <row r="7" ht="21" customHeight="1" s="53">
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v/>
       </c>
       <c r="F7" s="35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
@@ -1703,12 +1703,12 @@
       <c r="K7" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="88" t="n"/>
-      <c r="N7" s="89" t="n"/>
+      <c r="M7" s="91" t="n"/>
+      <c r="N7" s="92" t="n"/>
       <c r="R7" s="5" t="n"/>
       <c r="T7" s="6" t="n"/>
     </row>
-    <row r="8" ht="18.75" customHeight="1" s="53">
+    <row r="8" ht="21" customHeight="1" s="53">
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
@@ -1741,12 +1741,12 @@
       <c r="K8" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="88" t="n"/>
-      <c r="N8" s="89" t="n"/>
+      <c r="M8" s="91" t="n"/>
+      <c r="N8" s="92" t="n"/>
       <c r="R8" s="5" t="n"/>
       <c r="T8" s="6" t="n"/>
     </row>
-    <row r="9" ht="18.75" customHeight="1" s="53">
+    <row r="9" ht="21" customHeight="1" s="53">
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
@@ -1779,12 +1779,12 @@
       <c r="K9" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M9" s="88" t="n"/>
-      <c r="N9" s="89" t="n"/>
+      <c r="M9" s="91" t="n"/>
+      <c r="N9" s="92" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="T9" s="6" t="n"/>
     </row>
-    <row r="10" ht="18.75" customHeight="1" s="53">
+    <row r="10" ht="21" customHeight="1" s="53">
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
@@ -1817,12 +1817,12 @@
       <c r="K10" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M10" s="88" t="n"/>
-      <c r="N10" s="89" t="n"/>
+      <c r="M10" s="91" t="n"/>
+      <c r="N10" s="92" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="T10" s="6" t="n"/>
     </row>
-    <row r="11" ht="18.75" customHeight="1" s="53">
+    <row r="11" ht="21" customHeight="1" s="53">
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
@@ -1855,12 +1855,12 @@
       <c r="K11" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M11" s="88" t="n"/>
-      <c r="N11" s="89" t="n"/>
+      <c r="M11" s="91" t="n"/>
+      <c r="N11" s="92" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="T11" s="6" t="n"/>
     </row>
-    <row r="12" ht="18.75" customHeight="1" s="53">
+    <row r="12" ht="21" customHeight="1" s="53">
       <c r="A12" s="12" t="n">
         <v>11</v>
       </c>
@@ -1893,12 +1893,12 @@
       <c r="K12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M12" s="88" t="n"/>
-      <c r="N12" s="89" t="n"/>
+      <c r="M12" s="91" t="n"/>
+      <c r="N12" s="92" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="T12" s="6" t="n"/>
     </row>
-    <row r="13" ht="18.75" customHeight="1" s="53">
+    <row r="13" ht="21" customHeight="1" s="53">
       <c r="A13" s="12" t="n">
         <v>12</v>
       </c>
@@ -1931,12 +1931,12 @@
       <c r="K13" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="88" t="n"/>
-      <c r="N13" s="89" t="n"/>
+      <c r="M13" s="91" t="n"/>
+      <c r="N13" s="92" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="T13" s="6" t="n"/>
     </row>
-    <row r="14" ht="18.75" customHeight="1" s="53">
+    <row r="14" ht="21" customHeight="1" s="53">
       <c r="A14" s="12" t="n">
         <v>13</v>
       </c>
@@ -1969,12 +1969,12 @@
       <c r="K14" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M14" s="88" t="n"/>
-      <c r="N14" s="89" t="n"/>
+      <c r="M14" s="91" t="n"/>
+      <c r="N14" s="92" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="T14" s="6" t="n"/>
     </row>
-    <row r="15" ht="18.75" customHeight="1" s="53">
+    <row r="15" ht="21" customHeight="1" s="53">
       <c r="D15" s="17" t="n">
         <v>7</v>
       </c>
@@ -1999,12 +1999,12 @@
       <c r="K15" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M15" s="88" t="n"/>
-      <c r="N15" s="89" t="n"/>
+      <c r="M15" s="91" t="n"/>
+      <c r="N15" s="92" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="T15" s="6" t="n"/>
     </row>
-    <row r="16" ht="18.75" customHeight="1" s="53">
+    <row r="16" ht="21" customHeight="1" s="53">
       <c r="D16" s="33" t="n">
         <v>7</v>
       </c>
@@ -2029,12 +2029,12 @@
       <c r="K16" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M16" s="88" t="n"/>
-      <c r="N16" s="89" t="n"/>
+      <c r="M16" s="91" t="n"/>
+      <c r="N16" s="92" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="T16" s="6" t="n"/>
     </row>
-    <row r="17" ht="18.75" customHeight="1" s="53" thickBot="1">
+    <row r="17" ht="21.75" customHeight="1" s="53" thickBot="1">
       <c r="D17" s="33" t="n">
         <v>7</v>
       </c>
@@ -2059,12 +2059,12 @@
       <c r="K17" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M17" s="90" t="n"/>
-      <c r="N17" s="91" t="n"/>
+      <c r="M17" s="93" t="n"/>
+      <c r="N17" s="94" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="T17" s="6" t="n"/>
     </row>
-    <row r="18" ht="18.75" customHeight="1" s="53" thickTop="1">
+    <row r="18" ht="21.75" customHeight="1" s="53" thickTop="1">
       <c r="D18" s="33" t="n">
         <v>7</v>
       </c>
@@ -2093,7 +2093,7 @@
       <c r="R18" s="5" t="n"/>
       <c r="T18" s="6" t="n"/>
     </row>
-    <row r="19" ht="18.75" customHeight="1" s="53">
+    <row r="19" ht="21" customHeight="1" s="53">
       <c r="D19" s="33" t="n">
         <v>8</v>
       </c>
@@ -2122,7 +2122,7 @@
       <c r="R19" s="5" t="n"/>
       <c r="T19" s="6" t="n"/>
     </row>
-    <row r="20" ht="18.75" customHeight="1" s="53">
+    <row r="20" ht="21" customHeight="1" s="53">
       <c r="D20" s="33" t="n">
         <v>8</v>
       </c>
@@ -2151,7 +2151,7 @@
       <c r="R20" s="5" t="n"/>
       <c r="T20" s="6" t="n"/>
     </row>
-    <row r="21" ht="18.75" customHeight="1" s="53">
+    <row r="21" ht="21" customHeight="1" s="53">
       <c r="D21" s="33" t="n">
         <v>8</v>
       </c>
@@ -2180,7 +2180,7 @@
       <c r="R21" s="5" t="n"/>
       <c r="T21" s="6" t="n"/>
     </row>
-    <row r="22" ht="18.75" customHeight="1" s="53">
+    <row r="22" ht="21" customHeight="1" s="53">
       <c r="D22" s="33" t="n">
         <v>8</v>
       </c>
@@ -2215,17 +2215,17 @@
           <t>دخول السيد المسيح إلى أرض مصر</t>
         </is>
       </c>
-      <c r="I23" s="84" t="inlineStr">
+      <c r="I23" s="87" t="inlineStr">
         <is>
           <t>دور القمر في السنة الحالية</t>
         </is>
       </c>
-      <c r="J23" s="85" t="inlineStr">
+      <c r="J23" s="88" t="inlineStr">
         <is>
           <t>الفصح في السنة الحالية</t>
         </is>
       </c>
-      <c r="K23" s="81" t="n"/>
+      <c r="K23" s="84" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="53">
       <c r="D24" s="37" t="n">
@@ -2243,7 +2243,7 @@
           <t>عيد الصعود</t>
         </is>
       </c>
-      <c r="I24" s="83" t="n"/>
+      <c r="I24" s="86" t="n"/>
       <c r="J24" s="11" t="inlineStr">
         <is>
           <t>اليوم</t>
@@ -2400,42 +2400,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="53">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="B1" s="82" t="inlineStr">
+      <c r="B1" s="85" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
       </c>
-      <c r="C1" s="82" t="inlineStr">
+      <c r="C1" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">البولس </t>
         </is>
       </c>
-      <c r="D1" s="82" t="inlineStr">
+      <c r="D1" s="85" t="inlineStr">
         <is>
           <t>الكاثوليكون</t>
         </is>
       </c>
-      <c r="E1" s="82" t="inlineStr">
+      <c r="E1" s="85" t="inlineStr">
         <is>
           <t>الابركسيس</t>
         </is>
       </c>
-      <c r="F1" s="82" t="inlineStr">
+      <c r="F1" s="85" t="inlineStr">
         <is>
           <t>المزمور</t>
         </is>
       </c>
-      <c r="G1" s="82" t="inlineStr">
+      <c r="G1" s="85" t="inlineStr">
         <is>
           <t>الإنجيل</t>
         </is>
       </c>
-      <c r="H1" s="82" t="inlineStr">
+      <c r="H1" s="85" t="inlineStr">
         <is>
           <t>نهاية الانجيل</t>
         </is>
@@ -3823,28 +3823,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" s="53">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="B1" s="93" t="inlineStr">
+      <c r="B1" s="96" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
       </c>
-      <c r="C1" s="93" t="inlineStr">
+      <c r="C1" s="96" t="inlineStr">
         <is>
           <t>عناوين فقط</t>
         </is>
       </c>
-      <c r="D1" s="94" t="n"/>
-      <c r="E1" s="93" t="inlineStr">
+      <c r="D1" s="97" t="n"/>
+      <c r="E1" s="96" t="inlineStr">
         <is>
           <t>النص كامل</t>
         </is>
       </c>
-      <c r="F1" s="94" t="n"/>
+      <c r="F1" s="97" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="47" t="n">
@@ -12809,77 +12809,77 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" s="53" thickBot="1" thickTop="1">
-      <c r="A1" s="95" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="B1" s="96" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
       </c>
-      <c r="C1" s="97" t="inlineStr">
+      <c r="C1" s="82" t="inlineStr">
         <is>
           <t>مزمور عشية</t>
         </is>
       </c>
-      <c r="D1" s="96" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>إنجيل عشية</t>
         </is>
       </c>
-      <c r="E1" s="96" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>نهاية انجيل عشية</t>
         </is>
       </c>
-      <c r="F1" s="96" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>مزمور باكر</t>
         </is>
       </c>
-      <c r="G1" s="96" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>انجيل باكر</t>
         </is>
       </c>
-      <c r="H1" s="96" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>نهاية انجيل باكر</t>
         </is>
       </c>
-      <c r="I1" s="96" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">البولس </t>
         </is>
       </c>
-      <c r="J1" s="96" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>الكاثوليكون</t>
         </is>
       </c>
-      <c r="K1" s="96" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>الابركسيس</t>
         </is>
       </c>
-      <c r="L1" s="96" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>المزمور</t>
         </is>
       </c>
-      <c r="M1" s="96" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>الإنجيل</t>
         </is>
       </c>
-      <c r="N1" s="97" t="inlineStr">
+      <c r="N1" s="82" t="inlineStr">
         <is>
           <t>نهاية انجيل القداس</t>
         </is>
       </c>
-      <c r="O1" s="96" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
@@ -18429,8 +18429,8 @@
     <col width="12.7109375" customWidth="1" style="68" min="17" max="17"/>
     <col width="13.85546875" customWidth="1" style="68" min="18" max="18"/>
     <col width="14.140625" customWidth="1" style="68" min="19" max="19"/>
-    <col width="9.140625" customWidth="1" style="68" min="20" max="63"/>
-    <col width="9.140625" customWidth="1" style="68" min="64" max="16384"/>
+    <col width="9.140625" customWidth="1" style="68" min="20" max="64"/>
+    <col width="9.140625" customWidth="1" style="68" min="65" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" customFormat="1" customHeight="1" s="42">

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -2677,19 +2677,19 @@
         <v>182</v>
       </c>
       <c r="D10" s="47" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E10" s="47" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F10" s="47" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G10" s="47" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H10" s="47" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I10" s="43" t="n"/>
     </row>
@@ -2701,22 +2701,22 @@
         <v>8</v>
       </c>
       <c r="C11" s="47" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D11" s="47" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E11" s="47" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F11" s="47" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G11" s="47" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H11" s="47" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I11" s="43" t="n"/>
     </row>
@@ -2728,22 +2728,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="47" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D12" s="47" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E12" s="47" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I12" s="43" t="n"/>
     </row>
@@ -2755,22 +2755,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="47" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D13" s="47" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E13" s="47" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G13" s="47" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H13" s="47" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I13" s="43" t="n"/>
     </row>
@@ -2782,22 +2782,22 @@
         <v>8</v>
       </c>
       <c r="C14" s="47" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D14" s="47" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E14" s="47" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G14" s="47" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H14" s="47" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I14" s="43" t="n"/>
     </row>
@@ -2809,22 +2809,22 @@
         <v>8</v>
       </c>
       <c r="C15" s="47" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D15" s="47" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E15" s="47" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G15" s="47" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H15" s="47" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I15" s="43" t="n"/>
     </row>
@@ -2836,22 +2836,22 @@
         <v>8</v>
       </c>
       <c r="C16" s="47" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D16" s="47" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E16" s="47" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G16" s="47" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H16" s="47" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I16" s="43" t="n"/>
     </row>
@@ -2863,22 +2863,22 @@
         <v>8</v>
       </c>
       <c r="C17" s="47" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D17" s="47" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E17" s="47" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G17" s="47" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H17" s="47" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I17" s="43" t="n"/>
     </row>
@@ -2890,22 +2890,22 @@
         <v>8</v>
       </c>
       <c r="C18" s="47" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D18" s="47" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E18" s="47" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G18" s="47" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H18" s="47" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I18" s="43" t="n"/>
     </row>
@@ -2917,22 +2917,22 @@
         <v>8</v>
       </c>
       <c r="C19" s="47" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D19" s="47" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E19" s="47" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G19" s="47" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H19" s="47" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I19" s="43" t="n"/>
     </row>
@@ -2944,22 +2944,22 @@
         <v>8</v>
       </c>
       <c r="C20" s="47" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D20" s="47" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E20" s="47" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G20" s="47" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H20" s="47" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I20" s="43" t="n"/>
     </row>
@@ -2971,22 +2971,22 @@
         <v>8</v>
       </c>
       <c r="C21" s="47" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D21" s="47" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E21" s="47" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G21" s="47" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H21" s="47" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I21" s="43" t="n"/>
     </row>
@@ -2998,22 +2998,22 @@
         <v>8</v>
       </c>
       <c r="C22" s="47" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D22" s="47" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E22" s="47" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G22" s="47" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="H22" s="47" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I22" s="43" t="n"/>
     </row>
@@ -3025,22 +3025,22 @@
         <v>8</v>
       </c>
       <c r="C23" s="47" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D23" s="47" t="n">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E23" s="47" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G23" s="47" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="H23" s="47" t="n">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I23" s="43" t="n"/>
     </row>
@@ -3052,22 +3052,22 @@
         <v>8</v>
       </c>
       <c r="C24" s="47" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D24" s="47" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E24" s="47" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G24" s="47" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H24" s="47" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I24" s="43" t="n"/>
     </row>
@@ -3079,22 +3079,22 @@
         <v>8</v>
       </c>
       <c r="C25" s="47" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D25" s="47" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E25" s="47" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G25" s="47" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H25" s="47" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I25" s="43" t="n"/>
     </row>
@@ -3106,22 +3106,22 @@
         <v>8</v>
       </c>
       <c r="C26" s="47" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D26" s="47" t="n">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E26" s="47" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G26" s="47" t="n">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H26" s="47" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="I26" s="43" t="n"/>
     </row>
@@ -3133,22 +3133,22 @@
         <v>8</v>
       </c>
       <c r="C27" s="47" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D27" s="47" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E27" s="47" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G27" s="47" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H27" s="47" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="I27" s="43" t="n"/>
     </row>
@@ -3160,22 +3160,22 @@
         <v>8</v>
       </c>
       <c r="C28" s="47" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D28" s="47" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E28" s="47" t="n">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="G28" s="47" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="H28" s="47" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="I28" s="43" t="n"/>
     </row>
@@ -3187,22 +3187,22 @@
         <v>9</v>
       </c>
       <c r="C29" s="47" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D29" s="47" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E29" s="47" t="n">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="G29" s="47" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="H29" s="47" t="n">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="I29" s="43" t="n"/>
     </row>
@@ -3214,22 +3214,22 @@
         <v>9</v>
       </c>
       <c r="C30" s="47" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D30" s="47" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E30" s="47" t="n">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G30" s="47" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H30" s="47" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I30" s="43" t="n"/>
     </row>
@@ -3241,22 +3241,22 @@
         <v>9</v>
       </c>
       <c r="C31" s="47" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D31" s="47" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E31" s="47" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="G31" s="47" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H31" s="47" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="I31" s="43" t="n"/>
     </row>
@@ -3268,22 +3268,22 @@
         <v>9</v>
       </c>
       <c r="C32" s="47" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D32" s="47" t="n">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="E32" s="47" t="n">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="G32" s="47" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="H32" s="47" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="I32" s="43" t="n"/>
     </row>
@@ -3295,22 +3295,22 @@
         <v>9</v>
       </c>
       <c r="C33" s="47" t="n">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D33" s="47" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E33" s="47" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="G33" s="47" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="H33" s="47" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="I33" s="43" t="n"/>
     </row>
@@ -3322,22 +3322,22 @@
         <v>9</v>
       </c>
       <c r="C34" s="47" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D34" s="47" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E34" s="47" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="G34" s="47" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="H34" s="47" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="I34" s="43" t="n"/>
     </row>
@@ -3349,22 +3349,22 @@
         <v>9</v>
       </c>
       <c r="C35" s="47" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D35" s="47" t="n">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E35" s="47" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="G35" s="47" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H35" s="47" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="I35" s="43" t="n"/>
     </row>
@@ -3376,22 +3376,22 @@
         <v>9</v>
       </c>
       <c r="C36" s="47" t="n">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="D36" s="47" t="n">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="E36" s="47" t="n">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="G36" s="47" t="n">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="H36" s="47" t="n">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="I36" s="43" t="n"/>
     </row>
@@ -3403,22 +3403,22 @@
         <v>9</v>
       </c>
       <c r="C37" s="47" t="n">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D37" s="47" t="n">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="E37" s="47" t="n">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="G37" s="47" t="n">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="H37" s="47" t="n">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="I37" s="43" t="n"/>
     </row>
@@ -3430,22 +3430,22 @@
         <v>9</v>
       </c>
       <c r="C38" s="47" t="n">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D38" s="47" t="n">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="E38" s="47" t="n">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="G38" s="47" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="H38" s="47" t="n">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="I38" s="43" t="n"/>
     </row>
@@ -3457,22 +3457,22 @@
         <v>9</v>
       </c>
       <c r="C39" s="47" t="n">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="D39" s="47" t="n">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="E39" s="47" t="n">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="G39" s="47" t="n">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="H39" s="47" t="n">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="I39" s="43" t="n"/>
     </row>
@@ -3484,22 +3484,22 @@
         <v>9</v>
       </c>
       <c r="C40" s="47" t="n">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="D40" s="47" t="n">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="E40" s="47" t="n">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="G40" s="47" t="n">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="H40" s="47" t="n">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="I40" s="43" t="n"/>
     </row>
@@ -3511,22 +3511,22 @@
         <v>9</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="I41" s="77" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
         <v>9</v>
       </c>
       <c r="C42" s="47" t="n">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="D42" s="47" t="n">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="E42" s="47" t="n">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="G42" s="47" t="n">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="H42" s="47" t="n">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="I42" s="77" t="n"/>
     </row>
@@ -3569,22 +3569,22 @@
         <v>9</v>
       </c>
       <c r="C43" s="47" t="n">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="D43" s="47" t="n">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="E43" s="47" t="n">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="G43" s="47" t="n">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="H43" s="47" t="n">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="I43" s="77" t="n"/>
     </row>
@@ -3596,22 +3596,22 @@
         <v>9</v>
       </c>
       <c r="C44" s="47" t="n">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="D44" s="47" t="n">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="E44" s="47" t="n">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="G44" s="47" t="n">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="H44" s="47" t="n">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="I44" s="77" t="n"/>
     </row>
@@ -3623,22 +3623,22 @@
         <v>9</v>
       </c>
       <c r="C45" s="47" t="n">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="D45" s="47" t="n">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="E45" s="47" t="n">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="G45" s="47" t="n">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="H45" s="47" t="n">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="I45" s="77" t="n"/>
     </row>
@@ -3650,22 +3650,22 @@
         <v>9</v>
       </c>
       <c r="C46" s="47" t="n">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="D46" s="47" t="n">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="E46" s="47" t="n">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="G46" s="47" t="n">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="H46" s="47" t="n">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="I46" s="77" t="n"/>
     </row>
@@ -3677,22 +3677,22 @@
         <v>9</v>
       </c>
       <c r="C47" s="47" t="n">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="D47" s="47" t="n">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="E47" s="47" t="n">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="G47" s="47" t="n">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="H47" s="47" t="n">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="I47" s="77" t="n"/>
     </row>
@@ -3704,22 +3704,22 @@
         <v>9</v>
       </c>
       <c r="C48" s="47" t="n">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="D48" s="47" t="n">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="E48" s="47" t="n">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="G48" s="47" t="n">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="H48" s="47" t="n">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="I48" s="77" t="n"/>
     </row>
@@ -3731,22 +3731,22 @@
         <v>9</v>
       </c>
       <c r="C49" s="47" t="n">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="D49" s="47" t="n">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="E49" s="47" t="n">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="G49" s="47" t="n">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="H49" s="47" t="n">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="I49" s="77" t="n"/>
     </row>
@@ -3758,22 +3758,22 @@
         <v>9</v>
       </c>
       <c r="C50" s="47" t="n">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="D50" s="47" t="n">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="E50" s="47" t="n">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="G50" s="47" t="n">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="H50" s="47" t="n">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="I50" s="77" t="n"/>
     </row>
@@ -3785,22 +3785,22 @@
         <v>9</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="I51" s="77" t="inlineStr">
         <is>
@@ -18283,8 +18283,8 @@
       <c r="B3" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="47" t="n"/>
-      <c r="D3" s="47" t="n"/>
+      <c r="C3" s="47" t="inlineStr"/>
+      <c r="D3" s="47" t="inlineStr"/>
       <c r="E3" s="47" t="n"/>
       <c r="F3" s="47" t="n">
         <v>45</v>
@@ -18324,8 +18324,8 @@
       <c r="B4" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="47" t="n"/>
-      <c r="D4" s="47" t="n"/>
+      <c r="C4" s="47" t="inlineStr"/>
+      <c r="D4" s="47" t="inlineStr"/>
       <c r="E4" s="47" t="n"/>
       <c r="F4" s="47" t="n">
         <v>71</v>
@@ -18365,10 +18365,10 @@
       <c r="B5" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
+      <c r="C5" s="47" t="inlineStr"/>
+      <c r="D5" s="47" t="inlineStr"/>
       <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
+      <c r="F5" s="47" t="inlineStr"/>
       <c r="G5" s="47" t="n">
         <v>107</v>
       </c>
